--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$123</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5091" uniqueCount="825">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4571" uniqueCount="772">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T08:09:20+00:00</t>
+    <t>2026-01-28T19:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -921,144 +921,6 @@
     <t>MedicationRequest.medication[x].coding</t>
   </si>
   <si>
-    <t>MedicationRequest.medication[x]:medicationCodeableConcept.coding.id</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x].coding.id</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x]:medicationCodeableConcept.coding.extension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x].coding.extension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x]:medicationCodeableConcept.coding.system</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x].coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x]:medicationCodeableConcept.coding.version</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x].coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x]:medicationCodeableConcept.coding.code</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x].coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x]:medicationCodeableConcept.coding.display</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x].coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x]:medicationCodeableConcept.coding.userSelected</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x].coding.userSelected</t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
     <t>MedicationRequest.medication[x]:medicationCodeableConcept.text</t>
   </si>
   <si>
@@ -1312,27 +1174,6 @@
     <t>MedicationRequest.reasonCode.coding</t>
   </si>
   <si>
-    <t>MedicationRequest.reasonCode.coding.id</t>
-  </si>
-  <si>
-    <t>MedicationRequest.reasonCode.coding.extension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.reasonCode.coding.system</t>
-  </si>
-  <si>
-    <t>MedicationRequest.reasonCode.coding.version</t>
-  </si>
-  <si>
-    <t>MedicationRequest.reasonCode.coding.code</t>
-  </si>
-  <si>
-    <t>MedicationRequest.reasonCode.coding.display</t>
-  </si>
-  <si>
-    <t>MedicationRequest.reasonCode.coding.userSelected</t>
-  </si>
-  <si>
     <t>MedicationRequest.reasonCode.text</t>
   </si>
   <si>
@@ -1386,11 +1227,12 @@
     <t>MedicationRequest.basedOn</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-emed-mr-planeintrag)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|MedicationRequest|4.0.1|ServiceRequest|4.0.1|ImmunizationRecommendation|4.0.1)
 </t>
   </si>
   <si>
-    <t>Referenz auf einen zugrundeliegenden Medikationsplaneintrag. Verwendung im Medikationsplaneintrag zu prüfen: Bsp. nach einer Änderung; evtl. priorPrescription.</t>
+    <t>Verwendung im Medikationsplaneintrag zu prüfen. Nach einer Änderung kann mit priorPrescription auf die Vorversion referenziert werden.
+Sinnvoll wäre evtl. Referenz auf Medikationsplan (List), ist aber mit basedOn nicht möglich.</t>
   </si>
   <si>
     <t>A plan or request that is fulfilled in whole or in part by this medication request.</t>
@@ -2450,7 +2292,7 @@
     <t>MedicationRequest.substitution</t>
   </si>
   <si>
-    <t>Gibt an, ob eine Substitution Teil der Abgabe sein kann / sollte / nicht sein darf. Dieser Block erläutert die Absicht des Arztes, der den Medikationsplaneintrag erstellt. Wenn nichts angegeben ist, kann eine Substitution vorgenommen werden. -&gt; Zu prüfen ob Verwendung im Medikationsplaneintrag, Dokumentation über Substitution erfolg in der Dispenses-Resource.</t>
+    <t>Gibt an, ob eine Substitution Teil der Abgabe sein kann / sollte / nicht sein darf. Dieser Block erläutert die Absicht des Arztes, der den Medikationsplaneintrag erstellt. Wenn nichts angegeben ist, kann eine Substitution vorgenommen werden. -&gt; Zu prüfen ob Verwendung im Medikationsplaneintrag, Dokumentation über Substitution erfolg in der Dispense-Resource.</t>
   </si>
   <si>
     <t>Indicates whether or not substitution can or should be part of the dispense. In some cases, substitution must happen, in other cases substitution must not happen. This block explains the prescriber's intent. If nothing is specified substitution may be done.</t>
@@ -2526,7 +2368,7 @@
 </t>
   </si>
   <si>
-    <t>Im Falle einer Änderung wird auf den ersetzten Medikationsplaneintrag verwiesen.</t>
+    <t>Im Falle einer Änderung wird auf den ersetzten Medikationsplaneintrag verwiesen. Unterscheidung zu basedOn ?</t>
   </si>
   <si>
     <t>A link to a resource representing an earlier order related order or prescription.</t>
@@ -2905,10 +2747,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO137"/>
+  <dimension ref="A1:AO123"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="67.0546875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="58.75" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="53.40234375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="23.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
@@ -5641,7 +5483,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>250</v>
       </c>
@@ -5660,7 +5502,7 @@
         <v>90</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>91</v>
@@ -6481,19 +6323,23 @@
         <v>21</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
         <v>214</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
+        <v>236</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>21</v>
       </c>
@@ -6541,7 +6387,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -6553,7 +6399,7 @@
         <v>21</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>21</v>
@@ -6562,53 +6408,55 @@
         <v>21</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>218</v>
+        <v>240</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>21</v>
+        <v>241</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>287</v>
       </c>
       <c r="B32" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="C32" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>159</v>
+        <v>21</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>135</v>
+        <v>289</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>220</v>
+        <v>290</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>221</v>
+        <v>264</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>162</v>
+        <v>265</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6646,54 +6494,54 @@
         <v>21</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>222</v>
+        <v>21</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>223</v>
+        <v>261</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>21</v>
+        <v>270</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>21</v>
+        <v>271</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>218</v>
+        <v>272</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>21</v>
+        <v>273</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>21</v>
+        <v>274</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6707,7 +6555,7 @@
         <v>90</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>21</v>
@@ -6716,20 +6564,18 @@
         <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>104</v>
+        <v>292</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>294</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>21</v>
       </c>
@@ -6777,10 +6623,10 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>90</v>
@@ -6792,27 +6638,27 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>21</v>
+        <v>296</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>21</v>
+        <v>297</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>21</v>
+        <v>299</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6823,7 +6669,7 @@
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>21</v>
@@ -6832,19 +6678,19 @@
         <v>21</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>214</v>
+        <v>302</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6894,7 +6740,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6909,27 +6755,27 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>21</v>
+        <v>306</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>21</v>
+        <v>183</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>21</v>
+        <v>308</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6937,10 +6783,10 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>21</v>
@@ -6949,21 +6795,19 @@
         <v>21</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>110</v>
+        <v>311</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="N35" s="2"/>
-      <c r="O35" t="s" s="2">
-        <v>310</v>
-      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>21</v>
       </c>
@@ -7011,13 +6855,13 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>21</v>
@@ -7026,27 +6870,27 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>21</v>
+        <v>314</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>21</v>
+        <v>308</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>313</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7060,7 +6904,7 @@
         <v>90</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>21</v>
@@ -7069,18 +6913,16 @@
         <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>214</v>
+        <v>317</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="N36" s="2"/>
-      <c r="O36" t="s" s="2">
-        <v>318</v>
-      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>21</v>
       </c>
@@ -7128,7 +6970,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -7143,27 +6985,27 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>21</v>
+        <v>320</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>21</v>
+        <v>321</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>21</v>
+        <v>323</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7171,13 +7013,13 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>21</v>
@@ -7186,20 +7028,16 @@
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>251</v>
+        <v>326</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>327</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>21</v>
       </c>
@@ -7247,7 +7085,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -7262,19 +7100,19 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>21</v>
+        <v>329</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>329</v>
+        <v>298</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>21</v>
+        <v>330</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>330</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38" hidden="true">
@@ -7282,7 +7120,7 @@
         <v>331</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7293,7 +7131,7 @@
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>21</v>
@@ -7302,23 +7140,19 @@
         <v>21</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>214</v>
+        <v>332</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>235</v>
+        <v>333</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>238</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>21</v>
       </c>
@@ -7366,7 +7200,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>239</v>
+        <v>331</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -7381,31 +7215,29 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>21</v>
+        <v>335</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>240</v>
+        <v>336</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>21</v>
+        <v>337</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>241</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="C39" t="s" s="2">
-        <v>334</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>21</v>
       </c>
@@ -7414,10 +7246,10 @@
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>21</v>
@@ -7426,16 +7258,16 @@
         <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>335</v>
+        <v>187</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>264</v>
+        <v>340</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>265</v>
+        <v>341</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7461,13 +7293,13 @@
         <v>21</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>21</v>
+        <v>191</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>21</v>
+        <v>342</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>21</v>
+        <v>343</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>21</v>
@@ -7485,10 +7317,10 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>261</v>
+        <v>338</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>90</v>
@@ -7500,27 +7332,27 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>270</v>
+        <v>344</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>271</v>
+        <v>21</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>272</v>
+        <v>345</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>273</v>
+        <v>21</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>274</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7528,32 +7360,30 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>341</v>
-      </c>
+        <v>349</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>21</v>
@@ -7602,10 +7432,10 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>90</v>
@@ -7617,27 +7447,27 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>342</v>
+        <v>21</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>343</v>
+        <v>21</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>346</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7648,10 +7478,10 @@
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>21</v>
@@ -7660,16 +7490,16 @@
         <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>348</v>
+        <v>187</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7695,13 +7525,13 @@
         <v>21</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>21</v>
+        <v>191</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>21</v>
+        <v>356</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>21</v>
+        <v>357</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>21</v>
@@ -7719,13 +7549,13 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>21</v>
@@ -7734,27 +7564,27 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>183</v>
+        <v>359</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>355</v>
+        <v>362</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7765,7 +7595,7 @@
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>21</v>
@@ -7777,13 +7607,13 @@
         <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>357</v>
+        <v>214</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>358</v>
+        <v>215</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>359</v>
+        <v>216</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7834,73 +7664,75 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>356</v>
+        <v>217</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>360</v>
+        <v>21</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>361</v>
+        <v>218</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>354</v>
+        <v>21</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>21</v>
+        <v>159</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>363</v>
+        <v>135</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>364</v>
+        <v>220</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>221</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>21</v>
@@ -7937,54 +7769,54 @@
         <v>21</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>21</v>
+        <v>222</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>362</v>
+        <v>223</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>366</v>
+        <v>21</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>367</v>
+        <v>21</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>368</v>
+        <v>218</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>369</v>
+        <v>21</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>370</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7995,10 +7827,10 @@
         <v>90</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>21</v>
@@ -8007,16 +7839,20 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>372</v>
+        <v>225</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>373</v>
+        <v>226</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+        <v>227</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>21</v>
       </c>
@@ -8064,13 +7900,13 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>371</v>
+        <v>231</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>21</v>
@@ -8079,27 +7915,27 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>375</v>
+        <v>21</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>344</v>
+        <v>232</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>376</v>
+        <v>21</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>21</v>
+        <v>233</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>377</v>
+        <v>366</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>377</v>
+        <v>366</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8110,7 +7946,7 @@
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>21</v>
@@ -8119,19 +7955,23 @@
         <v>21</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>378</v>
+        <v>214</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>379</v>
+        <v>235</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+        <v>236</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>21</v>
       </c>
@@ -8179,7 +8019,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>377</v>
+        <v>239</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -8194,27 +8034,27 @@
         <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>381</v>
+        <v>21</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>382</v>
+        <v>240</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>383</v>
+        <v>21</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>21</v>
+        <v>241</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
-        <v>384</v>
+        <v>367</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>384</v>
+        <v>367</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8225,28 +8065,28 @@
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>187</v>
+        <v>368</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>385</v>
+        <v>353</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>386</v>
+        <v>369</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>387</v>
+        <v>370</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -8272,13 +8112,13 @@
         <v>21</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>388</v>
+        <v>21</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>389</v>
+        <v>21</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>21</v>
@@ -8296,13 +8136,13 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>384</v>
+        <v>367</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>21</v>
@@ -8311,16 +8151,16 @@
         <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>390</v>
+        <v>371</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>21</v>
+        <v>183</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>391</v>
+        <v>372</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>21</v>
+        <v>361</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>21</v>
@@ -8328,10 +8168,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>392</v>
+        <v>373</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>392</v>
+        <v>373</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8351,16 +8191,16 @@
         <v>21</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>393</v>
+        <v>374</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>394</v>
+        <v>375</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>395</v>
+        <v>376</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -8411,13 +8251,13 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>392</v>
+        <v>373</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>21</v>
@@ -8426,27 +8266,27 @@
         <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>21</v>
+        <v>377</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>396</v>
+        <v>378</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>397</v>
+        <v>21</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>398</v>
+        <v>379</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>398</v>
+        <v>379</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8457,29 +8297,27 @@
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J48" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I48" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J48" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K48" t="s" s="2">
-        <v>187</v>
+        <v>104</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>399</v>
+        <v>380</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>401</v>
-      </c>
+        <v>381</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>21</v>
@@ -8504,13 +8342,13 @@
         <v>21</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>402</v>
+        <v>21</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>403</v>
+        <v>21</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>21</v>
@@ -8528,7 +8366,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>398</v>
+        <v>379</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8543,27 +8381,27 @@
         <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>404</v>
+        <v>21</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>405</v>
+        <v>21</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>406</v>
+        <v>378</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>407</v>
+        <v>21</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>408</v>
+        <v>21</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>409</v>
+        <v>382</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>409</v>
+        <v>382</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8574,7 +8412,7 @@
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>21</v>
@@ -8583,16 +8421,16 @@
         <v>21</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>214</v>
+        <v>383</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>215</v>
+        <v>384</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>216</v>
+        <v>385</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8643,28 +8481,28 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>217</v>
+        <v>382</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>21</v>
+        <v>386</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>218</v>
+        <v>387</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>21</v>
@@ -8675,21 +8513,21 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>410</v>
+        <v>388</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>410</v>
+        <v>388</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>159</v>
+        <v>21</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>21</v>
@@ -8698,21 +8536,21 @@
         <v>21</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>135</v>
+        <v>166</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>220</v>
+        <v>389</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O50" s="2"/>
+        <v>390</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" t="s" s="2">
+        <v>391</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>21</v>
       </c>
@@ -8748,40 +8586,40 @@
         <v>21</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>222</v>
+        <v>21</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>223</v>
+        <v>388</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>21</v>
+        <v>392</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>218</v>
+        <v>393</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>21</v>
@@ -8790,12 +8628,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
-        <v>411</v>
+        <v>394</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>411</v>
+        <v>394</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8803,35 +8641,33 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G51" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="G51" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="H51" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>225</v>
+        <v>187</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>226</v>
+        <v>395</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>227</v>
+        <v>396</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>397</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>21</v>
       </c>
@@ -8855,13 +8691,13 @@
         <v>21</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>21</v>
+        <v>191</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>21</v>
+        <v>398</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>21</v>
+        <v>399</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>21</v>
@@ -8879,13 +8715,13 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>231</v>
+        <v>394</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>21</v>
@@ -8900,21 +8736,21 @@
         <v>21</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>232</v>
+        <v>400</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>233</v>
+        <v>21</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8925,7 +8761,7 @@
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>21</v>
@@ -8937,13 +8773,13 @@
         <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>214</v>
+        <v>402</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>215</v>
+        <v>403</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>216</v>
+        <v>404</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8994,28 +8830,28 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>217</v>
+        <v>401</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>21</v>
+        <v>405</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>218</v>
+        <v>406</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>21</v>
@@ -9026,14 +8862,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>159</v>
+        <v>21</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -9052,17 +8888,15 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>135</v>
+        <v>408</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>220</v>
+        <v>409</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>162</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>21</v>
@@ -9099,19 +8933,19 @@
         <v>21</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>222</v>
+        <v>21</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>223</v>
+        <v>407</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -9123,16 +8957,16 @@
         <v>21</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>21</v>
+        <v>411</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>21</v>
+        <v>412</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>218</v>
+        <v>413</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>21</v>
@@ -9154,10 +8988,10 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>21</v>
@@ -9166,23 +9000,21 @@
         <v>21</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>104</v>
+        <v>415</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>291</v>
+        <v>416</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>292</v>
+        <v>417</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>294</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>21</v>
       </c>
@@ -9230,13 +9062,13 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>295</v>
+        <v>414</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>21</v>
@@ -9245,27 +9077,27 @@
         <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>21</v>
+        <v>419</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>296</v>
+        <v>420</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>297</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9285,20 +9117,18 @@
         <v>21</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
         <v>214</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>300</v>
+        <v>215</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>302</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>21</v>
@@ -9347,7 +9177,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>303</v>
+        <v>217</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -9359,7 +9189,7 @@
         <v>21</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>21</v>
@@ -9368,32 +9198,32 @@
         <v>21</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>304</v>
+        <v>218</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>305</v>
+        <v>21</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>21</v>
+        <v>159</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>21</v>
@@ -9402,21 +9232,21 @@
         <v>21</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>308</v>
+        <v>220</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" t="s" s="2">
-        <v>310</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>21</v>
       </c>
@@ -9452,31 +9282,31 @@
         <v>21</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>21</v>
+        <v>222</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>311</v>
+        <v>223</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>21</v>
@@ -9485,54 +9315,56 @@
         <v>21</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>312</v>
+        <v>218</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>313</v>
+        <v>21</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>21</v>
+        <v>424</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J57" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>214</v>
+        <v>135</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>316</v>
+        <v>425</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>426</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="O57" t="s" s="2">
-        <v>318</v>
+        <v>163</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>21</v>
@@ -9581,19 +9413,19 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>319</v>
+        <v>427</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>21</v>
@@ -9602,21 +9434,21 @@
         <v>21</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>320</v>
+        <v>133</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>321</v>
+        <v>21</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9639,19 +9471,17 @@
         <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>251</v>
+        <v>429</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>324</v>
+        <v>430</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>326</v>
-      </c>
+        <v>431</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>327</v>
+        <v>432</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>21</v>
@@ -9700,7 +9530,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>328</v>
+        <v>433</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9721,21 +9551,21 @@
         <v>21</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>329</v>
+        <v>434</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>330</v>
+        <v>435</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>419</v>
+        <v>436</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>419</v>
+        <v>436</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9761,16 +9591,14 @@
         <v>214</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>235</v>
+        <v>437</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>237</v>
-      </c>
+        <v>438</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>238</v>
+        <v>439</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>21</v>
@@ -9819,7 +9647,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>239</v>
+        <v>440</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9840,21 +9668,21 @@
         <v>21</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>240</v>
+        <v>434</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>241</v>
+        <v>441</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>420</v>
+        <v>442</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>420</v>
+        <v>442</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9868,27 +9696,29 @@
         <v>81</v>
       </c>
       <c r="H60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J60" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J60" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K60" t="s" s="2">
-        <v>421</v>
+        <v>187</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>399</v>
+        <v>443</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>422</v>
+        <v>444</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>445</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>446</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>21</v>
       </c>
@@ -9912,13 +9742,13 @@
         <v>21</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>21</v>
+        <v>191</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>21</v>
+        <v>447</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>21</v>
+        <v>448</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>21</v>
@@ -9936,7 +9766,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>420</v>
+        <v>449</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9951,27 +9781,27 @@
         <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>424</v>
+        <v>21</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>183</v>
+        <v>21</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>407</v>
+        <v>21</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>21</v>
+        <v>450</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>426</v>
+        <v>451</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>426</v>
+        <v>451</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9982,7 +9812,7 @@
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>21</v>
@@ -9994,13 +9824,13 @@
         <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>427</v>
+        <v>214</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>428</v>
+        <v>452</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>429</v>
+        <v>453</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -10051,13 +9881,13 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>426</v>
+        <v>454</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>21</v>
@@ -10066,27 +9896,27 @@
         <v>102</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>430</v>
+        <v>21</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>21</v>
+        <v>450</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>432</v>
+        <v>455</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>432</v>
+        <v>455</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10097,7 +9927,7 @@
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>21</v>
@@ -10109,16 +9939,20 @@
         <v>91</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>104</v>
+        <v>456</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>433</v>
+        <v>457</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+        <v>458</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>460</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>21</v>
       </c>
@@ -10166,13 +10000,13 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>432</v>
+        <v>461</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>21</v>
@@ -10187,7 +10021,7 @@
         <v>21</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>431</v>
+        <v>462</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>21</v>
@@ -10198,10 +10032,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>435</v>
+        <v>463</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>435</v>
+        <v>463</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10221,16 +10055,16 @@
         <v>21</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>436</v>
+        <v>214</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>437</v>
+        <v>215</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>438</v>
+        <v>216</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -10281,28 +10115,28 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>435</v>
+        <v>217</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>439</v>
+        <v>21</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>440</v>
+        <v>218</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>21</v>
@@ -10313,21 +10147,21 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>441</v>
+        <v>464</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>441</v>
+        <v>464</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>21</v>
+        <v>159</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>21</v>
@@ -10336,21 +10170,21 @@
         <v>21</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>166</v>
+        <v>135</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>442</v>
+        <v>220</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="N64" s="2"/>
-      <c r="O64" t="s" s="2">
-        <v>444</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>21</v>
       </c>
@@ -10386,40 +10220,40 @@
         <v>21</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>21</v>
+        <v>222</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>441</v>
+        <v>223</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>445</v>
+        <v>21</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>446</v>
+        <v>218</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>21</v>
@@ -10430,44 +10264,46 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>447</v>
+        <v>465</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>447</v>
+        <v>465</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>21</v>
+        <v>424</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>187</v>
+        <v>135</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>448</v>
+        <v>425</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>449</v>
+        <v>426</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="O65" s="2"/>
+        <v>162</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>21</v>
       </c>
@@ -10491,13 +10327,13 @@
         <v>21</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>451</v>
+        <v>21</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>452</v>
+        <v>21</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>21</v>
@@ -10515,19 +10351,19 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>447</v>
+        <v>427</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>21</v>
@@ -10536,7 +10372,7 @@
         <v>21</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>453</v>
+        <v>133</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>21</v>
@@ -10547,10 +10383,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>454</v>
+        <v>466</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>454</v>
+        <v>466</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10561,7 +10397,7 @@
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>21</v>
@@ -10570,19 +10406,21 @@
         <v>21</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>455</v>
+        <v>317</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>456</v>
+        <v>467</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+      <c r="O66" t="s" s="2">
+        <v>469</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>21</v>
       </c>
@@ -10630,7 +10468,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>454</v>
+        <v>470</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10645,13 +10483,13 @@
         <v>102</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>458</v>
+        <v>21</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>459</v>
+        <v>471</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>21</v>
@@ -10662,10 +10500,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10676,7 +10514,7 @@
         <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>21</v>
@@ -10685,19 +10523,21 @@
         <v>21</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>462</v>
+        <v>474</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>463</v>
+        <v>475</v>
       </c>
       <c r="N67" s="2"/>
-      <c r="O67" s="2"/>
+      <c r="O67" t="s" s="2">
+        <v>476</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>21</v>
       </c>
@@ -10745,28 +10585,28 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>460</v>
+        <v>477</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>102</v>
+        <v>478</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>464</v>
+        <v>21</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>465</v>
+        <v>21</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>466</v>
+        <v>479</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>21</v>
@@ -10777,10 +10617,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>467</v>
+        <v>480</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>467</v>
+        <v>480</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10791,7 +10631,7 @@
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>21</v>
@@ -10803,17 +10643,15 @@
         <v>21</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>468</v>
+        <v>214</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>469</v>
+        <v>215</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>471</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>21</v>
@@ -10862,28 +10700,28 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>467</v>
+        <v>217</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>472</v>
+        <v>21</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>473</v>
+        <v>218</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>21</v>
@@ -10894,21 +10732,21 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>21</v>
+        <v>159</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>21</v>
@@ -10920,15 +10758,17 @@
         <v>21</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>214</v>
+        <v>135</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>221</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>21</v>
@@ -10965,31 +10805,31 @@
         <v>21</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>21</v>
+        <v>222</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>21</v>
+        <v>141</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>21</v>
@@ -11009,21 +10849,21 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>159</v>
+        <v>21</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>21</v>
@@ -11032,20 +10872,18 @@
         <v>21</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>135</v>
+        <v>483</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>220</v>
+        <v>484</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>162</v>
-      </c>
+        <v>485</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>21</v>
@@ -11082,31 +10920,31 @@
         <v>21</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>222</v>
+        <v>21</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>223</v>
+        <v>486</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>21</v>
@@ -11115,7 +10953,7 @@
         <v>21</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>218</v>
+        <v>487</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>21</v>
@@ -11126,45 +10964,45 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>476</v>
+        <v>488</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>476</v>
+        <v>488</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>477</v>
+        <v>21</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J71" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>135</v>
+        <v>489</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>162</v>
+        <v>492</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>163</v>
+        <v>493</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>21</v>
@@ -11213,19 +11051,19 @@
         <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>480</v>
+        <v>494</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>21</v>
@@ -11234,7 +11072,7 @@
         <v>21</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>133</v>
+        <v>495</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>21</v>
@@ -11245,10 +11083,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>481</v>
+        <v>496</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>481</v>
+        <v>496</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11271,18 +11109,16 @@
         <v>91</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>483</v>
+        <v>497</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>484</v>
+        <v>498</v>
       </c>
       <c r="N72" s="2"/>
-      <c r="O72" t="s" s="2">
-        <v>485</v>
-      </c>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>21</v>
       </c>
@@ -11330,7 +11166,7 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>486</v>
+        <v>499</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -11351,21 +11187,21 @@
         <v>21</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>488</v>
+        <v>21</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>489</v>
+        <v>500</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>489</v>
+        <v>500</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11388,17 +11224,19 @@
         <v>91</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>214</v>
+        <v>501</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>490</v>
+        <v>502</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="N73" s="2"/>
+        <v>503</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>504</v>
+      </c>
       <c r="O73" t="s" s="2">
-        <v>492</v>
+        <v>505</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>21</v>
@@ -11447,7 +11285,7 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>493</v>
+        <v>506</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11468,21 +11306,21 @@
         <v>21</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>487</v>
+        <v>507</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>494</v>
+        <v>21</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>495</v>
+        <v>508</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>495</v>
+        <v>508</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11493,7 +11331,7 @@
         <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>21</v>
@@ -11505,19 +11343,19 @@
         <v>91</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>187</v>
+        <v>501</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>496</v>
+        <v>509</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>497</v>
+        <v>510</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>21</v>
@@ -11542,13 +11380,13 @@
         <v>21</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>501</v>
+        <v>21</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>21</v>
@@ -11566,13 +11404,13 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>502</v>
+        <v>511</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>21</v>
@@ -11587,21 +11425,21 @@
         <v>21</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>487</v>
+        <v>507</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>503</v>
+        <v>21</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11624,13 +11462,13 @@
         <v>91</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11657,13 +11495,13 @@
         <v>21</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>21</v>
+        <v>179</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>21</v>
+        <v>515</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>21</v>
+        <v>516</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>21</v>
@@ -11681,7 +11519,7 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>507</v>
+        <v>517</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11702,21 +11540,21 @@
         <v>21</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>487</v>
+        <v>518</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>503</v>
+        <v>21</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>508</v>
+        <v>519</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>508</v>
+        <v>519</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11739,24 +11577,22 @@
         <v>91</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>509</v>
+        <v>489</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>513</v>
-      </c>
+        <v>521</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q76" s="2"/>
+      <c r="Q76" t="s" s="2">
+        <v>522</v>
+      </c>
       <c r="R76" t="s" s="2">
         <v>21</v>
       </c>
@@ -11800,7 +11636,7 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>514</v>
+        <v>523</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11821,7 +11657,7 @@
         <v>21</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>21</v>
@@ -11832,10 +11668,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11855,16 +11691,16 @@
         <v>21</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>214</v>
+        <v>489</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>215</v>
+        <v>525</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>216</v>
+        <v>526</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11915,7 +11751,7 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>217</v>
+        <v>527</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11927,7 +11763,7 @@
         <v>21</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>21</v>
@@ -11936,7 +11772,7 @@
         <v>21</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>218</v>
+        <v>507</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>21</v>
@@ -11947,21 +11783,21 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>517</v>
+        <v>528</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>517</v>
+        <v>528</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>159</v>
+        <v>21</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>21</v>
@@ -11970,20 +11806,18 @@
         <v>21</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>135</v>
+        <v>501</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>220</v>
+        <v>529</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>162</v>
-      </c>
+        <v>530</v>
+      </c>
+      <c r="N78" s="2"/>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>21</v>
@@ -12020,31 +11854,31 @@
         <v>21</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AC78" t="s" s="2">
-        <v>222</v>
+        <v>21</v>
       </c>
       <c r="AD78" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>223</v>
+        <v>531</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>21</v>
@@ -12053,7 +11887,7 @@
         <v>21</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>218</v>
+        <v>507</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>21</v>
@@ -12064,46 +11898,42 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>518</v>
+        <v>532</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>518</v>
+        <v>532</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>477</v>
+        <v>21</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J79" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>135</v>
+        <v>501</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>478</v>
+        <v>533</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>534</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>21</v>
       </c>
@@ -12151,19 +11981,19 @@
         <v>21</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>480</v>
+        <v>535</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>21</v>
@@ -12172,7 +12002,7 @@
         <v>21</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>133</v>
+        <v>507</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>21</v>
@@ -12183,10 +12013,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>519</v>
+        <v>536</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>519</v>
+        <v>536</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12197,7 +12027,7 @@
         <v>80</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>21</v>
@@ -12209,18 +12039,16 @@
         <v>91</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>363</v>
+        <v>110</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>521</v>
+        <v>538</v>
       </c>
       <c r="N80" s="2"/>
-      <c r="O80" t="s" s="2">
-        <v>522</v>
-      </c>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>21</v>
       </c>
@@ -12244,13 +12072,13 @@
         <v>21</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>21</v>
+        <v>179</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>21</v>
+        <v>515</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>21</v>
+        <v>516</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>21</v>
@@ -12268,13 +12096,13 @@
         <v>21</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>523</v>
+        <v>539</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>21</v>
@@ -12289,7 +12117,7 @@
         <v>21</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>21</v>
@@ -12300,10 +12128,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>525</v>
+        <v>540</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>525</v>
+        <v>540</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12314,7 +12142,7 @@
         <v>80</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>21</v>
@@ -12326,18 +12154,18 @@
         <v>91</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>526</v>
+        <v>110</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>527</v>
+        <v>541</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="N81" s="2"/>
-      <c r="O81" t="s" s="2">
-        <v>529</v>
-      </c>
+        <v>542</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>21</v>
       </c>
@@ -12361,13 +12189,11 @@
         <v>21</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y81" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="Y81" s="2"/>
       <c r="Z81" t="s" s="2">
-        <v>21</v>
+        <v>544</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>21</v>
@@ -12385,19 +12211,19 @@
         <v>21</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>530</v>
+        <v>545</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>531</v>
+        <v>102</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>21</v>
@@ -12406,7 +12232,7 @@
         <v>21</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>532</v>
+        <v>218</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>21</v>
@@ -12417,10 +12243,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>533</v>
+        <v>546</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>533</v>
+        <v>546</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12431,7 +12257,7 @@
         <v>80</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>21</v>
@@ -12440,18 +12266,20 @@
         <v>21</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>214</v>
+        <v>547</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>215</v>
+        <v>548</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N82" s="2"/>
+        <v>549</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>550</v>
+      </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>21</v>
@@ -12500,19 +12328,19 @@
         <v>21</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>217</v>
+        <v>551</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>21</v>
@@ -12532,14 +12360,14 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>534</v>
+        <v>552</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>534</v>
+        <v>552</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>159</v>
+        <v>21</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -12555,21 +12383,23 @@
         <v>21</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>220</v>
+        <v>553</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>221</v>
+        <v>554</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O83" s="2"/>
+        <v>555</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>556</v>
+      </c>
       <c r="P83" t="s" s="2">
         <v>21</v>
       </c>
@@ -12593,31 +12423,29 @@
         <v>21</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="Y83" s="2"/>
       <c r="Z83" t="s" s="2">
-        <v>21</v>
+        <v>557</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AC83" t="s" s="2">
-        <v>222</v>
+        <v>21</v>
       </c>
       <c r="AD83" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>223</v>
+        <v>558</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12629,7 +12457,7 @@
         <v>21</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>21</v>
@@ -12638,7 +12466,7 @@
         <v>21</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>218</v>
+        <v>559</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>21</v>
@@ -12649,10 +12477,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>535</v>
+        <v>560</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>535</v>
+        <v>560</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12675,13 +12503,13 @@
         <v>91</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>536</v>
+        <v>561</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>537</v>
+        <v>562</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>538</v>
+        <v>563</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12732,7 +12560,7 @@
         <v>21</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>539</v>
+        <v>564</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12753,7 +12581,7 @@
         <v>21</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>540</v>
+        <v>565</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>21</v>
@@ -12764,10 +12592,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>541</v>
+        <v>566</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>541</v>
+        <v>566</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12790,20 +12618,18 @@
         <v>91</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>542</v>
+        <v>187</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>543</v>
+        <v>567</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>544</v>
+        <v>568</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>546</v>
-      </c>
+        <v>569</v>
+      </c>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>21</v>
       </c>
@@ -12827,13 +12653,13 @@
         <v>21</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>21</v>
+        <v>570</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>21</v>
+        <v>571</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>21</v>
@@ -12851,7 +12677,7 @@
         <v>21</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>547</v>
+        <v>572</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12872,7 +12698,7 @@
         <v>21</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>548</v>
+        <v>573</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>21</v>
@@ -12883,10 +12709,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>549</v>
+        <v>574</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>549</v>
+        <v>574</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12909,15 +12735,17 @@
         <v>91</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>542</v>
+        <v>575</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>550</v>
+        <v>576</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="N86" s="2"/>
+        <v>577</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>578</v>
+      </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>21</v>
@@ -12942,13 +12770,13 @@
         <v>21</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>21</v>
+        <v>191</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>21</v>
+        <v>579</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>21</v>
+        <v>580</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>21</v>
@@ -12966,7 +12794,7 @@
         <v>21</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>552</v>
+        <v>581</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12987,21 +12815,21 @@
         <v>21</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>548</v>
+        <v>582</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>21</v>
+        <v>583</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>553</v>
+        <v>584</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>553</v>
+        <v>584</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13024,19 +12852,19 @@
         <v>91</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>554</v>
+        <v>187</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>555</v>
+        <v>585</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>556</v>
+        <v>586</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>557</v>
+        <v>587</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>558</v>
+        <v>588</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>21</v>
@@ -13061,13 +12889,13 @@
         <v>21</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>21</v>
+        <v>191</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>21</v>
+        <v>589</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>21</v>
+        <v>590</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>21</v>
@@ -13085,7 +12913,7 @@
         <v>21</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>559</v>
+        <v>591</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -13106,21 +12934,21 @@
         <v>21</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>560</v>
+        <v>592</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>21</v>
+        <v>593</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>561</v>
+        <v>594</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>561</v>
+        <v>594</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13143,19 +12971,17 @@
         <v>91</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>554</v>
+        <v>187</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>562</v>
+        <v>595</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>557</v>
-      </c>
+        <v>596</v>
+      </c>
+      <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>558</v>
+        <v>597</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>21</v>
@@ -13180,13 +13006,13 @@
         <v>21</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>21</v>
+        <v>191</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>21</v>
+        <v>598</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>21</v>
+        <v>599</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>21</v>
@@ -13204,7 +13030,7 @@
         <v>21</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>564</v>
+        <v>600</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -13225,21 +13051,21 @@
         <v>21</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>560</v>
+        <v>601</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>21</v>
+        <v>602</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>565</v>
+        <v>603</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>565</v>
+        <v>603</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13262,16 +13088,20 @@
         <v>91</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>110</v>
+        <v>187</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>566</v>
+        <v>604</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="N89" s="2"/>
-      <c r="O89" s="2"/>
+        <v>605</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>607</v>
+      </c>
       <c r="P89" t="s" s="2">
         <v>21</v>
       </c>
@@ -13295,13 +13125,13 @@
         <v>21</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>568</v>
+        <v>608</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>569</v>
+        <v>609</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>21</v>
@@ -13319,7 +13149,7 @@
         <v>21</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>570</v>
+        <v>610</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -13340,21 +13170,21 @@
         <v>21</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>571</v>
+        <v>611</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>21</v>
+        <v>612</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>572</v>
+        <v>613</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>572</v>
+        <v>613</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13365,7 +13195,7 @@
         <v>80</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>21</v>
@@ -13377,22 +13207,20 @@
         <v>91</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>542</v>
+        <v>473</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>573</v>
+        <v>614</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>574</v>
+        <v>615</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q90" t="s" s="2">
-        <v>575</v>
-      </c>
+      <c r="Q90" s="2"/>
       <c r="R90" t="s" s="2">
         <v>21</v>
       </c>
@@ -13436,13 +13264,13 @@
         <v>21</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>576</v>
+        <v>616</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>21</v>
@@ -13457,21 +13285,21 @@
         <v>21</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>560</v>
+        <v>21</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>21</v>
+        <v>617</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>577</v>
+        <v>618</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>577</v>
+        <v>618</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13491,16 +13319,16 @@
         <v>21</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>542</v>
+        <v>214</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>578</v>
+        <v>215</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>579</v>
+        <v>216</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -13551,7 +13379,7 @@
         <v>21</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>580</v>
+        <v>217</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13563,7 +13391,7 @@
         <v>21</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>21</v>
@@ -13572,7 +13400,7 @@
         <v>21</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>560</v>
+        <v>218</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>21</v>
@@ -13583,21 +13411,21 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>581</v>
+        <v>619</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>581</v>
+        <v>619</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>21</v>
+        <v>159</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>21</v>
@@ -13606,18 +13434,20 @@
         <v>21</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>554</v>
+        <v>135</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>582</v>
+        <v>220</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="N92" s="2"/>
+        <v>221</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>21</v>
@@ -13654,31 +13484,31 @@
         <v>21</v>
       </c>
       <c r="AB92" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="AC92" t="s" s="2">
-        <v>21</v>
+        <v>222</v>
       </c>
       <c r="AD92" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE92" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>584</v>
+        <v>223</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>21</v>
@@ -13687,7 +13517,7 @@
         <v>21</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>560</v>
+        <v>218</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>21</v>
@@ -13698,10 +13528,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>585</v>
+        <v>620</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>585</v>
+        <v>620</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13724,16 +13554,18 @@
         <v>91</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>554</v>
+        <v>187</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>586</v>
+        <v>621</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>587</v>
+        <v>622</v>
       </c>
       <c r="N93" s="2"/>
-      <c r="O93" s="2"/>
+      <c r="O93" t="s" s="2">
+        <v>623</v>
+      </c>
       <c r="P93" t="s" s="2">
         <v>21</v>
       </c>
@@ -13757,13 +13589,13 @@
         <v>21</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>21</v>
+        <v>191</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>21</v>
+        <v>624</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>21</v>
+        <v>625</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>21</v>
@@ -13781,7 +13613,7 @@
         <v>21</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>588</v>
+        <v>626</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13802,21 +13634,21 @@
         <v>21</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>560</v>
+        <v>21</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>21</v>
+        <v>627</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>589</v>
+        <v>628</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>589</v>
+        <v>628</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13839,16 +13671,20 @@
         <v>91</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>110</v>
+        <v>629</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>590</v>
+        <v>630</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="N94" s="2"/>
-      <c r="O94" s="2"/>
+        <v>631</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>633</v>
+      </c>
       <c r="P94" t="s" s="2">
         <v>21</v>
       </c>
@@ -13872,13 +13708,13 @@
         <v>21</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>179</v>
+        <v>21</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>568</v>
+        <v>21</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>569</v>
+        <v>21</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>21</v>
@@ -13896,7 +13732,7 @@
         <v>21</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>592</v>
+        <v>634</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13917,21 +13753,21 @@
         <v>21</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>571</v>
+        <v>611</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>21</v>
+        <v>635</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>593</v>
+        <v>636</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>593</v>
+        <v>636</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13942,7 +13778,7 @@
         <v>80</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>21</v>
@@ -13954,18 +13790,20 @@
         <v>91</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>110</v>
+        <v>637</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>594</v>
+        <v>638</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>595</v>
+        <v>639</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="O95" s="2"/>
+        <v>640</v>
+      </c>
+      <c r="O95" t="s" s="2">
+        <v>641</v>
+      </c>
       <c r="P95" t="s" s="2">
         <v>21</v>
       </c>
@@ -13989,11 +13827,13 @@
         <v>21</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="Y95" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z95" t="s" s="2">
-        <v>597</v>
+        <v>21</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>21</v>
@@ -14011,13 +13851,13 @@
         <v>21</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>598</v>
+        <v>642</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>21</v>
@@ -14032,21 +13872,21 @@
         <v>21</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>218</v>
+        <v>643</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>21</v>
+        <v>644</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>599</v>
+        <v>645</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>599</v>
+        <v>645</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14057,7 +13897,7 @@
         <v>80</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>21</v>
@@ -14069,18 +13909,20 @@
         <v>91</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>600</v>
+        <v>646</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>601</v>
+        <v>647</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>602</v>
+        <v>648</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="O96" s="2"/>
+        <v>649</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>650</v>
+      </c>
       <c r="P96" t="s" s="2">
         <v>21</v>
       </c>
@@ -14128,13 +13970,13 @@
         <v>21</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>604</v>
+        <v>651</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>21</v>
@@ -14149,21 +13991,21 @@
         <v>21</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>218</v>
+        <v>652</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>21</v>
+        <v>653</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>605</v>
+        <v>654</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>605</v>
+        <v>654</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14174,7 +14016,7 @@
         <v>80</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>21</v>
@@ -14186,19 +14028,19 @@
         <v>91</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>110</v>
+        <v>655</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>606</v>
+        <v>656</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>607</v>
+        <v>657</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>608</v>
+        <v>658</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>609</v>
+        <v>659</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>21</v>
@@ -14223,11 +14065,13 @@
         <v>21</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="Y97" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z97" t="s" s="2">
-        <v>610</v>
+        <v>21</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>21</v>
@@ -14245,13 +14089,13 @@
         <v>21</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>611</v>
+        <v>660</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>21</v>
@@ -14266,7 +14110,7 @@
         <v>21</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>612</v>
+        <v>661</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>21</v>
@@ -14277,10 +14121,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>613</v>
+        <v>662</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>613</v>
+        <v>662</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14303,16 +14147,18 @@
         <v>91</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>614</v>
+        <v>655</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>615</v>
+        <v>663</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>616</v>
+        <v>664</v>
       </c>
       <c r="N98" s="2"/>
-      <c r="O98" s="2"/>
+      <c r="O98" t="s" s="2">
+        <v>665</v>
+      </c>
       <c r="P98" t="s" s="2">
         <v>21</v>
       </c>
@@ -14360,7 +14206,7 @@
         <v>21</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>617</v>
+        <v>666</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14381,7 +14227,7 @@
         <v>21</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>618</v>
+        <v>661</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>21</v>
@@ -14392,10 +14238,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>619</v>
+        <v>667</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>619</v>
+        <v>667</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14415,20 +14261,18 @@
         <v>21</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>187</v>
+        <v>668</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>620</v>
+        <v>669</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>622</v>
-      </c>
+        <v>670</v>
+      </c>
+      <c r="N99" s="2"/>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>21</v>
@@ -14453,13 +14297,13 @@
         <v>21</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>623</v>
+        <v>21</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>624</v>
+        <v>21</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>21</v>
@@ -14477,7 +14321,7 @@
         <v>21</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>625</v>
+        <v>667</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14495,10 +14339,10 @@
         <v>21</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>21</v>
+        <v>671</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>626</v>
+        <v>672</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>21</v>
@@ -14509,10 +14353,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>627</v>
+        <v>673</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>627</v>
+        <v>673</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14532,20 +14376,18 @@
         <v>21</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>628</v>
+        <v>214</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>629</v>
+        <v>215</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>631</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="N100" s="2"/>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>21</v>
@@ -14570,13 +14412,13 @@
         <v>21</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>632</v>
+        <v>21</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>633</v>
+        <v>21</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>21</v>
@@ -14594,7 +14436,7 @@
         <v>21</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>634</v>
+        <v>217</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14606,7 +14448,7 @@
         <v>21</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>21</v>
@@ -14615,32 +14457,32 @@
         <v>21</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>635</v>
+        <v>218</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>636</v>
+        <v>21</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>637</v>
+        <v>674</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>637</v>
+        <v>674</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>21</v>
+        <v>159</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>21</v>
@@ -14649,23 +14491,21 @@
         <v>21</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>187</v>
+        <v>135</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>638</v>
+        <v>220</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>639</v>
+        <v>221</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>641</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>21</v>
       </c>
@@ -14689,13 +14529,13 @@
         <v>21</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>642</v>
+        <v>21</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>643</v>
+        <v>21</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>21</v>
@@ -14713,19 +14553,19 @@
         <v>21</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>644</v>
+        <v>223</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>21</v>
@@ -14734,54 +14574,56 @@
         <v>21</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>645</v>
+        <v>218</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>646</v>
+        <v>21</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>647</v>
+        <v>675</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>647</v>
+        <v>675</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>21</v>
+        <v>424</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I102" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J102" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>187</v>
+        <v>135</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>648</v>
+        <v>425</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="N102" s="2"/>
+        <v>426</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="O102" t="s" s="2">
-        <v>650</v>
+        <v>163</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>21</v>
@@ -14806,13 +14648,13 @@
         <v>21</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>651</v>
+        <v>21</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>652</v>
+        <v>21</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>21</v>
@@ -14830,19 +14672,19 @@
         <v>21</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>653</v>
+        <v>427</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>21</v>
@@ -14851,21 +14693,21 @@
         <v>21</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>654</v>
+        <v>133</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>655</v>
+        <v>21</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>656</v>
+        <v>676</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>656</v>
+        <v>676</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14885,23 +14727,21 @@
         <v>21</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>187</v>
+        <v>668</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>657</v>
+        <v>677</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>658</v>
+        <v>678</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>660</v>
-      </c>
+        <v>679</v>
+      </c>
+      <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>21</v>
       </c>
@@ -14925,13 +14765,13 @@
         <v>21</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>661</v>
+        <v>21</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>662</v>
+        <v>21</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>21</v>
@@ -14949,7 +14789,7 @@
         <v>21</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>663</v>
+        <v>676</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14970,21 +14810,21 @@
         <v>21</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>664</v>
+        <v>680</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>665</v>
+        <v>21</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>666</v>
+        <v>681</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>666</v>
+        <v>681</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14995,7 +14835,7 @@
         <v>80</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>21</v>
@@ -15004,16 +14844,16 @@
         <v>21</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>526</v>
+        <v>214</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>667</v>
+        <v>215</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>668</v>
+        <v>216</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -15064,19 +14904,19 @@
         <v>21</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>669</v>
+        <v>217</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>21</v>
@@ -15085,32 +14925,32 @@
         <v>21</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>21</v>
+        <v>218</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>670</v>
+        <v>21</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>671</v>
+        <v>682</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>671</v>
+        <v>682</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>21</v>
+        <v>159</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>21</v>
@@ -15122,15 +14962,17 @@
         <v>21</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>214</v>
+        <v>135</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N105" s="2"/>
+        <v>221</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>21</v>
@@ -15179,19 +15021,19 @@
         <v>21</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>21</v>
+        <v>141</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>21</v>
@@ -15211,14 +15053,14 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>672</v>
+        <v>683</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>672</v>
+        <v>683</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>159</v>
+        <v>424</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -15231,24 +15073,26 @@
         <v>21</v>
       </c>
       <c r="I106" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K106" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>220</v>
+        <v>425</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>221</v>
+        <v>426</v>
       </c>
       <c r="N106" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="O106" s="2"/>
+      <c r="O106" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="P106" t="s" s="2">
         <v>21</v>
       </c>
@@ -15284,19 +15128,19 @@
         <v>21</v>
       </c>
       <c r="AB106" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AC106" t="s" s="2">
-        <v>222</v>
+        <v>21</v>
       </c>
       <c r="AD106" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE106" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>223</v>
+        <v>427</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15317,7 +15161,7 @@
         <v>21</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>218</v>
+        <v>133</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>21</v>
@@ -15328,10 +15172,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>673</v>
+        <v>684</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>673</v>
+        <v>684</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15351,21 +15195,19 @@
         <v>21</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>187</v>
+        <v>655</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>674</v>
+        <v>685</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>675</v>
+        <v>686</v>
       </c>
       <c r="N107" s="2"/>
-      <c r="O107" t="s" s="2">
-        <v>676</v>
-      </c>
+      <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>21</v>
       </c>
@@ -15389,13 +15231,13 @@
         <v>21</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>677</v>
+        <v>21</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>678</v>
+        <v>21</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>21</v>
@@ -15413,7 +15255,7 @@
         <v>21</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>679</v>
+        <v>684</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15434,21 +15276,21 @@
         <v>21</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>21</v>
+        <v>687</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>680</v>
+        <v>21</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>681</v>
+        <v>688</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>681</v>
+        <v>688</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15468,23 +15310,19 @@
         <v>21</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>682</v>
+        <v>689</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>683</v>
+        <v>690</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>684</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>685</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>686</v>
-      </c>
+        <v>691</v>
+      </c>
+      <c r="N108" s="2"/>
+      <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>21</v>
       </c>
@@ -15532,7 +15370,7 @@
         <v>21</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15553,21 +15391,21 @@
         <v>21</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>664</v>
+        <v>692</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>688</v>
+        <v>21</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15578,7 +15416,7 @@
         <v>80</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>21</v>
@@ -15587,23 +15425,19 @@
         <v>21</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>692</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>693</v>
-      </c>
-      <c r="O109" t="s" s="2">
-        <v>694</v>
-      </c>
+        <v>695</v>
+      </c>
+      <c r="N109" s="2"/>
+      <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>21</v>
       </c>
@@ -15651,7 +15485,7 @@
         <v>21</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15672,21 +15506,21 @@
         <v>21</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>697</v>
+        <v>21</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15706,22 +15540,22 @@
         <v>21</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K110" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="L110" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="M110" t="s" s="2">
         <v>699</v>
       </c>
-      <c r="L110" t="s" s="2">
+      <c r="N110" t="s" s="2">
         <v>700</v>
       </c>
-      <c r="M110" t="s" s="2">
+      <c r="O110" t="s" s="2">
         <v>701</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>702</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>703</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>21</v>
@@ -15770,7 +15604,7 @@
         <v>21</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>704</v>
+        <v>696</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15788,24 +15622,24 @@
         <v>21</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>21</v>
+        <v>702</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>706</v>
+        <v>21</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15825,23 +15659,21 @@
         <v>21</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>708</v>
+        <v>561</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>711</v>
-      </c>
-      <c r="O111" t="s" s="2">
-        <v>712</v>
-      </c>
+        <v>707</v>
+      </c>
+      <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>21</v>
       </c>
@@ -15889,7 +15721,7 @@
         <v>21</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>713</v>
+        <v>704</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15907,24 +15739,24 @@
         <v>21</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>21</v>
+        <v>708</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>21</v>
+        <v>710</v>
       </c>
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15944,21 +15776,19 @@
         <v>21</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>708</v>
+        <v>655</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="N112" s="2"/>
-      <c r="O112" t="s" s="2">
-        <v>718</v>
-      </c>
+      <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>21</v>
       </c>
@@ -16006,7 +15836,7 @@
         <v>21</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>719</v>
+        <v>711</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -16024,24 +15854,24 @@
         <v>21</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>21</v>
+        <v>714</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AN112" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>21</v>
+        <v>716</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16064,15 +15894,17 @@
         <v>21</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>721</v>
+        <v>689</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>723</v>
-      </c>
-      <c r="N113" s="2"/>
+        <v>719</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>720</v>
+      </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>21</v>
@@ -16121,7 +15953,7 @@
         <v>21</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -16139,10 +15971,10 @@
         <v>21</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>21</v>
@@ -16153,10 +15985,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16179,13 +16011,13 @@
         <v>21</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>214</v>
+        <v>724</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>215</v>
+        <v>725</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>216</v>
+        <v>726</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -16236,7 +16068,7 @@
         <v>21</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>217</v>
+        <v>723</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -16248,7 +16080,7 @@
         <v>21</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>21</v>
@@ -16257,10 +16089,10 @@
         <v>21</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>218</v>
+        <v>727</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>21</v>
+        <v>351</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>21</v>
@@ -16268,21 +16100,21 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>159</v>
+        <v>21</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>21</v>
@@ -16294,17 +16126,15 @@
         <v>21</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>135</v>
+        <v>668</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>220</v>
+        <v>729</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>162</v>
-      </c>
+        <v>730</v>
+      </c>
+      <c r="N115" s="2"/>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
         <v>21</v>
@@ -16353,28 +16183,28 @@
         <v>21</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>223</v>
+        <v>728</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>21</v>
+        <v>731</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>218</v>
+        <v>732</v>
       </c>
       <c r="AN115" t="s" s="2">
         <v>21</v>
@@ -16385,46 +16215,42 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>728</v>
+        <v>733</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>728</v>
+        <v>733</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>477</v>
+        <v>21</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I116" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>135</v>
+        <v>214</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>478</v>
+        <v>215</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O116" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="N116" s="2"/>
+      <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
         <v>21</v>
       </c>
@@ -16472,19 +16298,19 @@
         <v>21</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>480</v>
+        <v>217</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI116" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="AK116" t="s" s="2">
         <v>21</v>
@@ -16493,7 +16319,7 @@
         <v>21</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>133</v>
+        <v>218</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>21</v>
@@ -16504,21 +16330,21 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>729</v>
+        <v>734</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>729</v>
+        <v>734</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>21</v>
+        <v>159</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>21</v>
@@ -16530,16 +16356,16 @@
         <v>21</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>721</v>
+        <v>135</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>730</v>
+        <v>220</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>731</v>
+        <v>221</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>732</v>
+        <v>162</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -16589,19 +16415,19 @@
         <v>21</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>729</v>
+        <v>223</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI117" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>21</v>
@@ -16610,7 +16436,7 @@
         <v>21</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>733</v>
+        <v>218</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>21</v>
@@ -16621,42 +16447,46 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>21</v>
+        <v>424</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H118" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I118" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>214</v>
+        <v>135</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>215</v>
+        <v>425</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N118" s="2"/>
-      <c r="O118" s="2"/>
+        <v>426</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="O118" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="P118" t="s" s="2">
         <v>21</v>
       </c>
@@ -16704,19 +16534,19 @@
         <v>21</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>217</v>
+        <v>427</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI118" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>21</v>
+        <v>141</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>21</v>
@@ -16725,7 +16555,7 @@
         <v>21</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>218</v>
+        <v>133</v>
       </c>
       <c r="AN118" t="s" s="2">
         <v>21</v>
@@ -16736,21 +16566,21 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>159</v>
+        <v>21</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H119" t="s" s="2">
         <v>21</v>
@@ -16762,16 +16592,16 @@
         <v>21</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>135</v>
+        <v>575</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>220</v>
+        <v>737</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>221</v>
+        <v>738</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>162</v>
+        <v>739</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -16797,13 +16627,13 @@
         <v>21</v>
       </c>
       <c r="X119" t="s" s="2">
-        <v>21</v>
+        <v>191</v>
       </c>
       <c r="Y119" t="s" s="2">
-        <v>21</v>
+        <v>740</v>
       </c>
       <c r="Z119" t="s" s="2">
-        <v>21</v>
+        <v>741</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>21</v>
@@ -16821,78 +16651,74 @@
         <v>21</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>223</v>
+        <v>736</v>
       </c>
       <c r="AG119" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK119" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>21</v>
+        <v>731</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>218</v>
+        <v>742</v>
       </c>
       <c r="AN119" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO119" t="s" s="2">
-        <v>21</v>
+        <v>743</v>
       </c>
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>736</v>
+        <v>744</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>736</v>
+        <v>744</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>477</v>
+        <v>21</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H120" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I120" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J120" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>135</v>
+        <v>187</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>478</v>
+        <v>745</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="N120" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O120" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>746</v>
+      </c>
+      <c r="N120" s="2"/>
+      <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
         <v>21</v>
       </c>
@@ -16916,13 +16742,13 @@
         <v>21</v>
       </c>
       <c r="X120" t="s" s="2">
-        <v>21</v>
+        <v>191</v>
       </c>
       <c r="Y120" t="s" s="2">
-        <v>21</v>
+        <v>747</v>
       </c>
       <c r="Z120" t="s" s="2">
-        <v>21</v>
+        <v>748</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>21</v>
@@ -16940,42 +16766,42 @@
         <v>21</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>480</v>
+        <v>744</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH120" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI120" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK120" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>21</v>
+        <v>749</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>133</v>
+        <v>750</v>
       </c>
       <c r="AN120" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO120" t="s" s="2">
-        <v>21</v>
+        <v>751</v>
       </c>
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>737</v>
+        <v>752</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>737</v>
+        <v>752</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16998,13 +16824,13 @@
         <v>21</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>708</v>
+        <v>753</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>738</v>
+        <v>754</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>739</v>
+        <v>755</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -17055,7 +16881,7 @@
         <v>21</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>737</v>
+        <v>752</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -17070,13 +16896,13 @@
         <v>102</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>21</v>
+        <v>756</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>21</v>
+        <v>749</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>740</v>
+        <v>757</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>21</v>
@@ -17087,21 +16913,21 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>741</v>
+        <v>758</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>741</v>
+        <v>758</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>21</v>
+        <v>759</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G122" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H122" t="s" s="2">
         <v>21</v>
@@ -17113,15 +16939,17 @@
         <v>21</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>742</v>
+        <v>760</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>743</v>
+        <v>761</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>744</v>
-      </c>
-      <c r="N122" s="2"/>
+        <v>762</v>
+      </c>
+      <c r="N122" t="s" s="2">
+        <v>763</v>
+      </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
         <v>21</v>
@@ -17170,13 +16998,13 @@
         <v>21</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>741</v>
+        <v>758</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH122" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI122" t="s" s="2">
         <v>21</v>
@@ -17191,7 +17019,7 @@
         <v>21</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>745</v>
+        <v>764</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>21</v>
@@ -17202,10 +17030,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>746</v>
+        <v>765</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>746</v>
+        <v>765</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17216,7 +17044,7 @@
         <v>80</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H123" t="s" s="2">
         <v>21</v>
@@ -17228,15 +17056,17 @@
         <v>21</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>742</v>
+        <v>766</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>747</v>
+        <v>767</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>748</v>
-      </c>
-      <c r="N123" s="2"/>
+        <v>768</v>
+      </c>
+      <c r="N123" t="s" s="2">
+        <v>769</v>
+      </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
         <v>21</v>
@@ -17285,13 +17115,13 @@
         <v>21</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>746</v>
+        <v>765</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>21</v>
@@ -17300,1653 +17130,23 @@
         <v>102</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>21</v>
+        <v>770</v>
       </c>
       <c r="AL123" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>745</v>
+        <v>771</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO123" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="124" hidden="true">
-      <c r="A124" t="s" s="2">
-        <v>749</v>
-      </c>
-      <c r="B124" t="s" s="2">
-        <v>749</v>
-      </c>
-      <c r="C124" s="2"/>
-      <c r="D124" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E124" s="2"/>
-      <c r="F124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G124" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H124" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I124" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J124" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K124" t="s" s="2">
-        <v>750</v>
-      </c>
-      <c r="L124" t="s" s="2">
-        <v>751</v>
-      </c>
-      <c r="M124" t="s" s="2">
-        <v>752</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>753</v>
-      </c>
-      <c r="O124" t="s" s="2">
-        <v>754</v>
-      </c>
-      <c r="P124" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q124" s="2"/>
-      <c r="R124" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S124" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T124" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U124" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V124" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W124" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X124" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y124" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z124" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA124" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB124" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC124" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD124" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE124" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF124" t="s" s="2">
-        <v>749</v>
-      </c>
-      <c r="AG124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH124" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI124" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ124" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK124" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL124" t="s" s="2">
-        <v>755</v>
-      </c>
-      <c r="AM124" t="s" s="2">
-        <v>756</v>
-      </c>
-      <c r="AN124" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO124" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="125" hidden="true">
-      <c r="A125" t="s" s="2">
-        <v>757</v>
-      </c>
-      <c r="B125" t="s" s="2">
-        <v>757</v>
-      </c>
-      <c r="C125" s="2"/>
-      <c r="D125" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E125" s="2"/>
-      <c r="F125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G125" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H125" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I125" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J125" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K125" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="L125" t="s" s="2">
-        <v>758</v>
-      </c>
-      <c r="M125" t="s" s="2">
-        <v>759</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>760</v>
-      </c>
-      <c r="O125" s="2"/>
-      <c r="P125" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q125" s="2"/>
-      <c r="R125" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S125" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T125" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U125" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V125" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W125" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X125" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y125" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z125" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA125" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB125" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC125" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD125" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE125" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF125" t="s" s="2">
-        <v>757</v>
-      </c>
-      <c r="AG125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH125" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI125" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ125" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK125" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL125" t="s" s="2">
-        <v>761</v>
-      </c>
-      <c r="AM125" t="s" s="2">
-        <v>762</v>
-      </c>
-      <c r="AN125" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO125" t="s" s="2">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="126" hidden="true">
-      <c r="A126" t="s" s="2">
-        <v>764</v>
-      </c>
-      <c r="B126" t="s" s="2">
-        <v>764</v>
-      </c>
-      <c r="C126" s="2"/>
-      <c r="D126" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E126" s="2"/>
-      <c r="F126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G126" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H126" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I126" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J126" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K126" t="s" s="2">
-        <v>708</v>
-      </c>
-      <c r="L126" t="s" s="2">
-        <v>765</v>
-      </c>
-      <c r="M126" t="s" s="2">
-        <v>766</v>
-      </c>
-      <c r="N126" s="2"/>
-      <c r="O126" s="2"/>
-      <c r="P126" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q126" s="2"/>
-      <c r="R126" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S126" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T126" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U126" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V126" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W126" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X126" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y126" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z126" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA126" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB126" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC126" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD126" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE126" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF126" t="s" s="2">
-        <v>764</v>
-      </c>
-      <c r="AG126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH126" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI126" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ126" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK126" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL126" t="s" s="2">
-        <v>767</v>
-      </c>
-      <c r="AM126" t="s" s="2">
-        <v>768</v>
-      </c>
-      <c r="AN126" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO126" t="s" s="2">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="127" hidden="true">
-      <c r="A127" t="s" s="2">
-        <v>770</v>
-      </c>
-      <c r="B127" t="s" s="2">
-        <v>770</v>
-      </c>
-      <c r="C127" s="2"/>
-      <c r="D127" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E127" s="2"/>
-      <c r="F127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G127" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H127" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I127" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J127" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K127" t="s" s="2">
-        <v>742</v>
-      </c>
-      <c r="L127" t="s" s="2">
-        <v>771</v>
-      </c>
-      <c r="M127" t="s" s="2">
-        <v>772</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>773</v>
-      </c>
-      <c r="O127" s="2"/>
-      <c r="P127" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q127" s="2"/>
-      <c r="R127" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S127" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T127" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U127" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V127" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W127" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X127" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y127" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z127" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA127" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB127" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC127" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD127" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE127" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF127" t="s" s="2">
-        <v>770</v>
-      </c>
-      <c r="AG127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH127" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI127" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ127" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK127" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL127" t="s" s="2">
-        <v>774</v>
-      </c>
-      <c r="AM127" t="s" s="2">
-        <v>775</v>
-      </c>
-      <c r="AN127" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO127" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="128" hidden="true">
-      <c r="A128" t="s" s="2">
-        <v>776</v>
-      </c>
-      <c r="B128" t="s" s="2">
-        <v>776</v>
-      </c>
-      <c r="C128" s="2"/>
-      <c r="D128" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E128" s="2"/>
-      <c r="F128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G128" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H128" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I128" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J128" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K128" t="s" s="2">
-        <v>777</v>
-      </c>
-      <c r="L128" t="s" s="2">
-        <v>778</v>
-      </c>
-      <c r="M128" t="s" s="2">
-        <v>779</v>
-      </c>
-      <c r="N128" s="2"/>
-      <c r="O128" s="2"/>
-      <c r="P128" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q128" s="2"/>
-      <c r="R128" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S128" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T128" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U128" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V128" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W128" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X128" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y128" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z128" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA128" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB128" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC128" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD128" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE128" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF128" t="s" s="2">
-        <v>776</v>
-      </c>
-      <c r="AG128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH128" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI128" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ128" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK128" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL128" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM128" t="s" s="2">
-        <v>780</v>
-      </c>
-      <c r="AN128" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="AO128" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="129" hidden="true">
-      <c r="A129" t="s" s="2">
-        <v>781</v>
-      </c>
-      <c r="B129" t="s" s="2">
-        <v>781</v>
-      </c>
-      <c r="C129" s="2"/>
-      <c r="D129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E129" s="2"/>
-      <c r="F129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G129" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K129" t="s" s="2">
-        <v>721</v>
-      </c>
-      <c r="L129" t="s" s="2">
-        <v>782</v>
-      </c>
-      <c r="M129" t="s" s="2">
-        <v>783</v>
-      </c>
-      <c r="N129" s="2"/>
-      <c r="O129" s="2"/>
-      <c r="P129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q129" s="2"/>
-      <c r="R129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF129" t="s" s="2">
-        <v>781</v>
-      </c>
-      <c r="AG129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH129" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ129" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL129" t="s" s="2">
-        <v>784</v>
-      </c>
-      <c r="AM129" t="s" s="2">
-        <v>785</v>
-      </c>
-      <c r="AN129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO129" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="130" hidden="true">
-      <c r="A130" t="s" s="2">
-        <v>786</v>
-      </c>
-      <c r="B130" t="s" s="2">
-        <v>786</v>
-      </c>
-      <c r="C130" s="2"/>
-      <c r="D130" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E130" s="2"/>
-      <c r="F130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G130" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H130" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I130" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J130" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K130" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="L130" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="M130" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N130" s="2"/>
-      <c r="O130" s="2"/>
-      <c r="P130" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q130" s="2"/>
-      <c r="R130" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S130" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T130" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U130" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V130" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W130" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X130" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y130" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z130" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA130" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB130" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC130" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD130" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE130" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF130" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="AG130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH130" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI130" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ130" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AK130" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL130" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM130" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="AN130" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO130" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="131" hidden="true">
-      <c r="A131" t="s" s="2">
-        <v>787</v>
-      </c>
-      <c r="B131" t="s" s="2">
-        <v>787</v>
-      </c>
-      <c r="C131" s="2"/>
-      <c r="D131" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="E131" s="2"/>
-      <c r="F131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G131" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H131" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I131" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J131" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K131" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L131" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="M131" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N131" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O131" s="2"/>
-      <c r="P131" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q131" s="2"/>
-      <c r="R131" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S131" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T131" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U131" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V131" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W131" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X131" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y131" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z131" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA131" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB131" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC131" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD131" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE131" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF131" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="AG131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH131" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI131" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ131" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AK131" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL131" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM131" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="AN131" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO131" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="132" hidden="true">
-      <c r="A132" t="s" s="2">
-        <v>788</v>
-      </c>
-      <c r="B132" t="s" s="2">
-        <v>788</v>
-      </c>
-      <c r="C132" s="2"/>
-      <c r="D132" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="E132" s="2"/>
-      <c r="F132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G132" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H132" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I132" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="J132" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K132" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L132" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="M132" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O132" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="P132" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q132" s="2"/>
-      <c r="R132" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S132" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T132" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U132" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V132" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W132" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X132" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y132" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z132" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA132" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB132" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC132" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD132" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE132" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF132" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="AG132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH132" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI132" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ132" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AK132" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL132" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM132" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AN132" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO132" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="133" hidden="true">
-      <c r="A133" t="s" s="2">
-        <v>789</v>
-      </c>
-      <c r="B133" t="s" s="2">
-        <v>789</v>
-      </c>
-      <c r="C133" s="2"/>
-      <c r="D133" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E133" s="2"/>
-      <c r="F133" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="G133" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H133" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I133" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J133" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K133" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="L133" t="s" s="2">
-        <v>790</v>
-      </c>
-      <c r="M133" t="s" s="2">
-        <v>791</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>792</v>
-      </c>
-      <c r="O133" s="2"/>
-      <c r="P133" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q133" s="2"/>
-      <c r="R133" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S133" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T133" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U133" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V133" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W133" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X133" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="Y133" t="s" s="2">
-        <v>793</v>
-      </c>
-      <c r="Z133" t="s" s="2">
-        <v>794</v>
-      </c>
-      <c r="AA133" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB133" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC133" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD133" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE133" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF133" t="s" s="2">
-        <v>789</v>
-      </c>
-      <c r="AG133" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AH133" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI133" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ133" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK133" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL133" t="s" s="2">
-        <v>784</v>
-      </c>
-      <c r="AM133" t="s" s="2">
-        <v>795</v>
-      </c>
-      <c r="AN133" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO133" t="s" s="2">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="134" hidden="true">
-      <c r="A134" t="s" s="2">
-        <v>797</v>
-      </c>
-      <c r="B134" t="s" s="2">
-        <v>797</v>
-      </c>
-      <c r="C134" s="2"/>
-      <c r="D134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E134" s="2"/>
-      <c r="F134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G134" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K134" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="L134" t="s" s="2">
-        <v>798</v>
-      </c>
-      <c r="M134" t="s" s="2">
-        <v>799</v>
-      </c>
-      <c r="N134" s="2"/>
-      <c r="O134" s="2"/>
-      <c r="P134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q134" s="2"/>
-      <c r="R134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X134" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="Y134" t="s" s="2">
-        <v>800</v>
-      </c>
-      <c r="Z134" t="s" s="2">
-        <v>801</v>
-      </c>
-      <c r="AA134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF134" t="s" s="2">
-        <v>797</v>
-      </c>
-      <c r="AG134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH134" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ134" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL134" t="s" s="2">
-        <v>802</v>
-      </c>
-      <c r="AM134" t="s" s="2">
-        <v>803</v>
-      </c>
-      <c r="AN134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO134" t="s" s="2">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="135" hidden="true">
-      <c r="A135" t="s" s="2">
-        <v>805</v>
-      </c>
-      <c r="B135" t="s" s="2">
-        <v>805</v>
-      </c>
-      <c r="C135" s="2"/>
-      <c r="D135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E135" s="2"/>
-      <c r="F135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G135" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K135" t="s" s="2">
-        <v>806</v>
-      </c>
-      <c r="L135" t="s" s="2">
-        <v>807</v>
-      </c>
-      <c r="M135" t="s" s="2">
-        <v>808</v>
-      </c>
-      <c r="N135" s="2"/>
-      <c r="O135" s="2"/>
-      <c r="P135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q135" s="2"/>
-      <c r="R135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF135" t="s" s="2">
-        <v>805</v>
-      </c>
-      <c r="AG135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH135" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ135" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK135" t="s" s="2">
-        <v>809</v>
-      </c>
-      <c r="AL135" t="s" s="2">
-        <v>802</v>
-      </c>
-      <c r="AM135" t="s" s="2">
-        <v>810</v>
-      </c>
-      <c r="AN135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO135" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="136" hidden="true">
-      <c r="A136" t="s" s="2">
-        <v>811</v>
-      </c>
-      <c r="B136" t="s" s="2">
-        <v>811</v>
-      </c>
-      <c r="C136" s="2"/>
-      <c r="D136" t="s" s="2">
-        <v>812</v>
-      </c>
-      <c r="E136" s="2"/>
-      <c r="F136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H136" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I136" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J136" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K136" t="s" s="2">
-        <v>813</v>
-      </c>
-      <c r="L136" t="s" s="2">
-        <v>814</v>
-      </c>
-      <c r="M136" t="s" s="2">
-        <v>815</v>
-      </c>
-      <c r="N136" t="s" s="2">
-        <v>816</v>
-      </c>
-      <c r="O136" s="2"/>
-      <c r="P136" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q136" s="2"/>
-      <c r="R136" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S136" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T136" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U136" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V136" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W136" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X136" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y136" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z136" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA136" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB136" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC136" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD136" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE136" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF136" t="s" s="2">
-        <v>811</v>
-      </c>
-      <c r="AG136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH136" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI136" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ136" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK136" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL136" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM136" t="s" s="2">
-        <v>817</v>
-      </c>
-      <c r="AN136" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO136" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="137" hidden="true">
-      <c r="A137" t="s" s="2">
-        <v>818</v>
-      </c>
-      <c r="B137" t="s" s="2">
-        <v>818</v>
-      </c>
-      <c r="C137" s="2"/>
-      <c r="D137" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E137" s="2"/>
-      <c r="F137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H137" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I137" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J137" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K137" t="s" s="2">
-        <v>819</v>
-      </c>
-      <c r="L137" t="s" s="2">
-        <v>820</v>
-      </c>
-      <c r="M137" t="s" s="2">
-        <v>821</v>
-      </c>
-      <c r="N137" t="s" s="2">
-        <v>822</v>
-      </c>
-      <c r="O137" s="2"/>
-      <c r="P137" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q137" s="2"/>
-      <c r="R137" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S137" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T137" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U137" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V137" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W137" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X137" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y137" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z137" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA137" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB137" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC137" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD137" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE137" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF137" t="s" s="2">
-        <v>818</v>
-      </c>
-      <c r="AG137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH137" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI137" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ137" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK137" t="s" s="2">
-        <v>823</v>
-      </c>
-      <c r="AL137" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM137" t="s" s="2">
-        <v>824</v>
-      </c>
-      <c r="AN137" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO137" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO137">
+  <autoFilter ref="A1:AO123">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -18956,7 +17156,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI136">
+  <conditionalFormatting sqref="A2:AI122">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T19:29:09+00:00</t>
+    <t>2026-01-29T08:16:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>ELGA e-Medikation Planeintrag</t>
+    <t>ELGA e-Med Planeintrag</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T08:16:48+00:00</t>
+    <t>2026-01-29T15:27:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,9 +87,9 @@
     <t>Description</t>
   </si>
   <si>
-    <t>**Beschreibung:** Bildet einen Medikationsplaneintrag im Medikationsplan eines ELGA Teilnehmers ab. 
+    <t>**Beschreibung:** Bildet einen Medikationsplaneintrag im Medikationsplan eines ELGA Teilnehmers ab ("MedicationRequest"-Ressource).
 Er enthält genau ein Arzneimittel und dessen Dosierung.
-Kann in weiterer Folge dazu dienen, eine geplante Abgabe zu erstellen (AtEmedMRGeplanteAbgabe).</t>
+Kann in weiterer Folge dazu dienen, eine geplante Abgabe zu erstellen. Verwendet R5 Backport Extensions.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T14:55:57+00:00</t>
+    <t>2026-02-09T17:27:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T17:27:03+00:00</t>
+    <t>2026-02-10T17:53:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -545,8 +545,8 @@
 </t>
   </si>
   <si>
-    <t>TODO: Verwendung im Medikationsplaneintrag zu prüfen. 
-Geplante-Abgabe-ID (e-Med-ID) steht jedenfalls erst zum Zeitpunkt der Erstellung einer 
+    <t>Verwendung im Medikationsplaneintrag zu prüfen. 
+Geplante-Abgabe-ID (e-Med-ID) steht erst zum Zeitpunkt der Erstellung einer 
 geplanten Abgabe (Rezeptierung) zur Verfügung.</t>
   </si>
   <si>
@@ -575,7 +575,7 @@
   </si>
   <si>
     <t>Status des Medikationsplaneintrags (im Standardfall active oder complete): 
-active | on-hold | cancelled | completed | entered-in-error | stopped | draft | unknown -&gt; entfernen: draft, unknown</t>
+(req) active | on-hold | cancelled | completed | entered-in-error | stopped | draft | unknown -&gt; entfernen: draft, unknown</t>
   </si>
   <si>
     <t>A code specifying the current state of the order.  Generally, this will be active or completed state.</t>
@@ -612,7 +612,7 @@
 </t>
   </si>
   <si>
-    <t>Grund für den aktuellen Status des Medikationsplaneintrags: https://hl7.org/fhir/R4/valueset-medicationrequest-status-reason.html. Verwendung prüfen.</t>
+    <t>Grund für den aktuellen Status des Medikationsplaneintrags: (ex) https://hl7.org/fhir/R4/valueset-medicationrequest-status-reason.html. Verwendung prüfen.</t>
   </si>
   <si>
     <t>Captures the reason for the current state of the MedicationRequest.</t>
@@ -640,7 +640,8 @@
   </si>
   <si>
     <t>Der Medikationsplaneintrag stellt eine Anforderung und Ermächtigung 
-zum Handeln durch den Antragsteller dar, daher ist intent immer "order".</t>
+zum Handeln durch den Antragsteller dar, daher ist intent immer "order". 
+(req) proposal | plan | order | original-order | reflex-order | filler-order | instance-order | option</t>
   </si>
   <si>
     <t>Whether the request is a proposal, plan, or an original order.</t>
@@ -674,8 +675,7 @@
     <t>MedicationRequest.category</t>
   </si>
   <si>
-    <t>Kategorie damit Instanz einer geplanten Abgabe von Medikationsplaneintrag
- unterschieden werden kann (beide haben intent order)</t>
+    <t>Kategorie damit Medikationsplaneintrag von geplanter Abgabe unterschieden werden kann (beide haben intent order)</t>
   </si>
   <si>
     <t>Indicates the type of medication request (for example, where the medication is expected to be consumed or administered (i.e. inpatient or outpatient)).</t>
@@ -711,7 +711,7 @@
     <t>MedicationRequest.priority</t>
   </si>
   <si>
-    <t>Priorität des Medikationsplaneintrag: routine | urgent | asap | stat. Keine Verwendung in Medikationsplaneintrag.</t>
+    <t>Priorität des Medikationsplaneintrag: (req) routine | urgent | asap | stat. Keine Verwendung in Medikationsplaneintrag.</t>
   </si>
   <si>
     <t>Indicates how quickly the Medication Request should be addressed with respect to other requests.</t>
@@ -740,7 +740,7 @@
   </si>
   <si>
     <t>Gibt an, ob der Medikationsplaneintrag die Verordnung einer Medikation 
-(und somit die Erstellung einer geplanten Abgabe) untersagt ist. Verwendung prüfen.</t>
+(und somit die Erstellung einer geplanten Abgabe) untersagt. Verwendung prüfen.</t>
   </si>
   <si>
     <t>If true indicates that the provider is asking for the medication request not to occur.</t>
@@ -982,7 +982,7 @@
 </t>
   </si>
   <si>
-    <t>Die Begegnung, während der Medikationsplaneintrag erstellt wurde. Verwendung im Medikationsplaneintrag prüfen.</t>
+    <t>Aufenthalt/Begegnung, während dessen/der der Medikationsplaneintrag erstellt wurde. Verwendung im Medikationsplaneintrag prüfen.</t>
   </si>
   <si>
     <t>The Encounter during which this [x] was created or to which the creation of this record is tightly associated.</t>
@@ -1031,7 +1031,7 @@
 </t>
   </si>
   <si>
-    <t>Datum der Ausstellung des Medikationsplaneintrags.</t>
+    <t>Datum der Erstellung des Medikationsplaneintrags.</t>
   </si>
   <si>
     <t>The date (and perhaps time) when the prescription was initially written or authored on.</t>
@@ -1144,7 +1144,7 @@
   </si>
   <si>
     <t>Grund für die Verordnung des Arzneimittels. 
-Entweder Code oder Referenz (evtl. Invariante).</t>
+Entweder Code oder Referenz (TODO: Evtl. Invariante).</t>
   </si>
   <si>
     <t>The reason or the indication for ordering or not ordering the medication.</t>
@@ -1580,7 +1580,7 @@
     <t>Gibt an, ob eine Substitution Teil der Abgabe sein kann/sollte/nicht sein darf. 
 Dieser Block erläutert die Absicht des Arztes, der den Medikationsplaneintrag erstellt. 
 Wenn nichts angegeben ist, kann eine Substitution vorgenommen werden. 
-TODO: Zu prüfen ob Verwendung im Medikationsplaneintrag; Dokumentation über Substitution erfolg in der Dispense-Resource. 
+TODO: Zu prüfen, ob Verwendung im Medikationsplaneintrag; Dokumentation über Substitution erfolg in der Dispense-Resource. 
 Usecase: mit welchem Medikament der Patient das Medikament ersetzen kann. Hinweis: vor allem bei
 OTC Medikamenten sinnvoll, da keine geplante Abgabe dazu existiert</t>
   </si>
@@ -1708,7 +1708,7 @@
 </t>
   </si>
   <si>
-    <t>Bezeichnet eine Liste von Provenance-Ressourcen, 
+    <t>Referenz auf Provenance-Ressourcen, 
 die verschiedene relevante Versionen dieser Ressource dokumentieren. 
 TODO: Verwendung im Medikationsplaneintrag zu prüfen.</t>
   </si>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2797" uniqueCount="530">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2794" uniqueCount="542">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-10T17:53:58+00:00</t>
+    <t>2026-02-12T16:23:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>**Beschreibung:** Bildet einen Medikationsplaneintrag im Medikationsplan eines ELGA Teilnehmers ab ("MedicationRequest"-Ressource).
+    <t>**Beschreibung:** Bildet einen Medikationsplaneintrag im Medikationsplan eines ELGA-Teilnehmers ab ("MedicationRequest"-Ressource).
 Er enthält genau ein Arzneimittel und dessen Dosierung.
 Kann in weiterer Folge dazu dienen, eine geplante Abgabe zu erstellen. Verwendet R5 Backport Extensions.</t>
   </si>
@@ -278,7 +278,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}med-1:Für die geplante Abgabe muss entweder CodeableConcept (PZN) oder Reference(Medication) angegeben werden – aber genau eins. {medicationCodeableConcept.exists() xor medicationReference.exists()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Request</t>
@@ -428,10 +428,64 @@
     <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
   </si>
   <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
     <t>DomainResource.contained</t>
   </si>
   <si>
     <t>N/A</t>
+  </si>
+  <si>
+    <t>MedicationRequest.contained:medication</t>
+  </si>
+  <si>
+    <t>medication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medication {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-emed-medication}
+</t>
+  </si>
+  <si>
+    <t>Definition of a Medication</t>
+  </si>
+  <si>
+    <t>This resource is primarily used for the identification and definition of a medication for the purposes of prescribing, dispensing, and administering a medication as well as for making statements about medication use.</t>
+  </si>
+  <si>
+    <t>NewRx/MedicationPrescribed+-or-+RxFill/MedicationDispensed+-or-+RxHistoryResponse/MedicationDispensed+-or-+RxHistoryResponse/MedicationPrescribed</t>
+  </si>
+  <si>
+    <t>ManufacturedProduct[classCode=ADMM]</t>
+  </si>
+  <si>
+    <t>MedicationRequest.contained:substance</t>
+  </si>
+  <si>
+    <t>substance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Substance {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-emed-substance}
+</t>
+  </si>
+  <si>
+    <t>A homogeneous material with a definite composition</t>
+  </si>
+  <si>
+    <t>A homogeneous material with a definite composition.</t>
+  </si>
+  <si>
+    <t>Material</t>
   </si>
   <si>
     <t>MedicationRequest.extension</t>
@@ -449,9 +503,6 @@
   <si>
     <t xml:space="preserve">value:url}
 </t>
-  </si>
-  <si>
-    <t>open</t>
   </si>
   <si>
     <t>DomainResource.extension</t>
@@ -509,7 +560,9 @@
 </t>
   </si>
   <si>
-    <t>Weist darauf hin, dass der verschreibende Arzt das Medikament wissentlich für eine Indikation, Altersgruppe, Dosierung oder Verabreichungsform verschrieben hat, die nicht von den Aufsichtsbehörden zugelassen ist und in der Verschreibungsinformation für das Produkt nicht erwähnt wird.</t>
+    <t>Weist darauf hin, dass der verschreibende Arzt das Medikament wissentlich für eine Indikation, 
+Altersgruppe, Dosierung oder Verabreichungsform verschrieben hat, die nicht von den Aufsichtsbehörden zugelassen ist und in der 
+Verschreibungsinformation für das Produkt nicht erwähnt wird.</t>
   </si>
   <si>
     <t>Indicates that the prescriber has intentionally prescribed the medication in a manner not covered by the product authorization — such as for a different indication, age group, dosage, or route of administration.</t>
@@ -545,9 +598,14 @@
 </t>
   </si>
   <si>
-    <t>Verwendung im Medikationsplaneintrag zu prüfen. 
-Geplante-Abgabe-ID (e-Med-ID) steht erst zum Zeitpunkt der Erstellung einer 
-geplanten Abgabe (Rezeptierung) zur Verfügung.</t>
+    <t>Medikationsplaneintrag-ID. TODO: Verwendung einer logischen Medikationsplaneintrag-ID prüfen.
+Evt. mit Zeitstempel (Planeintrag-ID_{Zeitstempel}) zur Herstellung eines Bezugs von geänderten Planeinträgen.
+Vorteil: 
+- Auch wenn sich die PZN ändert, aber logisch der gleiche Eintrag betroffen ist (z.B. Austausch eines Arzneimittels durch ein anderes mit weniger Wechselwirkung), kann ein Bezug hergestellt werden.
+- Wenn zur Vorversion des Eintrags bereits eine geplante Abgabe erstellt wurde, kann ein Bezug zum ursprünglichen Eintrag hergestellt werden.
+Nachteil: 
+- Falls Planeinträge mit komplett neuer Arznei überschrieben werden, entsteht dadurch ein verwirrender Bezug. 
+- Die Verantwortung, dass nur Einträge geändert werden, die keine komplett neue Medikation beinhalten, liegt beim Client.</t>
   </si>
   <si>
     <t>Identifiers associated with this medication request that are defined by business processes and/or used to refer to it when a direct URL reference to the resource itself is not appropriate. They are business identifiers assigned to this resource by the performer or other systems and remain constant as the resource is updated and propagates from server to server.</t>
@@ -574,8 +632,11 @@
     <t>MedicationRequest.status</t>
   </si>
   <si>
-    <t>Status des Medikationsplaneintrags (im Standardfall active oder complete): 
-(req) active | on-hold | cancelled | completed | entered-in-error | stopped | draft | unknown -&gt; entfernen: draft, unknown</t>
+    <t xml:space="preserve">Status des Medikationsplaneintrags. TODO: Einschränken auf active, complete, on hold; 
+(req) active | on-hold | cancelled | completed | entered-in-error | stopped | draft | unknown 
+TODO: Fachlich zu püfen, ob im Medikationsplan dokumentiert werden soll, dass und warum ein Medikament abgesetzt wurde (z.B. Allergie).
+Auch im Kontext mit statusReason, wo dieser Grund codiert angegeben werden kann.
+</t>
   </si>
   <si>
     <t>A code specifying the current state of the order.  Generally, this will be active or completed state.</t>
@@ -612,7 +673,8 @@
 </t>
   </si>
   <si>
-    <t>Grund für den aktuellen Status des Medikationsplaneintrags: (ex) https://hl7.org/fhir/R4/valueset-medicationrequest-status-reason.html. Verwendung prüfen.</t>
+    <t>Grund für den aktuellen Status des Medikationsplaneintrags: (ex) https://hl7.org/fhir/R4/valueset-medicationrequest-status-reason.html.
+TODO: Verwendung prüfen im Zusammenhang mit status.</t>
   </si>
   <si>
     <t>Captures the reason for the current state of the MedicationRequest.</t>
@@ -639,9 +701,11 @@
     <t>MedicationRequest.intent</t>
   </si>
   <si>
-    <t>Der Medikationsplaneintrag stellt eine Anforderung und Ermächtigung 
-zum Handeln durch den Antragsteller dar, daher ist intent immer "order". 
-(req) proposal | plan | order | original-order | reflex-order | filler-order | instance-order | option</t>
+    <t>TODO: Begründung, warum hier immer "order" anzugeben ist:
+Der Medikationsplaneintrag ist eine Handlungsermächtigung. Dieser wurde von einem:r Arzt:Ärztin erstellt und ermächtigt (auch andere Ärzte) zur Ausstellung einer geplanten Abgabe
+basierend auf diesen Eintrag.
+(req) proposal | plan | order | original-order | reflex-order | filler-order | instance-order | option. 
+https://hl7.org/fhir/R4/valueset-medicationrequest-intent.html</t>
   </si>
   <si>
     <t>Whether the request is a proposal, plan, or an original order.</t>
@@ -675,7 +739,7 @@
     <t>MedicationRequest.category</t>
   </si>
   <si>
-    <t>Kategorie damit Medikationsplaneintrag von geplanter Abgabe unterschieden werden kann (beide haben intent order)</t>
+    <t>Kategorie zur Unterscheidung eines Medikationsplaneintrags von einer geplanten Abgabe (beide haben intent order)</t>
   </si>
   <si>
     <t>Indicates the type of medication request (for example, where the medication is expected to be consumed or administered (i.e. inpatient or outpatient)).</t>
@@ -740,7 +804,8 @@
   </si>
   <si>
     <t>Gibt an, ob der Medikationsplaneintrag die Verordnung einer Medikation 
-(und somit die Erstellung einer geplanten Abgabe) untersagt. Verwendung prüfen.</t>
+(und somit die Erstellung einer geplanten Abgabe) untersagt (z.B. bei Allergie). TODO: Fachlich zu prüfen, ob dieser Usecase existiert.
+Auch im Kontext mit status und statusReason zu betrachten. Evtl. erst in späterer Version</t>
   </si>
   <si>
     <t>If true indicates that the provider is asking for the medication request not to occur.</t>
@@ -759,43 +824,57 @@
 Reference(Patient|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)</t>
   </si>
   <si>
-    <t>Gibt an, ob dieser Datensatz als sekundärer „gemeldeter” Datensatz und nicht als ursprünglicher primärer Referenzdatensatz erfasst wurde. 
-Er kann auch die Quelle der Meldung angeben. Keine Verwendung in Medikationsplaneintrag.</t>
+    <t>TODO: Verwendung zu püfen: Kann zur Dokumentation von Fremdmedikation verwendet werden. Im Falle eines "Nachtrags" einer Medikation in den Medikationsplan
+durch einen anderen, nicht ursprünglich verordnenden Arzt. Dieser muss eindeutig identifiziert sein (im GDA-I vorhanden). Juristisch
+Verantwortlichkeit für Korrektheit des Eintrags zu klären.</t>
   </si>
   <si>
     <t>Indicates if this record was captured as a secondary 'reported' record rather than as an original primary source-of-truth record.  It may also indicate the source of the report.</t>
   </si>
   <si>
+    <t>closed</t>
+  </si>
+  <si>
     <t>.participation[typeCode=INF].role</t>
   </si>
   <si>
+    <t>MedicationRequest.reported[x]:reportedBoolean</t>
+  </si>
+  <si>
+    <t>reportedBoolean</t>
+  </si>
+  <si>
+    <t>TODO: entfernen?</t>
+  </si>
+  <si>
+    <t>MedicationRequest.reported[x]:reportedReference</t>
+  </si>
+  <si>
+    <t>reportedReference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Patient|Practitioner|PractitionerRole|RelatedPerson|Organization)
+</t>
+  </si>
+  <si>
+    <t>Im Falle einer Fremdmedikation verpflichtende Angabe einer Referen auf: (Patient | Practitioner | PractitionerRole | RelatedPerson | Organization)</t>
+  </si>
+  <si>
     <t>MedicationRequest.medication[x]</t>
   </si>
   <si>
-    <t>CodeableConcept
-Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-emed-medication)</t>
-  </si>
-  <si>
-    <t>Medication to be taken</t>
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-emed-medication)
+</t>
+  </si>
+  <si>
+    <t>Das Arzneimittel wird immer in einer contained Medication Ressource dokumentiert, damit 
+Arzneimittel mit und ohne PZN einheitlich dokumentiert werden können.</t>
   </si>
   <si>
     <t>Identifies the medication being requested. This is a link to a resource that represents the medication which may be the details of the medication or simply an attribute carrying a code that identifies the medication from a known list of medications.</t>
   </si>
   <si>
     <t>If only a code is specified, then it needs to be a code for a specific product. If more information is required, then the use of the Medication resource is recommended.  For example, if you require form or lot number or if the medication is compounded or extemporaneously prepared, then you must reference the Medication resource.</t>
-  </si>
-  <si>
-    <t>A coded concept identifying substance or product that can be ordered.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-codes|4.0.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>closed</t>
   </si>
   <si>
     <t>Request.code</t>
@@ -819,21 +898,6 @@
     <t>RXE-2-Give Code / RXO-1-Requested Give Code / RXC-2-Component Code</t>
   </si>
   <si>
-    <t>MedicationRequest.medication[x]:medicationCodeableConcept</t>
-  </si>
-  <si>
-    <t>medicationCodeableConcept</t>
-  </si>
-  <si>
-    <t>Angabe mittels Pharmazentralnummer (PZN) aus der ASP-Liste.</t>
-  </si>
-  <si>
-    <t>https://termgit.elga.gv.at/CodeSystem/asp-liste</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x]:medicationCodeableConcept.id</t>
-  </si>
-  <si>
     <t>MedicationRequest.medication[x].id</t>
   </si>
   <si>
@@ -853,9 +917,6 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>MedicationRequest.medication[x]:medicationCodeableConcept.extension</t>
-  </si>
-  <si>
     <t>MedicationRequest.medication[x].extension</t>
   </si>
   <si>
@@ -871,75 +932,88 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>MedicationRequest.medication[x]:medicationCodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x].coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
+    <t>MedicationRequest.medication[x].reference</t>
+  </si>
+  <si>
+    <t>Literal reference, Relative, internal or absolute URL</t>
+  </si>
+  <si>
+    <t>A reference to a location at which the other resource is found. The reference may be a relative reference, in which case it is relative to the service base URL, or an absolute URL that resolves to the location where the resource is found. The reference may be version specific or not. If the reference is not to a FHIR RESTful server, then it should be assumed to be version specific. Internal fragment references (start with '#') refer to contained resources.</t>
+  </si>
+  <si>
+    <t>Using absolute URLs provides a stable scalable approach suitable for a cloud/web context, while using relative/logical references provides a flexible approach suitable for use when trading across closed eco-system boundaries.   Absolute URLs do not need to point to a FHIR RESTful server, though this is the preferred approach. If the URL conforms to the structure "/[type]/[id]" then it should be assumed that the reference is to a FHIR RESTful server.</t>
+  </si>
+  <si>
+    <t>Reference.reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ref-1
 </t>
   </si>
   <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x]:medicationCodeableConcept.text</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x].text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x]:medicationReference</t>
-  </si>
-  <si>
-    <t>medicationReference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-emed-medication)
-</t>
-  </si>
-  <si>
-    <t>Bei magistralen Anwendungen oder Infusionen ohne PZN.</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+contained-ref:Medication must be contained (#...) {reference.startsWith('#')}</t>
+  </si>
+  <si>
+    <t>MedicationRequest.medication[x].type</t>
+  </si>
+  <si>
+    <t>Type the reference refers to (e.g. "Patient")</t>
+  </si>
+  <si>
+    <t>The expected type of the target of the reference. If both Reference.type and Reference.reference are populated and Reference.reference is a FHIR URL, both SHALL be consistent.
+The type is the Canonical URL of Resource Definition that is the type this reference refers to. References are URLs that are relative to http://hl7.org/fhir/StructureDefinition/ e.g. "Patient" is a reference to http://hl7.org/fhir/StructureDefinition/Patient. Absolute URLs are only allowed for logical models (and can only be used in references in logical models, not resources).</t>
+  </si>
+  <si>
+    <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Aa resource (or, for logical models, the URI of the logical model).</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
+  </si>
+  <si>
+    <t>Reference.type</t>
+  </si>
+  <si>
+    <t>MedicationRequest.medication[x].identifier</t>
+  </si>
+  <si>
+    <t>Logical reference, when literal reference is not known</t>
+  </si>
+  <si>
+    <t>An identifier for the target resource. This is used when there is no way to reference the other resource directly, either because the entity it represents is not available through a FHIR server, or because there is no way for the author of the resource to convert a known identifier to an actual location. There is no requirement that a Reference.identifier point to something that is actually exposed as a FHIR instance, but it SHALL point to a business concept that would be expected to be exposed as a FHIR instance, and that instance would need to be of a FHIR resource type allowed by the reference.</t>
+  </si>
+  <si>
+    <t>When an identifier is provided in place of a reference, any system processing the reference will only be able to resolve the identifier to a reference if it understands the business context in which the identifier is used. Sometimes this is global (e.g. a national identifier) but often it is not. For this reason, none of the useful mechanisms described for working with references (e.g. chaining, includes) are possible, nor should servers be expected to be able resolve the reference. Servers may accept an identifier based reference untouched, resolve it, and/or reject it - see CapabilityStatement.rest.resource.referencePolicy. 
+When both an identifier and a literal reference are provided, the literal reference is preferred. Applications processing the resource are allowed - but not required - to check that the identifier matches the literal reference
+Applications converting a logical reference to a literal reference may choose to leave the logical reference present, or remove it.
+Reference is intended to point to a structure that can potentially be expressed as a FHIR resource, though there is no need for it to exist as an actual FHIR resource instance - except in as much as an application wishes to actual find the target of the reference. The content referred to be the identifier must meet the logical constraints implied by any limitations on what resource types are permitted for the reference.  For example, it would not be legitimate to send the identifier for a drug prescription if the type were Reference(Observation|DiagnosticReport).  One of the use-cases for Reference.identifier is the situation where no FHIR representation exists (where the type is Reference (Any).</t>
+  </si>
+  <si>
+    <t>Reference.identifier</t>
+  </si>
+  <si>
+    <t>.identifier</t>
+  </si>
+  <si>
+    <t>MedicationRequest.medication[x].display</t>
+  </si>
+  <si>
+    <t>Text alternative for the resource</t>
+  </si>
+  <si>
+    <t>Plain text narrative that identifies the resource in addition to the resource reference.</t>
+  </si>
+  <si>
+    <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
+  </si>
+  <si>
+    <t>Reference.display</t>
   </si>
   <si>
     <t>MedicationRequest.subject</t>
@@ -949,7 +1023,8 @@
 </t>
   </si>
   <si>
-    <t>Österreichischer Patient für den der Medikationsplaneintrag ausgestellt wird.</t>
+    <t>Patient, für den der Medikationsplaneintrag ausgestellt werden soll, der über den 
+Zentralen Patientenindex identifizierbar und Teilnehmer von ELGA e-Medikation ist.</t>
   </si>
   <si>
     <t>A link to a resource representing the person or set of individuals to whom the medication will be given.</t>
@@ -982,7 +1057,7 @@
 </t>
   </si>
   <si>
-    <t>Aufenthalt/Begegnung, während dessen/der der Medikationsplaneintrag erstellt wurde. Verwendung im Medikationsplaneintrag prüfen.</t>
+    <t>Aufenthalt/Begegnung, während dessen/der der Medikationsplaneintrag erstellt wurde. Keine Verwendung im Medikationsplaneintrag.</t>
   </si>
   <si>
     <t>The Encounter during which this [x] was created or to which the creation of this record is tightly associated.</t>
@@ -1010,9 +1085,9 @@
 </t>
   </si>
   <si>
-    <t>Zusätzliche Informationen 
+    <t>Referenz auf zusätzliche Informationen (Ressource Any)
 (z. B. Größe und Gewicht des Patienten), die die Verschreibung des Medikaments unterstützen. 
-Es müsste eigene Ressource verlinkt werden, daher keine Verwendung im Medikationsplaneintrag.</t>
+Keine Verwendung im Medikationsplaneintrag.</t>
   </si>
   <si>
     <t>Include additional information (for example, patient height and weight) that supports the ordering of the medication.</t>
@@ -1059,8 +1134,9 @@
 </t>
   </si>
   <si>
-    <t>Der Arzt oder die Ärztin, die den Medikationsplaneintrag erstellt hat 
-und für den Inhalt verantwortlich ist.</t>
+    <t>Arzt oder Ärztin, die den Medikationsplaneintrag erstellt hat
+und für den Inhalt verantwortlich ist. Eindeutig identifiziert über den GDA-Index und berechtigt auf die ELGA e-Medikation 
+des Patienten zuzugreifen.</t>
   </si>
   <si>
     <t>The individual, organization, or device that initiated the request and has responsibility for its activation.</t>
@@ -1080,7 +1156,7 @@
   </si>
   <si>
     <t>Der gewünschte Ausführende der medikamentösen Behandlung 
-(z. B. der Ausführende der Medikamentengabe). Keine Verwendung im Planeintrag.</t>
+(z. B. der Ausführende der Medikamentengabe). Keine Verwendung im Planeintrag. TODO: evtl im Kontext Medikationsblatt zu prüfen.</t>
   </si>
   <si>
     <t>The specified desired performer of the medication treatment (e.g. the performer of the medication administration).</t>
@@ -1099,7 +1175,7 @@
   </si>
   <si>
     <t>Rollen: https://hl7.org/fhir/R4/valueset-performer-role.html. 
-Keine Verwendung im Planeintrag.</t>
+Keine Verwendung im Planeintrag. TODO: evtl im Kontext Medikationsblatt zu prüfen.</t>
   </si>
   <si>
     <t>Indicates the type of performer of the administration of the medication.</t>
@@ -1128,7 +1204,7 @@
   </si>
   <si>
     <t>Die Person, die den Medikationsplaneintrag im Auftrag eines GDA eingegeben hat. 
-Keine Verwendung im Planeintrag.</t>
+TODO: Prüfen, ob eine juristische Verpflichtung zur Dokumentation der Schreibkraft besteht.</t>
   </si>
   <si>
     <t>The person who entered the order on behalf of another individual for example in the case of a verbal or a telephone order.</t>
@@ -1144,7 +1220,7 @@
   </si>
   <si>
     <t>Grund für die Verordnung des Arzneimittels. 
-Entweder Code oder Referenz (TODO: Evtl. Invariante).</t>
+Entweder Code oder Referenz (TODO: Evtl. Invariante). Erst wenn codierte Angabe möglich.</t>
   </si>
   <si>
     <t>The reason or the indication for ordering or not ordering the medication.</t>
@@ -1172,18 +1248,6 @@
   </si>
   <si>
     <t>ORC-16-Order Control Code Reason /RXE-27-Give Indication/RXO-20-Indication / RXD-21-Indication / RXG-22-Indication / RXA-19-Indication</t>
-  </si>
-  <si>
-    <t>MedicationRequest.reasonCode.id</t>
-  </si>
-  <si>
-    <t>MedicationRequest.reasonCode.extension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.reasonCode.coding</t>
-  </si>
-  <si>
-    <t>MedicationRequest.reasonCode.text</t>
   </si>
   <si>
     <t>MedicationRequest.reasonReference</t>
@@ -1193,6 +1257,9 @@
 </t>
   </si>
   <si>
+    <t>Condition or observation that supports why the prescription is being written</t>
+  </si>
+  <si>
     <t>Condition or observation that supports why the medication was ordered.</t>
   </si>
   <si>
@@ -1212,10 +1279,8 @@
 </t>
   </si>
   <si>
-    <t>URL, die auf ein Protokoll, eine Richtlinie, 
-eine Guideline oder eine andere Definition verweist, die von diesem 
-Medikationsplaneintrag ganz oder teilweise eingehalten wird. TODO: Verwendung 
-im Medikationsplaneintrag zu prüfen.</t>
+    <t>URL, die auf ein Protokoll (Richtlinie, Guideline) verweist, das von diesem 
+Medikationsplaneintrag ganz oder teilweise eingehalten wird. Derzeit keine Verwendung im Medikationsplaneintrag.</t>
   </si>
   <si>
     <t>The URL pointing to a protocol, guideline, orderset, or other definition that is adhered to in whole or in part by this MedicationRequest.</t>
@@ -1230,10 +1295,8 @@
     <t>MedicationRequest.instantiatesUri</t>
   </si>
   <si>
-    <t>URL, die auf ein extern gepflegtes Protokoll, 
-eine Richtlinie, eine Guideline oder eine andere Definition verweist, 
-die von dieser Medikamentenanforderung ganz oder teilweise eingehalten wird. 
-TODO: Verwendung im Medikationsplaneintrag zu prüfen.</t>
+    <t>URL, die auf ein extern gepflegtes Protokoll (Richtlinie, Guideline) verweist, das von diesem 
+Medikationsplaneintrag ganz oder teilweise eingehalten wird. Derzeit keine Verwendung im Medikationsplaneintrag.</t>
   </si>
   <si>
     <t>The URL pointing to an externally maintained protocol, guideline, orderset or other definition that is adhered to in whole or in part by this MedicationRequest.</t>
@@ -1283,7 +1346,7 @@
   </si>
   <si>
     <t>Gesamtmuster der Medikamentengabe (z.B. saisonal). 
-Verwendung im Medikationsplaneintrag prüfen (dosageInstruction), paused soll im Status dokumentiert werden.</t>
+Verwendung im Medikationsplaneintrag prüfen (dosageInstruction), evtl. durch Dosierungsinformationen abgedeck.</t>
   </si>
   <si>
     <t>The description of the overall patte3rn of the administration of the medication to the patient.</t>
@@ -1327,7 +1390,9 @@
 </t>
   </si>
   <si>
-    <t>Zusätzliche Informationen zum Medikationsplaneintrag. TODO: zu prüfen im Kontext Korrekturvermerk</t>
+    <t>Zusätzliche Informationen zum Medikationsplaneintrag. TODO: zu prüfen im Kontext Korrekturvermerk
+TODO: fachlich prüfen, an welchen Stellen überall Freitext erforderlich sein soll/muss. Auch im Kontext zu entered-in-error
+Informationen.</t>
   </si>
   <si>
     <t>Extra information about the prescription that could not be conveyed by the other attributes.</t>
@@ -1577,12 +1642,12 @@
     <t>MedicationRequest.substitution</t>
   </si>
   <si>
-    <t>Gibt an, ob eine Substitution Teil der Abgabe sein kann/sollte/nicht sein darf. 
-Dieser Block erläutert die Absicht des Arztes, der den Medikationsplaneintrag erstellt. 
+    <t>Gibt an, ob das Arzneimittel substituiert werden darf oder nicht. 
+Erläutert die Absicht des Arztes, der den Medikationsplaneintrag erstellt. 
 Wenn nichts angegeben ist, kann eine Substitution vorgenommen werden. 
-TODO: Zu prüfen, ob Verwendung im Medikationsplaneintrag; Dokumentation über Substitution erfolg in der Dispense-Resource. 
-Usecase: mit welchem Medikament der Patient das Medikament ersetzen kann. Hinweis: vor allem bei
-OTC Medikamenten sinnvoll, da keine geplante Abgabe dazu existiert</t>
+Die Dokumentation über eine tatsächlich erfolgte Substitution erfolgt in der Dispense-Resource. 
+TODO: Usecase fachlich zu prüfen. Es kann für den Patienten selbst oder das Pflegeheim eine wichtige Information sein,
+mit welchem Medikament das verordnete Medikament im Bedarfsfall ersetzen werden kann.</t>
   </si>
   <si>
     <t>Indicates whether or not substitution can or should be part of the dispense. In some cases, substitution must happen, in other cases substitution must not happen. This block explains the prescriber's intent. If nothing is specified substitution may be done.</t>
@@ -1686,10 +1751,8 @@
 </t>
   </si>
   <si>
-    <t>Bezeichnet ein tatsächliches/potenzielles klinisches Problem mit oder 
-zwischen aktiven/vorgeschlagenen klinischen Maßnahmen für einen Patienten, 
-z. B. Wechselwirkungen zwischen Medikamenten, doppelte Therapie, Dosierungswarnung usw. 
-TODO: Es wäre eine eigene Ressource nötig, daher unrealistisch.</t>
+    <t>Klinisches Problem mit Maßnahme. Nur mittesl Referenz auf Ressouce DetectedIssue, 
+Keine Verwendung im Medikationsplaneintrag.</t>
   </si>
   <si>
     <t>Indicates an actual or potential clinical issue with or between one or more active or proposed clinical actions for a patient; e.g. Drug-drug interaction, duplicate therapy, dosage alert etc.</t>
@@ -1708,9 +1771,8 @@
 </t>
   </si>
   <si>
-    <t>Referenz auf Provenance-Ressourcen, 
-die verschiedene relevante Versionen dieser Ressource dokumentieren. 
-TODO: Verwendung im Medikationsplaneintrag zu prüfen.</t>
+    <t>Referenz auf Provenance-Ressourcen, die verschiedene relevante Versionen dieser Ressource dokumentieren. 
+Keine Verwendung im Medikationsplaneintrag.</t>
   </si>
   <si>
     <t>Links to Provenance records for past versions of this resource or fulfilling request or event resources that identify key state transitions or updates that are likely to be relevant to a user looking at the current version of the resource.</t>
@@ -2050,9 +2112,9 @@
   <dimension ref="A1:AO75"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="58.75" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="51.68359375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="51.68359375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="23.5546875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="22.41015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -2928,7 +2990,7 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G8" t="s" s="2">
         <v>81</v>
@@ -2990,19 +3052,17 @@
         <v>21</v>
       </c>
       <c r="AB8" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC8" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AC8" s="2"/>
       <c r="AD8" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE8" t="s" s="2">
-        <v>21</v>
+        <v>133</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -3023,7 +3083,7 @@
         <v>21</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AN8" t="s" s="2">
         <v>21</v>
@@ -3034,21 +3094,23 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="C9" s="2"/>
+        <v>126</v>
+      </c>
+      <c r="C9" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="D9" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>21</v>
@@ -3060,15 +3122,17 @@
         <v>21</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N9" s="2"/>
+        <v>140</v>
+      </c>
+      <c r="N9" t="s" s="2">
+        <v>131</v>
+      </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>21</v>
@@ -3105,17 +3169,19 @@
         <v>21</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AC9" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD9" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -3127,16 +3193,16 @@
         <v>21</v>
       </c>
       <c r="AJ9" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK9" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL9" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="AK9" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL9" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="AM9" t="s" s="2">
-        <v>21</v>
+        <v>142</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>21</v>
@@ -3147,13 +3213,13 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>21</v>
@@ -3163,7 +3229,7 @@
         <v>80</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>21</v>
@@ -3175,15 +3241,17 @@
         <v>21</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N10" s="2"/>
+        <v>147</v>
+      </c>
+      <c r="N10" t="s" s="2">
+        <v>131</v>
+      </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>21</v>
@@ -3232,7 +3300,7 @@
         <v>21</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -3241,10 +3309,10 @@
         <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>147</v>
+        <v>21</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>21</v>
@@ -3253,7 +3321,7 @@
         <v>21</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>21</v>
@@ -3264,14 +3332,12 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="C11" t="s" s="2">
         <v>149</v>
       </c>
+      <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
         <v>21</v>
       </c>
@@ -3280,7 +3346,7 @@
         <v>80</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>21</v>
@@ -3337,19 +3403,17 @@
         <v>21</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC11" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="AC11" s="2"/>
       <c r="AD11" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>21</v>
+        <v>133</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3358,10 +3422,10 @@
         <v>81</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>147</v>
+        <v>21</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>21</v>
@@ -3370,7 +3434,7 @@
         <v>21</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="AN11" t="s" s="2">
         <v>21</v>
@@ -3381,13 +3445,13 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>21</v>
@@ -3409,13 +3473,13 @@
         <v>21</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3466,7 +3530,7 @@
         <v>21</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3475,10 +3539,10 @@
         <v>81</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>21</v>
@@ -3487,7 +3551,7 @@
         <v>21</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>21</v>
+        <v>135</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>21</v>
@@ -3498,46 +3562,44 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="C13" s="2"/>
+        <v>149</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="D13" t="s" s="2">
-        <v>159</v>
+        <v>21</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O13" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>21</v>
       </c>
@@ -3585,7 +3647,7 @@
         <v>21</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3594,10 +3656,10 @@
         <v>81</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>21</v>
@@ -3606,7 +3668,7 @@
         <v>21</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>21</v>
@@ -3615,14 +3677,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="C14" s="2"/>
+        <v>149</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="D14" t="s" s="2">
         <v>21</v>
       </c>
@@ -3631,10 +3695,10 @@
         <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>21</v>
@@ -3643,17 +3707,15 @@
         <v>21</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>169</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>21</v>
@@ -3702,7 +3764,7 @@
         <v>21</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -3711,67 +3773,69 @@
         <v>81</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>102</v>
+        <v>155</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>170</v>
+        <v>21</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>171</v>
+        <v>21</v>
       </c>
       <c r="AM14" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN14" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO14" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" hidden="true">
+      <c r="A15" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="AN14" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="AO14" t="s" s="2">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>175</v>
-      </c>
       <c r="B15" t="s" s="2">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>21</v>
+        <v>173</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>91</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="N15" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="N15" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>21</v>
       </c>
@@ -3795,66 +3859,66 @@
         <v>21</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF15" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AG15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH15" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AK15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM15" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AN15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO15" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="Y15" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="AG15" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AH15" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ15" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK15" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="AN15" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" hidden="true">
-      <c r="A16" t="s" s="2">
-        <v>186</v>
-      </c>
       <c r="B16" t="s" s="2">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3865,10 +3929,10 @@
         <v>80</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>21</v>
@@ -3877,16 +3941,16 @@
         <v>21</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3912,13 +3976,13 @@
         <v>21</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>192</v>
+        <v>21</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>193</v>
+        <v>21</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>21</v>
@@ -3936,13 +4000,13 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>21</v>
@@ -3951,27 +4015,27 @@
         <v>102</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>21</v>
+        <v>187</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>21</v>
+        <v>188</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3997,13 +4061,13 @@
         <v>110</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4014,7 +4078,7 @@
         <v>21</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>200</v>
+        <v>21</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>21</v>
@@ -4029,13 +4093,13 @@
         <v>21</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>21</v>
@@ -4053,7 +4117,7 @@
         <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>90</v>
@@ -4068,27 +4132,27 @@
         <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>21</v>
+        <v>197</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4096,13 +4160,13 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>21</v>
@@ -4111,16 +4175,16 @@
         <v>21</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4131,7 +4195,7 @@
         <v>21</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>210</v>
+        <v>21</v>
       </c>
       <c r="T18" t="s" s="2">
         <v>21</v>
@@ -4146,13 +4210,13 @@
         <v>21</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>21</v>
@@ -4170,13 +4234,13 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>21</v>
@@ -4185,27 +4249,27 @@
         <v>102</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>21</v>
+        <v>208</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>213</v>
+        <v>21</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>205</v>
+        <v>21</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4213,16 +4277,16 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J19" t="s" s="2">
         <v>91</v>
@@ -4231,12 +4295,14 @@
         <v>110</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>212</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>213</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>21</v>
@@ -4246,7 +4312,7 @@
         <v>21</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>21</v>
+        <v>214</v>
       </c>
       <c r="T19" t="s" s="2">
         <v>21</v>
@@ -4261,13 +4327,13 @@
         <v>21</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>21</v>
@@ -4285,10 +4351,10 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>90</v>
@@ -4300,16 +4366,16 @@
         <v>102</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>21</v>
@@ -4317,10 +4383,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4328,7 +4394,7 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>90</v>
@@ -4337,22 +4403,22 @@
         <v>91</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>224</v>
+        <v>201</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4363,7 +4429,7 @@
         <v>21</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>21</v>
+        <v>224</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>21</v>
@@ -4378,13 +4444,13 @@
         <v>21</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>21</v>
+        <v>205</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>21</v>
+        <v>225</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>21</v>
+        <v>226</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>21</v>
@@ -4402,13 +4468,13 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>21</v>
@@ -4420,13 +4486,13 @@
         <v>21</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>21</v>
+        <v>227</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>228</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>21</v>
+        <v>219</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>21</v>
@@ -4460,13 +4526,13 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4493,13 +4559,13 @@
         <v>21</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>21</v>
+        <v>193</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>21</v>
+        <v>232</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>21</v>
+        <v>233</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>21</v>
@@ -4532,16 +4598,16 @@
         <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>21</v>
+        <v>234</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>21</v>
+        <v>236</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>21</v>
@@ -4549,10 +4615,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4560,31 +4626,31 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I22" t="s" s="2">
         <v>91</v>
-      </c>
-      <c r="I22" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4610,32 +4676,34 @@
         <v>21</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>239</v>
+        <v>21</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>240</v>
+        <v>21</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="AC22" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>242</v>
+        <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>90</v>
@@ -4647,31 +4715,29 @@
         <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AN22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO22" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" hidden="true">
+      <c r="A23" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="AL22" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="2">
-        <v>248</v>
-      </c>
       <c r="B23" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="C23" t="s" s="2">
-        <v>249</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
         <v>21</v>
       </c>
@@ -4692,17 +4758,15 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>187</v>
+        <v>244</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>238</v>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>21</v>
@@ -4727,32 +4791,32 @@
         <v>21</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="Y23" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z23" t="s" s="2">
-        <v>251</v>
+        <v>21</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>21</v>
+        <v>247</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>90</v>
@@ -4764,29 +4828,31 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>243</v>
+        <v>21</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>244</v>
+        <v>21</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>246</v>
+        <v>21</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>247</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>250</v>
+      </c>
       <c r="D24" t="s" s="2">
         <v>21</v>
       </c>
@@ -4804,16 +4870,16 @@
         <v>21</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4864,7 +4930,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4876,7 +4942,7 @@
         <v>21</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>21</v>
@@ -4885,7 +4951,7 @@
         <v>21</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>21</v>
@@ -4896,21 +4962,23 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="C25" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>253</v>
+      </c>
       <c r="D25" t="s" s="2">
-        <v>159</v>
+        <v>21</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>21</v>
@@ -4919,20 +4987,18 @@
         <v>21</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>135</v>
+        <v>254</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>162</v>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>21</v>
@@ -4969,31 +5035,31 @@
         <v>21</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>263</v>
+        <v>21</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>264</v>
+        <v>243</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>21</v>
@@ -5002,7 +5068,7 @@
         <v>21</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>21</v>
@@ -5011,12 +5077,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5027,10 +5093,10 @@
         <v>90</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>21</v>
@@ -5039,20 +5105,18 @@
         <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>271</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>21</v>
       </c>
@@ -5100,13 +5164,13 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>272</v>
+        <v>256</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>21</v>
@@ -5115,27 +5179,27 @@
         <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>21</v>
+        <v>261</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>21</v>
+        <v>262</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>21</v>
+        <v>264</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>274</v>
+        <v>265</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5155,23 +5219,19 @@
         <v>21</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>280</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>21</v>
       </c>
@@ -5219,7 +5279,7 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5231,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>21</v>
@@ -5240,55 +5300,53 @@
         <v>21</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>283</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="C28" t="s" s="2">
-        <v>285</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>21</v>
+        <v>173</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>286</v>
+        <v>150</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>287</v>
+        <v>273</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>237</v>
+        <v>274</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>238</v>
+        <v>176</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5326,54 +5384,54 @@
         <v>21</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>21</v>
+        <v>153</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>21</v>
+        <v>275</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>21</v>
+        <v>133</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>234</v>
+        <v>276</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>102</v>
+        <v>155</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>243</v>
+        <v>21</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>244</v>
+        <v>21</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>245</v>
+        <v>271</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>246</v>
+        <v>21</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>247</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5381,13 +5439,13 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>21</v>
@@ -5396,16 +5454,16 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>289</v>
+        <v>267</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5455,42 +5513,42 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>21</v>
+        <v>282</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>102</v>
+        <v>283</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>293</v>
+        <v>21</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>294</v>
+        <v>21</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>295</v>
+        <v>135</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>296</v>
+        <v>21</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>297</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>298</v>
+        <v>284</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>298</v>
+        <v>284</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5501,7 +5559,7 @@
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>21</v>
@@ -5510,19 +5568,19 @@
         <v>21</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>299</v>
+        <v>104</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5548,13 +5606,13 @@
         <v>21</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>21</v>
+        <v>288</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>21</v>
+        <v>289</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>21</v>
+        <v>290</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>21</v>
@@ -5572,7 +5630,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5587,27 +5645,27 @@
         <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>303</v>
+        <v>21</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>183</v>
+        <v>21</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>304</v>
+        <v>135</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>305</v>
+        <v>21</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>306</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5618,7 +5676,7 @@
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>21</v>
@@ -5627,18 +5685,20 @@
         <v>21</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>308</v>
+        <v>180</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>309</v>
+        <v>293</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>21</v>
@@ -5687,13 +5747,13 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>307</v>
+        <v>296</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>21</v>
@@ -5702,27 +5762,27 @@
         <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>311</v>
+        <v>21</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>305</v>
+        <v>21</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5730,13 +5790,13 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>21</v>
@@ -5745,15 +5805,17 @@
         <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>314</v>
+        <v>267</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>315</v>
+        <v>299</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>300</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>21</v>
@@ -5802,7 +5864,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5817,27 +5879,27 @@
         <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>317</v>
+        <v>21</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>318</v>
+        <v>21</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>319</v>
+        <v>135</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>320</v>
+        <v>21</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>321</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>322</v>
+        <v>303</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>322</v>
+        <v>303</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5860,15 +5922,17 @@
         <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>323</v>
+        <v>304</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>324</v>
+        <v>305</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>306</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>21</v>
@@ -5917,10 +5981,10 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>322</v>
+        <v>303</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>90</v>
@@ -5932,27 +5996,27 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>326</v>
+        <v>308</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>21</v>
+        <v>309</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>295</v>
+        <v>310</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>327</v>
+        <v>311</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>21</v>
+        <v>312</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>328</v>
+        <v>313</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>328</v>
+        <v>313</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5975,15 +6039,17 @@
         <v>21</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>329</v>
+        <v>314</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>330</v>
+        <v>315</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>316</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>317</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>21</v>
@@ -6032,7 +6098,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>328</v>
+        <v>313</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6047,27 +6113,27 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>332</v>
+        <v>318</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>21</v>
+        <v>197</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>333</v>
+        <v>319</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>21</v>
+        <v>321</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>335</v>
+        <v>322</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>335</v>
+        <v>322</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6087,20 +6153,18 @@
         <v>21</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>187</v>
+        <v>323</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>338</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>21</v>
@@ -6125,13 +6189,13 @@
         <v>21</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>339</v>
+        <v>21</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>340</v>
+        <v>21</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>21</v>
@@ -6149,13 +6213,13 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>335</v>
+        <v>322</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>21</v>
@@ -6164,27 +6228,27 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>341</v>
+        <v>326</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>342</v>
+        <v>327</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>21</v>
+        <v>320</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6192,28 +6256,28 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>344</v>
+        <v>329</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>345</v>
+        <v>330</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>346</v>
+        <v>331</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6264,7 +6328,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6279,27 +6343,27 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>21</v>
+        <v>332</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>21</v>
+        <v>333</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>21</v>
+        <v>336</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6307,10 +6371,10 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>91</v>
@@ -6319,20 +6383,18 @@
         <v>21</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>187</v>
+        <v>338</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>352</v>
-      </c>
+        <v>340</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>21</v>
@@ -6357,13 +6419,13 @@
         <v>21</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>353</v>
+        <v>21</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>354</v>
+        <v>21</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>21</v>
@@ -6381,13 +6443,13 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>21</v>
@@ -6396,27 +6458,27 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>355</v>
+        <v>341</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>356</v>
+        <v>21</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>357</v>
+        <v>310</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>358</v>
+        <v>342</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>359</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>360</v>
+        <v>343</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>360</v>
+        <v>343</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6427,7 +6489,7 @@
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>21</v>
@@ -6439,13 +6501,13 @@
         <v>21</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>254</v>
+        <v>344</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>255</v>
+        <v>345</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>256</v>
+        <v>346</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6496,7 +6558,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>257</v>
+        <v>343</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6508,19 +6570,19 @@
         <v>21</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>21</v>
+        <v>347</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>258</v>
+        <v>348</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>21</v>
+        <v>349</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>21</v>
@@ -6528,21 +6590,21 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>361</v>
+        <v>350</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>361</v>
+        <v>350</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>159</v>
+        <v>21</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>21</v>
@@ -6551,19 +6613,19 @@
         <v>21</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>135</v>
+        <v>201</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>261</v>
+        <v>351</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>262</v>
+        <v>352</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>162</v>
+        <v>353</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6589,52 +6651,52 @@
         <v>21</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>21</v>
+        <v>205</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>21</v>
+        <v>354</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>21</v>
+        <v>355</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>263</v>
+        <v>21</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>264</v>
+        <v>350</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>21</v>
+        <v>356</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>258</v>
+        <v>357</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>21</v>
@@ -6645,10 +6707,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6656,10 +6718,10 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>21</v>
@@ -6668,23 +6730,19 @@
         <v>21</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>267</v>
+        <v>359</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>268</v>
+        <v>360</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>271</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>21</v>
       </c>
@@ -6732,13 +6790,13 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>272</v>
+        <v>358</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>21</v>
@@ -6753,21 +6811,21 @@
         <v>21</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>273</v>
+        <v>362</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>21</v>
+        <v>363</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>274</v>
+        <v>21</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6778,7 +6836,7 @@
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>21</v>
@@ -6787,23 +6845,21 @@
         <v>21</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>254</v>
+        <v>201</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>277</v>
+        <v>365</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>278</v>
+        <v>366</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>280</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>21</v>
       </c>
@@ -6827,13 +6883,13 @@
         <v>21</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>21</v>
+        <v>205</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>21</v>
+        <v>368</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>21</v>
+        <v>369</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>21</v>
@@ -6851,13 +6907,13 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>281</v>
+        <v>364</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>21</v>
@@ -6866,27 +6922,27 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>21</v>
+        <v>370</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>21</v>
+        <v>371</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>282</v>
+        <v>372</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>21</v>
+        <v>373</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>283</v>
+        <v>374</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6897,10 +6953,10 @@
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>21</v>
@@ -6909,16 +6965,16 @@
         <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>350</v>
+        <v>377</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6968,7 +7024,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6983,27 +7039,27 @@
         <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>358</v>
+        <v>373</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7014,10 +7070,10 @@
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>21</v>
@@ -7026,13 +7082,13 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7083,7 +7139,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7098,13 +7154,13 @@
         <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>21</v>
@@ -7113,12 +7169,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7129,10 +7185,10 @@
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>21</v>
@@ -7144,10 +7200,10 @@
         <v>104</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7198,7 +7254,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7219,7 +7275,7 @@
         <v>21</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>21</v>
@@ -7230,10 +7286,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7256,13 +7312,13 @@
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7313,7 +7369,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7328,13 +7384,13 @@
         <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>21</v>
@@ -7345,10 +7401,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7371,17 +7427,17 @@
         <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>388</v>
+        <v>400</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>21</v>
@@ -7430,7 +7486,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7445,13 +7501,13 @@
         <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>21</v>
@@ -7462,10 +7518,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7488,16 +7544,16 @@
         <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7523,13 +7579,13 @@
         <v>21</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>21</v>
@@ -7547,7 +7603,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7568,7 +7624,7 @@
         <v>21</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>21</v>
@@ -7579,10 +7635,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7605,13 +7661,13 @@
         <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7662,7 +7718,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7677,13 +7733,13 @@
         <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>21</v>
@@ -7694,10 +7750,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7720,13 +7776,13 @@
         <v>21</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>407</v>
+        <v>419</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7777,7 +7833,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7792,13 +7848,13 @@
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>21</v>
@@ -7809,10 +7865,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>411</v>
+        <v>423</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>411</v>
+        <v>423</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7835,16 +7891,16 @@
         <v>21</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>414</v>
+        <v>426</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>415</v>
+        <v>427</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7894,7 +7950,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>411</v>
+        <v>423</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7909,13 +7965,13 @@
         <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>21</v>
@@ -7926,10 +7982,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7952,13 +8008,13 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8009,7 +8065,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8027,10 +8083,10 @@
         <v>21</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>21</v>
@@ -8041,10 +8097,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8067,13 +8123,13 @@
         <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8124,7 +8180,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8145,7 +8201,7 @@
         <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>21</v>
@@ -8156,14 +8212,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8182,16 +8238,16 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8241,7 +8297,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8253,7 +8309,7 @@
         <v>21</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>21</v>
@@ -8262,7 +8318,7 @@
         <v>21</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>21</v>
@@ -8273,14 +8329,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8299,19 +8355,19 @@
         <v>91</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>21</v>
@@ -8360,7 +8416,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8372,7 +8428,7 @@
         <v>21</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>21</v>
@@ -8381,7 +8437,7 @@
         <v>21</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>21</v>
@@ -8392,10 +8448,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8418,16 +8474,16 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>432</v>
+        <v>444</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8477,7 +8533,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8498,7 +8554,7 @@
         <v>21</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>21</v>
@@ -8509,10 +8565,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8535,13 +8591,13 @@
         <v>21</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8592,7 +8648,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8613,7 +8669,7 @@
         <v>21</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>21</v>
@@ -8624,14 +8680,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8650,16 +8706,16 @@
         <v>21</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8709,7 +8765,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8721,7 +8777,7 @@
         <v>21</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>21</v>
@@ -8730,7 +8786,7 @@
         <v>21</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>21</v>
@@ -8741,14 +8797,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>438</v>
+        <v>450</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>438</v>
+        <v>450</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8767,19 +8823,19 @@
         <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>21</v>
@@ -8828,7 +8884,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8840,7 +8896,7 @@
         <v>21</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>21</v>
@@ -8849,7 +8905,7 @@
         <v>21</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>21</v>
@@ -8860,10 +8916,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>439</v>
+        <v>451</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>439</v>
+        <v>451</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8886,13 +8942,13 @@
         <v>21</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8943,7 +8999,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>439</v>
+        <v>451</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -8964,7 +9020,7 @@
         <v>21</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>21</v>
@@ -8975,10 +9031,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9001,13 +9057,13 @@
         <v>21</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>447</v>
+        <v>459</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9058,7 +9114,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9079,7 +9135,7 @@
         <v>21</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>21</v>
@@ -9090,10 +9146,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>449</v>
+        <v>461</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>449</v>
+        <v>461</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9116,13 +9172,13 @@
         <v>21</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9173,7 +9229,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>449</v>
+        <v>461</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9194,7 +9250,7 @@
         <v>21</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>21</v>
@@ -9205,10 +9261,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9231,19 +9287,19 @@
         <v>21</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>453</v>
+        <v>465</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>454</v>
+        <v>466</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>455</v>
+        <v>467</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>457</v>
+        <v>469</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>21</v>
@@ -9292,7 +9348,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9310,10 +9366,10 @@
         <v>21</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>458</v>
+        <v>470</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>459</v>
+        <v>471</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>21</v>
@@ -9324,10 +9380,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9350,16 +9406,16 @@
         <v>21</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>462</v>
+        <v>474</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>463</v>
+        <v>475</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9409,7 +9465,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9427,24 +9483,24 @@
         <v>21</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>466</v>
+        <v>478</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>467</v>
+        <v>479</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9467,13 +9523,13 @@
         <v>21</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>470</v>
+        <v>482</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9524,7 +9580,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9542,24 +9598,24 @@
         <v>21</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>472</v>
+        <v>484</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>473</v>
+        <v>485</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>474</v>
+        <v>486</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>474</v>
+        <v>486</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9582,16 +9638,16 @@
         <v>21</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>476</v>
+        <v>488</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9641,7 +9697,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>474</v>
+        <v>486</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9659,10 +9715,10 @@
         <v>21</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>21</v>
@@ -9673,10 +9729,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9699,13 +9755,13 @@
         <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>481</v>
+        <v>493</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>483</v>
+        <v>495</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9756,7 +9812,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -9777,10 +9833,10 @@
         <v>21</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>484</v>
+        <v>496</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>348</v>
+        <v>363</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>21</v>
@@ -9788,10 +9844,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>485</v>
+        <v>497</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>485</v>
+        <v>497</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9814,13 +9870,13 @@
         <v>21</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9871,7 +9927,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>485</v>
+        <v>497</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -9889,10 +9945,10 @@
         <v>21</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>21</v>
@@ -9903,10 +9959,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>490</v>
+        <v>502</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>490</v>
+        <v>502</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9929,13 +9985,13 @@
         <v>21</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9986,7 +10042,7 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10007,7 +10063,7 @@
         <v>21</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>21</v>
@@ -10018,14 +10074,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>491</v>
+        <v>503</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>491</v>
+        <v>503</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10044,16 +10100,16 @@
         <v>21</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10103,7 +10159,7 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10115,7 +10171,7 @@
         <v>21</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>21</v>
@@ -10124,7 +10180,7 @@
         <v>21</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>21</v>
@@ -10135,14 +10191,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10161,19 +10217,19 @@
         <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>21</v>
@@ -10222,7 +10278,7 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10234,7 +10290,7 @@
         <v>21</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>21</v>
@@ -10243,7 +10299,7 @@
         <v>21</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>21</v>
@@ -10254,10 +10310,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10280,16 +10336,16 @@
         <v>21</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>495</v>
+        <v>507</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>497</v>
+        <v>509</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10315,13 +10371,13 @@
         <v>21</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>21</v>
@@ -10339,7 +10395,7 @@
         <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>90</v>
@@ -10357,24 +10413,24 @@
         <v>21</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>500</v>
+        <v>512</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>501</v>
+        <v>513</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10397,13 +10453,13 @@
         <v>21</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10430,13 +10486,13 @@
         <v>21</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>505</v>
+        <v>517</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>21</v>
@@ -10454,7 +10510,7 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10472,24 +10528,24 @@
         <v>21</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>508</v>
+        <v>520</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>509</v>
+        <v>521</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10512,13 +10568,13 @@
         <v>21</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10569,7 +10625,7 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10584,13 +10640,13 @@
         <v>102</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>21</v>
@@ -10601,14 +10657,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>516</v>
+        <v>528</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>516</v>
+        <v>528</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10627,16 +10683,16 @@
         <v>21</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>518</v>
+        <v>530</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>521</v>
+        <v>533</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10686,7 +10742,7 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>516</v>
+        <v>528</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -10707,7 +10763,7 @@
         <v>21</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>522</v>
+        <v>534</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>21</v>
@@ -10718,10 +10774,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10744,16 +10800,16 @@
         <v>21</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>524</v>
+        <v>536</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>525</v>
+        <v>537</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>526</v>
+        <v>538</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>527</v>
+        <v>539</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10803,7 +10859,7 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -10818,13 +10874,13 @@
         <v>102</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>528</v>
+        <v>540</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-12T16:23:56+00:00</t>
+    <t>2026-02-16T10:10:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2794" uniqueCount="542">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2793" uniqueCount="541">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T10:10:16+00:00</t>
+    <t>2026-02-16T15:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -632,11 +632,9 @@
     <t>MedicationRequest.status</t>
   </si>
   <si>
-    <t xml:space="preserve">Status des Medikationsplaneintrags. TODO: Einschränken auf active, complete, on hold; 
-(req) active | on-hold | cancelled | completed | entered-in-error | stopped | draft | unknown 
-TODO: Fachlich zu püfen, ob im Medikationsplan dokumentiert werden soll, dass und warum ein Medikament abgesetzt wurde (z.B. Allergie).
+    <t>Status des Medikationsplaneintrags. VS Einschränkung auf active, complete, on-hold, stopped (?); TODO: Fachlich zu püfen, ob im Medikationsplan dokumentiert werden soll, dass und warum ein Medikament abgesetzt wurde (Status: stopped, z.B. bei Allergie).
 Auch im Kontext mit statusReason, wo dieser Grund codiert angegeben werden kann.
-</t>
+(entfernt: cancelled, entered-in-error, draft, unknown)</t>
   </si>
   <si>
     <t>A code specifying the current state of the order.  Generally, this will be active or completed state.</t>
@@ -648,10 +646,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>A coded concept specifying the state of the prescribing event. Describes the lifecycle of the prescription.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationrequest-status|4.0.1</t>
+    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/MedikationsplaneintragStatusVS</t>
   </si>
   <si>
     <t>Request.status</t>
@@ -674,7 +669,7 @@
   </si>
   <si>
     <t>Grund für den aktuellen Status des Medikationsplaneintrags: (ex) https://hl7.org/fhir/R4/valueset-medicationrequest-status-reason.html.
-TODO: Verwendung prüfen im Zusammenhang mit status.</t>
+TODO: Verwendung fachlich zu prüfen im Zusammenhang mit Status.</t>
   </si>
   <si>
     <t>Captures the reason for the current state of the MedicationRequest.</t>
@@ -701,9 +696,7 @@
     <t>MedicationRequest.intent</t>
   </si>
   <si>
-    <t>TODO: Begründung, warum hier immer "order" anzugeben ist:
-Der Medikationsplaneintrag ist eine Handlungsermächtigung. Dieser wurde von einem:r Arzt:Ärztin erstellt und ermächtigt (auch andere Ärzte) zur Ausstellung einer geplanten Abgabe
-basierend auf diesen Eintrag.
+    <t>Ein Medikationsplaneintrag ist eine autorisierte ärztliche Anordnung und stellt eine verbindliche Einnahmeanweisung für den Patienten dar, auf dessen Basis eine geplante Abgabe erstellt werden kann. Fixer Wert: "order".
 (req) proposal | plan | order | original-order | reflex-order | filler-order | instance-order | option. 
 https://hl7.org/fhir/R4/valueset-medicationrequest-intent.html</t>
   </si>
@@ -3913,7 +3906,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
         <v>179</v>
       </c>
@@ -3926,13 +3919,13 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>21</v>
@@ -4095,11 +4088,9 @@
       <c r="X17" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="Y17" t="s" s="2">
+      <c r="Y17" s="2"/>
+      <c r="Z17" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="Z17" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>21</v>
@@ -4132,16 +4123,16 @@
         <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AL17" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="AL17" t="s" s="2">
+      <c r="AM17" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="AM17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>21</v>
@@ -4149,10 +4140,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4175,16 +4166,16 @@
         <v>21</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4210,14 +4201,14 @@
         <v>21</v>
       </c>
       <c r="X18" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="Y18" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="Y18" t="s" s="2">
+      <c r="Z18" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="Z18" t="s" s="2">
-        <v>207</v>
-      </c>
       <c r="AA18" t="s" s="2">
         <v>21</v>
       </c>
@@ -4234,7 +4225,7 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4249,13 +4240,13 @@
         <v>102</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM18" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="AL18" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>21</v>
@@ -4266,10 +4257,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4295,13 +4286,13 @@
         <v>110</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4312,7 +4303,7 @@
         <v>21</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="T19" t="s" s="2">
         <v>21</v>
@@ -4330,11 +4321,11 @@
         <v>193</v>
       </c>
       <c r="Y19" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Z19" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="Z19" t="s" s="2">
-        <v>216</v>
-      </c>
       <c r="AA19" t="s" s="2">
         <v>21</v>
       </c>
@@ -4351,7 +4342,7 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>90</v>
@@ -4366,16 +4357,16 @@
         <v>102</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM19" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="AL19" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM19" t="s" s="2">
+      <c r="AN19" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>219</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>21</v>
@@ -4383,10 +4374,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4409,16 +4400,16 @@
         <v>21</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4429,29 +4420,29 @@
         <v>21</v>
       </c>
       <c r="S20" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="T20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X20" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="Y20" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="T20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X20" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="Y20" t="s" s="2">
+      <c r="Z20" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="Z20" t="s" s="2">
-        <v>226</v>
-      </c>
       <c r="AA20" t="s" s="2">
         <v>21</v>
       </c>
@@ -4468,7 +4459,7 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4486,13 +4477,13 @@
         <v>21</v>
       </c>
       <c r="AL20" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="AM20" t="s" s="2">
-        <v>228</v>
-      </c>
       <c r="AN20" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>21</v>
@@ -4500,10 +4491,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4529,10 +4520,10 @@
         <v>110</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>231</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4562,11 +4553,11 @@
         <v>193</v>
       </c>
       <c r="Y21" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="Z21" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="Z21" t="s" s="2">
-        <v>233</v>
-      </c>
       <c r="AA21" t="s" s="2">
         <v>21</v>
       </c>
@@ -4583,7 +4574,7 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4598,16 +4589,16 @@
         <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="AL21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM21" t="s" s="2">
+      <c r="AN21" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>236</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>21</v>
@@ -4615,10 +4606,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4641,16 +4632,16 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4700,7 +4691,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4721,7 +4712,7 @@
         <v>21</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>21</v>
@@ -4732,10 +4723,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4758,13 +4749,13 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>246</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4810,10 +4801,10 @@
         <v>21</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4834,7 +4825,7 @@
         <v>21</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>21</v>
@@ -4845,13 +4836,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="C24" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="C24" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>21</v>
@@ -4873,13 +4864,13 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4930,7 +4921,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4951,7 +4942,7 @@
         <v>21</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>21</v>
@@ -4962,13 +4953,13 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="C25" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="D25" t="s" s="2">
         <v>21</v>
@@ -4990,13 +4981,13 @@
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="L25" t="s" s="2">
-        <v>255</v>
-      </c>
       <c r="M25" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -5047,7 +5038,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5068,7 +5059,7 @@
         <v>21</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>21</v>
@@ -5079,10 +5070,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5105,16 +5096,16 @@
         <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5164,7 +5155,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>90</v>
@@ -5179,27 +5170,27 @@
         <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AL26" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="AL26" t="s" s="2">
+      <c r="AM26" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="AM26" t="s" s="2">
+      <c r="AN26" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="AN26" t="s" s="2">
+      <c r="AO26" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>265</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5222,13 +5213,13 @@
         <v>21</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5279,7 +5270,7 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5300,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>21</v>
@@ -5311,10 +5302,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5340,10 +5331,10 @@
         <v>150</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="N28" t="s" s="2">
         <v>176</v>
@@ -5387,7 +5378,7 @@
         <v>153</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>21</v>
@@ -5396,7 +5387,7 @@
         <v>133</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5417,7 +5408,7 @@
         <v>21</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>21</v>
@@ -5428,10 +5419,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5454,16 +5445,16 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5513,7 +5504,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5522,10 +5513,10 @@
         <v>90</v>
       </c>
       <c r="AI29" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="AJ29" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>21</v>
@@ -5545,10 +5536,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5574,13 +5565,13 @@
         <v>104</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5606,31 +5597,31 @@
         <v>21</v>
       </c>
       <c r="X30" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="Y30" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="Y30" t="s" s="2">
+      <c r="Z30" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="Z30" t="s" s="2">
+      <c r="AA30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF30" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5662,10 +5653,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5691,13 +5682,13 @@
         <v>180</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5747,7 +5738,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5768,7 +5759,7 @@
         <v>21</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>21</v>
@@ -5779,10 +5770,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5805,16 +5796,16 @@
         <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5864,7 +5855,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5896,10 +5887,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5922,16 +5913,16 @@
         <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5981,7 +5972,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>90</v>
@@ -5996,27 +5987,27 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AL33" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="AL33" t="s" s="2">
+      <c r="AM33" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AM33" t="s" s="2">
+      <c r="AN33" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="AN33" t="s" s="2">
+      <c r="AO33" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>312</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6039,16 +6030,16 @@
         <v>21</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6098,7 +6089,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6113,27 +6104,27 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AM34" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="AL34" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="AM34" t="s" s="2">
+      <c r="AN34" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="AN34" t="s" s="2">
+      <c r="AO34" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>321</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6156,13 +6147,13 @@
         <v>21</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6213,7 +6204,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6228,16 +6219,16 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="AL35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>327</v>
-      </c>
       <c r="AN35" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>21</v>
@@ -6245,10 +6236,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6271,13 +6262,13 @@
         <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6328,7 +6319,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6343,27 +6334,27 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AL36" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="AL36" t="s" s="2">
+      <c r="AM36" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="AM36" t="s" s="2">
+      <c r="AN36" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="AN36" t="s" s="2">
+      <c r="AO36" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>336</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6386,13 +6377,13 @@
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6443,7 +6434,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6458,16 +6449,16 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>21</v>
@@ -6475,10 +6466,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6501,13 +6492,13 @@
         <v>21</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>346</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6558,7 +6549,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6573,16 +6564,16 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="AL38" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM38" t="s" s="2">
+      <c r="AN38" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>21</v>
@@ -6590,10 +6581,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6616,16 +6607,16 @@
         <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6651,14 +6642,14 @@
         <v>21</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Y39" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="Z39" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="Z39" t="s" s="2">
-        <v>355</v>
-      </c>
       <c r="AA39" t="s" s="2">
         <v>21</v>
       </c>
@@ -6675,7 +6666,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6690,13 +6681,13 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>21</v>
@@ -6707,10 +6698,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6733,13 +6724,13 @@
         <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6790,7 +6781,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6811,10 +6802,10 @@
         <v>21</v>
       </c>
       <c r="AM40" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>21</v>
@@ -6822,10 +6813,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6848,16 +6839,16 @@
         <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6883,14 +6874,14 @@
         <v>21</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Y41" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="Z41" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="Z41" t="s" s="2">
-        <v>369</v>
-      </c>
       <c r="AA41" t="s" s="2">
         <v>21</v>
       </c>
@@ -6907,7 +6898,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6922,27 +6913,27 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AL41" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="AL41" t="s" s="2">
+      <c r="AM41" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AN41" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AN41" t="s" s="2">
+      <c r="AO41" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>374</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6965,16 +6956,16 @@
         <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7024,7 +7015,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7039,16 +7030,16 @@
         <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="AL42" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>381</v>
-      </c>
       <c r="AN42" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>21</v>
@@ -7056,10 +7047,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7082,13 +7073,13 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7139,7 +7130,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7154,13 +7145,13 @@
         <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM43" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>21</v>
@@ -7171,10 +7162,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7200,10 +7191,10 @@
         <v>104</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7254,7 +7245,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7275,7 +7266,7 @@
         <v>21</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>21</v>
@@ -7286,10 +7277,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7312,13 +7303,13 @@
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7369,7 +7360,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7384,13 +7375,13 @@
         <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM45" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>396</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>21</v>
@@ -7401,10 +7392,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7430,14 +7421,14 @@
         <v>180</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>21</v>
@@ -7486,7 +7477,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7501,13 +7492,13 @@
         <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>21</v>
@@ -7518,10 +7509,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7544,16 +7535,16 @@
         <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7579,14 +7570,14 @@
         <v>21</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Y47" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="Z47" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="Z47" t="s" s="2">
-        <v>408</v>
-      </c>
       <c r="AA47" t="s" s="2">
         <v>21</v>
       </c>
@@ -7603,7 +7594,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7624,7 +7615,7 @@
         <v>21</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>21</v>
@@ -7635,10 +7626,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7661,13 +7652,13 @@
         <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7718,7 +7709,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7733,13 +7724,13 @@
         <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM48" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>21</v>
@@ -7750,10 +7741,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7776,13 +7767,13 @@
         <v>21</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7833,7 +7824,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7848,13 +7839,13 @@
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AL49" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="AL49" t="s" s="2">
+      <c r="AM49" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>21</v>
@@ -7865,10 +7856,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7891,16 +7882,16 @@
         <v>21</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>427</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7950,7 +7941,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7965,13 +7956,13 @@
         <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM50" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>21</v>
@@ -7982,10 +7973,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8008,13 +7999,13 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8065,7 +8056,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8083,10 +8074,10 @@
         <v>21</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>21</v>
@@ -8097,10 +8088,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8123,13 +8114,13 @@
         <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8180,7 +8171,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8201,7 +8192,7 @@
         <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>21</v>
@@ -8212,10 +8203,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8241,10 +8232,10 @@
         <v>150</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>176</v>
@@ -8297,7 +8288,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8318,7 +8309,7 @@
         <v>21</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>21</v>
@@ -8329,14 +8320,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8358,10 +8349,10 @@
         <v>150</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>176</v>
@@ -8416,7 +8407,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8448,10 +8439,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8474,16 +8465,16 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8533,7 +8524,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8554,7 +8545,7 @@
         <v>21</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>21</v>
@@ -8565,10 +8556,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8591,13 +8582,13 @@
         <v>21</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8648,7 +8639,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8669,7 +8660,7 @@
         <v>21</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>21</v>
@@ -8680,10 +8671,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8709,10 +8700,10 @@
         <v>150</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>176</v>
@@ -8765,7 +8756,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8786,7 +8777,7 @@
         <v>21</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>21</v>
@@ -8797,14 +8788,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8826,10 +8817,10 @@
         <v>150</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>176</v>
@@ -8884,7 +8875,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8916,10 +8907,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8942,13 +8933,13 @@
         <v>21</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8999,7 +8990,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9020,7 +9011,7 @@
         <v>21</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>21</v>
@@ -9031,10 +9022,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9057,13 +9048,13 @@
         <v>21</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9114,7 +9105,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9135,7 +9126,7 @@
         <v>21</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>21</v>
@@ -9146,10 +9137,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9172,13 +9163,13 @@
         <v>21</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>463</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9229,7 +9220,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9250,7 +9241,7 @@
         <v>21</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>21</v>
@@ -9261,10 +9252,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9287,19 +9278,19 @@
         <v>21</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="N62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>21</v>
@@ -9348,7 +9339,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9366,10 +9357,10 @@
         <v>21</v>
       </c>
       <c r="AL62" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AM62" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>21</v>
@@ -9380,10 +9371,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9406,16 +9397,16 @@
         <v>21</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9465,7 +9456,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9483,24 +9474,24 @@
         <v>21</v>
       </c>
       <c r="AL63" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AM63" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="AM63" t="s" s="2">
+      <c r="AN63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO63" t="s" s="2">
         <v>478</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>479</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9523,13 +9514,13 @@
         <v>21</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9580,7 +9571,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9598,24 +9589,24 @@
         <v>21</v>
       </c>
       <c r="AL64" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AM64" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="AM64" t="s" s="2">
+      <c r="AN64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO64" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>485</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9638,16 +9629,16 @@
         <v>21</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9697,7 +9688,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9715,10 +9706,10 @@
         <v>21</v>
       </c>
       <c r="AL65" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AM65" t="s" s="2">
         <v>490</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>491</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>21</v>
@@ -9729,10 +9720,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9755,13 +9746,13 @@
         <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9812,7 +9803,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -9833,10 +9824,10 @@
         <v>21</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>21</v>
@@ -9844,10 +9835,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9870,13 +9861,13 @@
         <v>21</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9927,7 +9918,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -9945,10 +9936,10 @@
         <v>21</v>
       </c>
       <c r="AL67" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AM67" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>21</v>
@@ -9959,10 +9950,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9985,13 +9976,13 @@
         <v>21</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="L68" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="L68" t="s" s="2">
+      <c r="M68" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10042,7 +10033,7 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10063,7 +10054,7 @@
         <v>21</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>21</v>
@@ -10074,10 +10065,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10103,10 +10094,10 @@
         <v>150</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>176</v>
@@ -10159,7 +10150,7 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10180,7 +10171,7 @@
         <v>21</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>21</v>
@@ -10191,14 +10182,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10220,10 +10211,10 @@
         <v>150</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>176</v>
@@ -10278,7 +10269,7 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10310,10 +10301,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10336,16 +10327,16 @@
         <v>21</v>
       </c>
       <c r="K71" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="L71" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="L71" t="s" s="2">
+      <c r="M71" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>509</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10371,14 +10362,14 @@
         <v>21</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Y71" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="Z71" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="Z71" t="s" s="2">
-        <v>511</v>
-      </c>
       <c r="AA71" t="s" s="2">
         <v>21</v>
       </c>
@@ -10395,7 +10386,7 @@
         <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>90</v>
@@ -10413,24 +10404,24 @@
         <v>21</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AM71" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO71" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>513</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10453,13 +10444,13 @@
         <v>21</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10486,14 +10477,14 @@
         <v>21</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Y72" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="Z72" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="Z72" t="s" s="2">
-        <v>518</v>
-      </c>
       <c r="AA72" t="s" s="2">
         <v>21</v>
       </c>
@@ -10510,7 +10501,7 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10528,24 +10519,24 @@
         <v>21</v>
       </c>
       <c r="AL72" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="AM72" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="AM72" t="s" s="2">
+      <c r="AN72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO72" t="s" s="2">
         <v>520</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>521</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10568,13 +10559,13 @@
         <v>21</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="L73" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="L73" t="s" s="2">
+      <c r="M73" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10625,7 +10616,7 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10640,13 +10631,13 @@
         <v>102</v>
       </c>
       <c r="AK73" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="AM73" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>527</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>21</v>
@@ -10657,14 +10648,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10683,16 +10674,16 @@
         <v>21</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="L74" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="M74" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10742,7 +10733,7 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -10763,7 +10754,7 @@
         <v>21</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>21</v>
@@ -10774,10 +10765,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10800,16 +10791,16 @@
         <v>21</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="L75" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="L75" t="s" s="2">
+      <c r="M75" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>539</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10859,7 +10850,7 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -10874,13 +10865,13 @@
         <v>102</v>
       </c>
       <c r="AK75" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM75" t="s" s="2">
         <v>540</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>541</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T15:59:40+00:00</t>
+    <t>2026-02-17T17:15:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -817,27 +817,27 @@
 Reference(Patient|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)</t>
   </si>
   <si>
-    <t>TODO: Verwendung zu püfen: Kann zur Dokumentation von Fremdmedikation verwendet werden. Im Falle eines "Nachtrags" einer Medikation in den Medikationsplan
-durch einen anderen, nicht ursprünglich verordnenden Arzt. Dieser muss eindeutig identifiziert sein (im GDA-I vorhanden). Juristisch
+    <t>Reported rather than primary record</t>
+  </si>
+  <si>
+    <t>Indicates if this record was captured as a secondary 'reported' record rather than as an original primary source-of-truth record.  It may also indicate the source of the report.</t>
+  </si>
+  <si>
+    <t>closed</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=INF].role</t>
+  </si>
+  <si>
+    <t>MedicationRequest.reported[x]:reportedBoolean</t>
+  </si>
+  <si>
+    <t>reportedBoolean</t>
+  </si>
+  <si>
+    <t>TRUE im Falle der Dokumentation von Fremdmedikation (ein anderer Arzt hat das Medikament ursprünglich verordnet), sonst FALSE.
+TODO: Klären ob hier der GDA eindeutig identifiziert sein muss (im GDA-I vorhanden) oder analog zu e-Impfpass Freitext sein kann. Juristisch
 Verantwortlichkeit für Korrektheit des Eintrags zu klären.</t>
-  </si>
-  <si>
-    <t>Indicates if this record was captured as a secondary 'reported' record rather than as an original primary source-of-truth record.  It may also indicate the source of the report.</t>
-  </si>
-  <si>
-    <t>closed</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=INF].role</t>
-  </si>
-  <si>
-    <t>MedicationRequest.reported[x]:reportedBoolean</t>
-  </si>
-  <si>
-    <t>reportedBoolean</t>
-  </si>
-  <si>
-    <t>TODO: entfernen?</t>
   </si>
   <si>
     <t>MedicationRequest.reported[x]:reportedReference</t>
@@ -850,7 +850,7 @@
 </t>
   </si>
   <si>
-    <t>Im Falle einer Fremdmedikation verpflichtende Angabe einer Referen auf: (Patient | Practitioner | PractitionerRole | RelatedPerson | Organization)</t>
+    <t>Im Falle einer Fremdmedikation Angabe einer Referenz auf: (Patient | Practitioner | PractitionerRole | RelatedPerson | Organization)</t>
   </si>
   <si>
     <t>MedicationRequest.medication[x]</t>
@@ -1050,7 +1050,7 @@
 </t>
   </si>
   <si>
-    <t>Aufenthalt/Begegnung, während dessen/der der Medikationsplaneintrag erstellt wurde. Keine Verwendung im Medikationsplaneintrag.</t>
+    <t>Aufenthalt/Begegnung, während dessen der Medikationsplaneintrag erstellt wurde. Keine Verwendung im Medikationsplaneintrag.</t>
   </si>
   <si>
     <t>The Encounter during which this [x] was created or to which the creation of this record is tightly associated.</t>
@@ -1383,7 +1383,7 @@
 </t>
   </si>
   <si>
-    <t>Zusätzliche Informationen zum Medikationsplaneintrag. TODO: zu prüfen im Kontext Korrekturvermerk
+    <t>Zusätzliche Informationen zum Medikationsplaneintrag.
 TODO: fachlich prüfen, an welchen Stellen überall Freitext erforderlich sein soll/muss. Auch im Kontext zu entered-in-error
 Informationen.</t>
   </si>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>90</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$76</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2793" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2830" uniqueCount="553">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T17:15:57+00:00</t>
+    <t>2026-02-20T10:02:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -525,9 +525,7 @@
     <t>Zeitraum, in dem die Medikation eingenommen werden soll.</t>
   </si>
   <si>
-    <t>Zeitraum, über den die Medikation eingenommen werden soll. 
-Wenn mehrere dosageInstruction-Zeilen vorhanden sind (z. B. bei einer ausschleichenden Dosierung), 
-entspricht dieser Zeitraum dem frühesten Startdatum und dem spätesten Enddatum der dosageInstructions.</t>
+    <t>Zeitraum, über den die Medikation eingenommen werden soll. Wenn mehrere dosageInstruction-Zeilen vorhanden sind (z. B. bei einer ausschleichenden Dosierung), entspricht dieser Zeitraum dem frühesten Startdatum und dem spätesten Enddatum der dosageInstructions.</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -560,9 +558,7 @@
 </t>
   </si>
   <si>
-    <t>Weist darauf hin, dass der verschreibende Arzt das Medikament wissentlich für eine Indikation, 
-Altersgruppe, Dosierung oder Verabreichungsform verschrieben hat, die nicht von den Aufsichtsbehörden zugelassen ist und in der 
-Verschreibungsinformation für das Produkt nicht erwähnt wird.</t>
+    <t>Weist darauf hin, dass der verschreibende Arzt das Medikament wissentlich für eine Indikation, Altersgruppe, Dosierung oder Verabreichungsform verschrieben hat, die nicht von den Aufsichtsbehörden zugelassen ist und in der Verschreibungsinformation für das Produkt nicht erwähnt wird.</t>
   </si>
   <si>
     <t>Indicates that the prescriber has intentionally prescribed the medication in a manner not covered by the product authorization — such as for a different indication, age group, dosage, or route of administration.</t>
@@ -632,9 +628,7 @@
     <t>MedicationRequest.status</t>
   </si>
   <si>
-    <t>Status des Medikationsplaneintrags. VS Einschränkung auf active, complete, on-hold, stopped (?); TODO: Fachlich zu püfen, ob im Medikationsplan dokumentiert werden soll, dass und warum ein Medikament abgesetzt wurde (Status: stopped, z.B. bei Allergie).
-Auch im Kontext mit statusReason, wo dieser Grund codiert angegeben werden kann.
-(entfernt: cancelled, entered-in-error, draft, unknown)</t>
+    <t>Status des Medikationsplaneintrags. VS Einschränkung auf active, complete, on-hold, stopped (?); TODO: Fachlich zu püfen, ob im Medikationsplan dokumentiert werden soll, dass und warum ein Medikament abgesetzt wurde (Status: stopped, z.B. bei Allergie). Auch im Kontext mit statusReason, wo dieser Grund codiert angegeben werden kann (entfernt: cancelled, entered-in-error, draft, unknown)</t>
   </si>
   <si>
     <t>A code specifying the current state of the order.  Generally, this will be active or completed state.</t>
@@ -668,8 +662,7 @@
 </t>
   </si>
   <si>
-    <t>Grund für den aktuellen Status des Medikationsplaneintrags: (ex) https://hl7.org/fhir/R4/valueset-medicationrequest-status-reason.html.
-TODO: Verwendung fachlich zu prüfen im Zusammenhang mit Status.</t>
+    <t>Grund für den aktuellen Status des Medikationsplaneintrags: (ex) https://hl7.org/fhir/R4/valueset-medicationrequest-status-reason.html. TODO: Verwendung fachlich zu prüfen im Zusammenhang mit Status.</t>
   </si>
   <si>
     <t>Captures the reason for the current state of the MedicationRequest.</t>
@@ -696,9 +689,7 @@
     <t>MedicationRequest.intent</t>
   </si>
   <si>
-    <t>Ein Medikationsplaneintrag ist eine autorisierte ärztliche Anordnung und stellt eine verbindliche Einnahmeanweisung für den Patienten dar, auf dessen Basis eine geplante Abgabe erstellt werden kann. Fixer Wert: "order".
-(req) proposal | plan | order | original-order | reflex-order | filler-order | instance-order | option. 
-https://hl7.org/fhir/R4/valueset-medicationrequest-intent.html</t>
+    <t>Ein Medikationsplaneintrag ist eine autorisierte ärztliche Anordnung und stellt eine verbindliche Einnahmeanweisung für den Patienten dar, auf dessen Basis eine geplante Abgabe erstellt werden kann. Fixer Wert: "order". (req) proposal | plan | order | original-order | reflex-order | filler-order | instance-order | option. https://hl7.org/fhir/R4/valueset-medicationrequest-intent.html</t>
   </si>
   <si>
     <t>Whether the request is a proposal, plan, or an original order.</t>
@@ -796,9 +787,7 @@
 </t>
   </si>
   <si>
-    <t>Gibt an, ob der Medikationsplaneintrag die Verordnung einer Medikation 
-(und somit die Erstellung einer geplanten Abgabe) untersagt (z.B. bei Allergie). TODO: Fachlich zu prüfen, ob dieser Usecase existiert.
-Auch im Kontext mit status und statusReason zu betrachten. Evtl. erst in späterer Version</t>
+    <t>Gibt an, ob der Medikationsplaneintrag die Verordnung einer Medikation (und somit die Erstellung einer geplanten Abgabe) untersagt (z.B. bei Allergie). TODO: Fachlich zu prüfen, ob dieser Usecase existiert. Auch im Kontext mit status und statusReason zu betrachten. Evtl. erst in späterer Version</t>
   </si>
   <si>
     <t>If true indicates that the provider is asking for the medication request not to occur.</t>
@@ -829,45 +818,48 @@
     <t>.participation[typeCode=INF].role</t>
   </si>
   <si>
+    <t>MedicationRequest.reported[x]:reportedReference</t>
+  </si>
+  <si>
+    <t>reportedReference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Patient|Practitioner|PractitionerRole)
+</t>
+  </si>
+  <si>
+    <t>Im Falle einer Fremdmedikation Angabe einer Referenz auf: (Patient | Practitioner | PractitionerRole | RelatedPerson | Organization)</t>
+  </si>
+  <si>
     <t>MedicationRequest.reported[x]:reportedBoolean</t>
   </si>
   <si>
     <t>reportedBoolean</t>
   </si>
   <si>
-    <t>TRUE im Falle der Dokumentation von Fremdmedikation (ein anderer Arzt hat das Medikament ursprünglich verordnet), sonst FALSE.
-TODO: Klären ob hier der GDA eindeutig identifiziert sein muss (im GDA-I vorhanden) oder analog zu e-Impfpass Freitext sein kann. Juristisch
-Verantwortlichkeit für Korrektheit des Eintrags zu klären.</t>
-  </si>
-  <si>
-    <t>MedicationRequest.reported[x]:reportedReference</t>
-  </si>
-  <si>
-    <t>reportedReference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Patient|Practitioner|PractitionerRole|RelatedPerson|Organization)
+    <t>TRUE im Falle der Dokumentation von Fremdmedikation (ein anderer Arzt hat das Medikament ursprünglich verordnet), sonst FALSE. TODO: Klären ob hier der GDA eindeutig identifiziert sein muss (im GDA-I vorhanden) oder analog zu e-Impfpass Freitext sein kann. Juristisch Verantwortlichkeit für Korrektheit des Eintrags zu klären.</t>
+  </si>
+  <si>
+    <t>MedicationRequest.medication[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Medication|4.0.1)
 </t>
   </si>
   <si>
-    <t>Im Falle einer Fremdmedikation Angabe einer Referenz auf: (Patient | Practitioner | PractitionerRole | RelatedPerson | Organization)</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-emed-medication)
-</t>
-  </si>
-  <si>
-    <t>Das Arzneimittel wird immer in einer contained Medication Ressource dokumentiert, damit 
-Arzneimittel mit und ohne PZN einheitlich dokumentiert werden können.</t>
+    <t>Medication to be taken</t>
   </si>
   <si>
     <t>Identifies the medication being requested. This is a link to a resource that represents the medication which may be the details of the medication or simply an attribute carrying a code that identifies the medication from a known list of medications.</t>
   </si>
   <si>
     <t>If only a code is specified, then it needs to be a code for a specific product. If more information is required, then the use of the Medication resource is recommended.  For example, if you require form or lot number or if the medication is compounded or extemporaneously prepared, then you must reference the Medication resource.</t>
+  </si>
+  <si>
+    <t>A coded concept identifying substance or product that can be ordered.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/medication-codes|4.0.1</t>
   </si>
   <si>
     <t>Request.code</t>
@@ -891,6 +883,22 @@
     <t>RXE-2-Give Code / RXO-1-Requested Give Code / RXC-2-Component Code</t>
   </si>
   <si>
+    <t>MedicationRequest.medication[x]:medicationReference</t>
+  </si>
+  <si>
+    <t>medicationReference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-emed-medication)
+</t>
+  </si>
+  <si>
+    <t>Das Arzneimittel wird immer in einer contained Medication Ressource dokumentiert, damit Arzneimittel mit und ohne PZN einheitlich dokumentiert werden können.</t>
+  </si>
+  <si>
+    <t>MedicationRequest.medication[x]:medicationReference.id</t>
+  </si>
+  <si>
     <t>MedicationRequest.medication[x].id</t>
   </si>
   <si>
@@ -910,6 +918,9 @@
     <t>n/a</t>
   </si>
   <si>
+    <t>MedicationRequest.medication[x]:medicationReference.extension</t>
+  </si>
+  <si>
     <t>MedicationRequest.medication[x].extension</t>
   </si>
   <si>
@@ -923,6 +934,9 @@
   </si>
   <si>
     <t>Element.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.medication[x]:medicationReference.reference</t>
   </si>
   <si>
     <t>MedicationRequest.medication[x].reference</t>
@@ -945,7 +959,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-contained-ref:Medication must be contained (#...) {reference.startsWith('#')}</t>
+contained-ref:Medication must be contained (#...) {$this.startsWith('#')}</t>
+  </si>
+  <si>
+    <t>MedicationRequest.medication[x]:medicationReference.type</t>
   </si>
   <si>
     <t>MedicationRequest.medication[x].type</t>
@@ -971,6 +988,9 @@
   </si>
   <si>
     <t>Reference.type</t>
+  </si>
+  <si>
+    <t>MedicationRequest.medication[x]:medicationReference.identifier</t>
   </si>
   <si>
     <t>MedicationRequest.medication[x].identifier</t>
@@ -994,6 +1014,9 @@
     <t>.identifier</t>
   </si>
   <si>
+    <t>MedicationRequest.medication[x]:medicationReference.display</t>
+  </si>
+  <si>
     <t>MedicationRequest.medication[x].display</t>
   </si>
   <si>
@@ -1016,8 +1039,7 @@
 </t>
   </si>
   <si>
-    <t>Patient, für den der Medikationsplaneintrag ausgestellt werden soll, der über den 
-Zentralen Patientenindex identifizierbar und Teilnehmer von ELGA e-Medikation ist.</t>
+    <t>Patient, für den der Medikationsplaneintrag ausgestellt werden soll, der über den Zentralen Patientenindex identifizierbar und Teilnehmer von ELGA e-Medikation ist.</t>
   </si>
   <si>
     <t>A link to a resource representing the person or set of individuals to whom the medication will be given.</t>
@@ -1078,9 +1100,7 @@
 </t>
   </si>
   <si>
-    <t>Referenz auf zusätzliche Informationen (Ressource Any)
-(z. B. Größe und Gewicht des Patienten), die die Verschreibung des Medikaments unterstützen. 
-Keine Verwendung im Medikationsplaneintrag.</t>
+    <t>Referenz auf zusätzliche Informationen (Ressource Any) (z. B. Größe und Gewicht des Patienten), die die Verschreibung des Medikaments unterstützen. Keine Verwendung im Medikationsplaneintrag.</t>
   </si>
   <si>
     <t>Include additional information (for example, patient height and weight) that supports the ordering of the medication.</t>
@@ -1127,9 +1147,7 @@
 </t>
   </si>
   <si>
-    <t>Arzt oder Ärztin, die den Medikationsplaneintrag erstellt hat
-und für den Inhalt verantwortlich ist. Eindeutig identifiziert über den GDA-Index und berechtigt auf die ELGA e-Medikation 
-des Patienten zuzugreifen.</t>
+    <t>Arzt oder Ärztin, die den Medikationsplaneintrag erstellt hat und für den Inhalt verantwortlich ist. Eindeutig identifiziert über den GDA-Index und berechtigt auf die ELGA e-Medikation des Patienten zuzugreifen.</t>
   </si>
   <si>
     <t>The individual, organization, or device that initiated the request and has responsibility for its activation.</t>
@@ -1148,8 +1166,7 @@
 </t>
   </si>
   <si>
-    <t>Der gewünschte Ausführende der medikamentösen Behandlung 
-(z. B. der Ausführende der Medikamentengabe). Keine Verwendung im Planeintrag. TODO: evtl im Kontext Medikationsblatt zu prüfen.</t>
+    <t>Der gewünschte Ausführende der medikamentösen Behandlung (z.B. der Ausführende der Medikamentengabe). Keine Verwendung im Planeintrag. TODO: evtl im Kontext Medikationsblatt zu prüfen.</t>
   </si>
   <si>
     <t>The specified desired performer of the medication treatment (e.g. the performer of the medication administration).</t>
@@ -1167,8 +1184,7 @@
     <t>MedicationRequest.performerType</t>
   </si>
   <si>
-    <t>Rollen: https://hl7.org/fhir/R4/valueset-performer-role.html. 
-Keine Verwendung im Planeintrag. TODO: evtl im Kontext Medikationsblatt zu prüfen.</t>
+    <t>Rollen: https://hl7.org/fhir/R4/valueset-performer-role.html. Keine Verwendung im Planeintrag. TODO: evtl im Kontext Medikationsblatt zu prüfen.</t>
   </si>
   <si>
     <t>Indicates the type of performer of the administration of the medication.</t>
@@ -1196,8 +1212,7 @@
 </t>
   </si>
   <si>
-    <t>Die Person, die den Medikationsplaneintrag im Auftrag eines GDA eingegeben hat. 
-TODO: Prüfen, ob eine juristische Verpflichtung zur Dokumentation der Schreibkraft besteht.</t>
+    <t>Die Person, die den Medikationsplaneintrag im Auftrag eines GDA eingegeben hat. TODO: Prüfen, ob eine juristische Verpflichtung zur Dokumentation der Schreibkraft besteht.</t>
   </si>
   <si>
     <t>The person who entered the order on behalf of another individual for example in the case of a verbal or a telephone order.</t>
@@ -1212,8 +1227,7 @@
     <t>MedicationRequest.reasonCode</t>
   </si>
   <si>
-    <t>Grund für die Verordnung des Arzneimittels. 
-Entweder Code oder Referenz (TODO: Evtl. Invariante). Erst wenn codierte Angabe möglich.</t>
+    <t>Grund für die Verordnung des Arzneimittels. Entweder Code oder Referenz (TODO: Evtl. Invariante). Erst wenn codierte Angabe möglich.</t>
   </si>
   <si>
     <t>The reason or the indication for ordering or not ordering the medication.</t>
@@ -1272,8 +1286,7 @@
 </t>
   </si>
   <si>
-    <t>URL, die auf ein Protokoll (Richtlinie, Guideline) verweist, das von diesem 
-Medikationsplaneintrag ganz oder teilweise eingehalten wird. Derzeit keine Verwendung im Medikationsplaneintrag.</t>
+    <t>URL, die auf ein Protokoll (Richtlinie, Guideline) verweist, das von diesem Medikationsplaneintrag ganz oder teilweise eingehalten wird. Derzeit keine Verwendung im Medikationsplaneintrag.</t>
   </si>
   <si>
     <t>The URL pointing to a protocol, guideline, orderset, or other definition that is adhered to in whole or in part by this MedicationRequest.</t>
@@ -1288,8 +1301,7 @@
     <t>MedicationRequest.instantiatesUri</t>
   </si>
   <si>
-    <t>URL, die auf ein extern gepflegtes Protokoll (Richtlinie, Guideline) verweist, das von diesem 
-Medikationsplaneintrag ganz oder teilweise eingehalten wird. Derzeit keine Verwendung im Medikationsplaneintrag.</t>
+    <t>URL, die auf ein extern gepflegtes Protokoll (Richtlinie, Guideline) verweist, das von diesem Medikationsplaneintrag ganz oder teilweise eingehalten wird. Derzeit keine Verwendung im Medikationsplaneintrag.</t>
   </si>
   <si>
     <t>The URL pointing to an externally maintained protocol, guideline, orderset or other definition that is adhered to in whole or in part by this MedicationRequest.</t>
@@ -1302,8 +1314,7 @@
 </t>
   </si>
   <si>
-    <t>TODO: Verwendung im Medikationsplaneintrag zu prüfen. Vermutlich nicht möglich, 
-da keine versionsspezifischen Referenzen verwendet werden.</t>
+    <t>TODO: Verwendung im Medikationsplaneintrag zu prüfen. Vermutlich nicht möglich, da keine versionsspezifischen Referenzen verwendet werden.</t>
   </si>
   <si>
     <t>A plan or request that is fulfilled in whole or in part by this medication request.</t>
@@ -1318,9 +1329,7 @@
     <t>MedicationRequest.groupIdentifier</t>
   </si>
   <si>
-    <t>TODO: Verwendung im Medikationsplaneintrag zu prüfen. 
-Erst bei der geplanten Abgabe (Rezepterstellung) relevant. Evtl ein Verweis auf erstellte Rezepte?
-Würde Extension erfordern, da Kardinalität nur 0..1 zulässig</t>
+    <t>TODO: Verwendung im Medikationsplaneintrag zu prüfen. Erst bei der geplanten Abgabe (Rezepterstellung) relevant. Evtl ein Verweis auf erstellte Rezepte? Würde Extension erfordern, da Kardinalität nur 0..1 zulässig</t>
   </si>
   <si>
     <t>A shared identifier common to all requests that were authorized more or less simultaneously by a single author, representing the identifier of the requisition or prescription.</t>
@@ -1338,8 +1347,7 @@
     <t>MedicationRequest.courseOfTherapyType</t>
   </si>
   <si>
-    <t>Gesamtmuster der Medikamentengabe (z.B. saisonal). 
-Verwendung im Medikationsplaneintrag prüfen (dosageInstruction), evtl. durch Dosierungsinformationen abgedeck.</t>
+    <t>Gesamtmuster der Medikamentengabe (z.B. saisonal). Verwendung im Medikationsplaneintrag prüfen (dosageInstruction), evtl. durch Dosierungsinformationen abgedeck.</t>
   </si>
   <si>
     <t>The description of the overall patte3rn of the administration of the medication to the patient.</t>
@@ -1383,9 +1391,7 @@
 </t>
   </si>
   <si>
-    <t>Zusätzliche Informationen zum Medikationsplaneintrag.
-TODO: fachlich prüfen, an welchen Stellen überall Freitext erforderlich sein soll/muss. Auch im Kontext zu entered-in-error
-Informationen.</t>
+    <t>Zusätzliche Informationen zum Medikationsplaneintrag. TODO: fachlich prüfen, an welchen Stellen überall Freitext erforderlich sein soll/muss. Auch im Kontext zu entered-in-error Informationen.</t>
   </si>
   <si>
     <t>Extra information about the prescription that could not be conveyed by the other attributes.</t>
@@ -1429,8 +1435,7 @@
 </t>
   </si>
   <si>
-    <t>Details zur geplanten Abgabe des Arzneimittels im Medikationsplan.
-Keine Verwendung im Medikationsplaneintrag.</t>
+    <t>Details zur geplanten Abgabe des Arzneimittels im Medikationsplan. Keine Verwendung im Medikationsplaneintrag.</t>
   </si>
   <si>
     <t>Indicates the specific details for the dispense or medication supply part of a medication request (also known as a Medication Prescription or Medication Order).  Note that this information is not always sent with the order.  There may be in some settings (e.g. hospitals) institutional or system support for completing the dispense details in the pharmacy department.</t>
@@ -1635,12 +1640,7 @@
     <t>MedicationRequest.substitution</t>
   </si>
   <si>
-    <t>Gibt an, ob das Arzneimittel substituiert werden darf oder nicht. 
-Erläutert die Absicht des Arztes, der den Medikationsplaneintrag erstellt. 
-Wenn nichts angegeben ist, kann eine Substitution vorgenommen werden. 
-Die Dokumentation über eine tatsächlich erfolgte Substitution erfolgt in der Dispense-Resource. 
-TODO: Usecase fachlich zu prüfen. Es kann für den Patienten selbst oder das Pflegeheim eine wichtige Information sein,
-mit welchem Medikament das verordnete Medikament im Bedarfsfall ersetzen werden kann.</t>
+    <t>Gibt an, ob das Arzneimittel substituiert werden darf oder nicht. Erläutert die Absicht des Arztes, der den Medikationsplaneintrag erstellt. Wenn nichts angegeben ist, kann eine Substitution vorgenommen werden. Die Dokumentation über eine tatsächlich erfolgte Substitution erfolgt in der Dispense-Resource. TODO: Usecase fachlich zu prüfen. Es kann für den Patienten selbst oder das Pflegeheim eine wichtige Information sein, mit welchem Medikament das verordnete Medikament im Bedarfsfall ersetzen werden kann.</t>
   </si>
   <si>
     <t>Indicates whether or not substitution can or should be part of the dispense. In some cases, substitution must happen, in other cases substitution must not happen. This block explains the prescriber's intent. If nothing is specified substitution may be done.</t>
@@ -1720,8 +1720,7 @@
 </t>
   </si>
   <si>
-    <t>Im Falle einer Änderung wird auf den ersetzten 
-Medikationsplaneintrag verwiesen.</t>
+    <t>Im Falle einer Änderung wird auf den ersetzten Medikationsplaneintrag verwiesen.</t>
   </si>
   <si>
     <t>A link to a resource representing an earlier order related order or prescription.</t>
@@ -1744,8 +1743,7 @@
 </t>
   </si>
   <si>
-    <t>Klinisches Problem mit Maßnahme. Nur mittesl Referenz auf Ressouce DetectedIssue, 
-Keine Verwendung im Medikationsplaneintrag.</t>
+    <t>Klinisches Problem mit Maßnahme. Nur mittesl Referenz auf Ressouce DetectedIssue, Keine Verwendung im Medikationsplaneintrag.</t>
   </si>
   <si>
     <t>Indicates an actual or potential clinical issue with or between one or more active or proposed clinical actions for a patient; e.g. Drug-drug interaction, duplicate therapy, dosage alert etc.</t>
@@ -1764,8 +1762,7 @@
 </t>
   </si>
   <si>
-    <t>Referenz auf Provenance-Ressourcen, die verschiedene relevante Versionen dieser Ressource dokumentieren. 
-Keine Verwendung im Medikationsplaneintrag.</t>
+    <t>Referenz auf Provenance-Ressourcen, die verschiedene relevante Versionen dieser Ressource dokumentieren. Keine Verwendung im Medikationsplaneintrag.</t>
   </si>
   <si>
     <t>Links to Provenance records for past versions of this resource or fulfilling request or event resources that identify key state transitions or updates that are likely to be relevant to a user looking at the current version of the resource.</t>
@@ -2102,10 +2099,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO75"/>
+  <dimension ref="A1:AO76"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="51.68359375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="52.8828125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="51.68359375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="22.41015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
@@ -4864,10 +4861,10 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M24" t="s" s="2">
         <v>245</v>
@@ -4953,13 +4950,13 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B25" t="s" s="2">
         <v>242</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D25" t="s" s="2">
         <v>21</v>
@@ -4981,7 +4978,7 @@
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>254</v>
@@ -5068,7 +5065,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
         <v>255</v>
       </c>
@@ -5131,28 +5128,26 @@
         <v>21</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>21</v>
+        <v>260</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>21</v>
+        <v>261</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AC26" s="2"/>
       <c r="AD26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>21</v>
+        <v>246</v>
       </c>
       <c r="AF26" t="s" s="2">
         <v>255</v>
@@ -5170,58 +5165,62 @@
         <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="C27" s="2"/>
+        <v>255</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>268</v>
+      </c>
       <c r="D27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>21</v>
@@ -5270,10 +5269,10 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>269</v>
+        <v>255</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>90</v>
@@ -5282,22 +5281,22 @@
         <v>21</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>21</v>
+        <v>262</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>21</v>
+        <v>263</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>21</v>
+        <v>265</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>21</v>
+        <v>266</v>
       </c>
     </row>
     <row r="28" hidden="true">
@@ -5305,18 +5304,18 @@
         <v>271</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>21</v>
@@ -5328,17 +5327,15 @@
         <v>21</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>150</v>
+        <v>273</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>176</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>21</v>
@@ -5375,31 +5372,31 @@
         <v>21</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>274</v>
+        <v>21</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>155</v>
+        <v>21</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>21</v>
@@ -5408,7 +5405,7 @@
         <v>21</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>21</v>
@@ -5419,21 +5416,21 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>21</v>
+        <v>173</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>21</v>
@@ -5442,19 +5439,19 @@
         <v>21</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>266</v>
+        <v>150</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>279</v>
+        <v>176</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5492,31 +5489,31 @@
         <v>21</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>21</v>
+        <v>153</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>21</v>
+        <v>282</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>21</v>
+        <v>133</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>281</v>
+        <v>21</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>282</v>
+        <v>155</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>21</v>
@@ -5525,7 +5522,7 @@
         <v>21</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>135</v>
+        <v>277</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>21</v>
@@ -5536,10 +5533,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5562,16 +5559,16 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>104</v>
+        <v>273</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5597,31 +5594,31 @@
         <v>21</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>287</v>
+        <v>21</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>288</v>
+        <v>21</v>
       </c>
       <c r="Z30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF30" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5630,10 +5627,10 @@
         <v>90</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>21</v>
+        <v>290</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>102</v>
+        <v>291</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>21</v>
@@ -5653,10 +5650,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5679,16 +5676,16 @@
         <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>180</v>
+        <v>104</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5714,13 +5711,13 @@
         <v>21</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>21</v>
+        <v>297</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>21</v>
+        <v>298</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>21</v>
+        <v>299</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>21</v>
@@ -5738,7 +5735,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5759,7 +5756,7 @@
         <v>21</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>296</v>
+        <v>135</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>21</v>
@@ -5770,10 +5767,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5796,16 +5793,16 @@
         <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>266</v>
+        <v>180</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5855,7 +5852,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5876,7 +5873,7 @@
         <v>21</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>135</v>
+        <v>307</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>21</v>
@@ -5885,12 +5882,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5898,13 +5895,13 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>21</v>
@@ -5913,16 +5910,16 @@
         <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>303</v>
+        <v>273</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5972,10 +5969,10 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>90</v>
@@ -5987,27 +5984,27 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>307</v>
+        <v>21</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>308</v>
+        <v>21</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>309</v>
+        <v>135</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>310</v>
+        <v>21</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>311</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6015,31 +6012,31 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6089,10 +6086,10 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>90</v>
@@ -6104,27 +6101,27 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>196</v>
+        <v>320</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6147,15 +6144,17 @@
         <v>21</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>327</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>328</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>21</v>
@@ -6204,13 +6203,13 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>21</v>
@@ -6219,27 +6218,27 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>21</v>
+        <v>196</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>21</v>
+        <v>332</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6247,28 +6246,28 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6319,13 +6318,13 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>21</v>
@@ -6334,27 +6333,27 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="AL36" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>334</v>
-      </c>
       <c r="AO36" t="s" s="2">
-        <v>335</v>
+        <v>21</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6377,13 +6376,13 @@
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6434,7 +6433,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6449,27 +6448,27 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>21</v>
+        <v>344</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>309</v>
+        <v>345</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>21</v>
+        <v>347</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6477,28 +6476,28 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6549,7 +6548,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6564,16 +6563,16 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>347</v>
+        <v>321</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>21</v>
@@ -6581,10 +6580,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6604,20 +6603,18 @@
         <v>21</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>200</v>
+        <v>355</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>352</v>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>21</v>
@@ -6642,31 +6639,31 @@
         <v>21</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>204</v>
+        <v>21</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>353</v>
+        <v>21</v>
       </c>
       <c r="Z39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF39" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="AA39" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF39" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6681,16 +6678,16 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>21</v>
+        <v>360</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>21</v>
@@ -6698,10 +6695,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6721,18 +6718,20 @@
         <v>21</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>358</v>
+        <v>200</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>363</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>364</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>21</v>
@@ -6757,13 +6756,13 @@
         <v>21</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>21</v>
+        <v>365</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>21</v>
+        <v>366</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>21</v>
@@ -6781,7 +6780,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6796,16 +6795,16 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>21</v>
+        <v>367</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>362</v>
+        <v>21</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>21</v>
@@ -6813,10 +6812,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6839,17 +6838,15 @@
         <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>200</v>
+        <v>370</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>366</v>
-      </c>
+        <v>372</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>21</v>
@@ -6874,13 +6871,13 @@
         <v>21</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>204</v>
+        <v>21</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>367</v>
+        <v>21</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>368</v>
+        <v>21</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>21</v>
@@ -6898,13 +6895,13 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>21</v>
@@ -6913,27 +6910,27 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>369</v>
+        <v>21</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>370</v>
+        <v>21</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>373</v>
+        <v>21</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6956,7 +6953,7 @@
         <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>375</v>
+        <v>200</v>
       </c>
       <c r="L42" t="s" s="2">
         <v>376</v>
@@ -6991,13 +6988,13 @@
         <v>21</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>21</v>
+        <v>379</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>21</v>
+        <v>380</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>21</v>
@@ -7015,7 +7012,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7030,27 +7027,27 @@
         <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>196</v>
+        <v>382</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>21</v>
+        <v>385</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7070,18 +7067,20 @@
         <v>21</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>389</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>390</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>21</v>
@@ -7130,7 +7129,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7145,16 +7144,16 @@
         <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>21</v>
+        <v>196</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>21</v>
+        <v>384</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>21</v>
@@ -7162,10 +7161,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7188,13 +7187,13 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>104</v>
+        <v>394</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7245,7 +7244,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7260,13 +7259,13 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>21</v>
+        <v>397</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>21</v>
@@ -7277,10 +7276,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7303,13 +7302,13 @@
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>391</v>
+        <v>104</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7360,7 +7359,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7375,13 +7374,13 @@
         <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>394</v>
+        <v>21</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>21</v>
@@ -7392,10 +7391,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7418,18 +7417,16 @@
         <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>180</v>
+        <v>403</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="N46" s="2"/>
-      <c r="O46" t="s" s="2">
-        <v>399</v>
-      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>21</v>
       </c>
@@ -7477,13 +7474,13 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>21</v>
@@ -7492,13 +7489,13 @@
         <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>21</v>
@@ -7507,12 +7504,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7523,30 +7520,30 @@
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J47" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J47" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K47" t="s" s="2">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>410</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" t="s" s="2">
+        <v>411</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>21</v>
       </c>
@@ -7570,13 +7567,13 @@
         <v>21</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>204</v>
+        <v>21</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>406</v>
+        <v>21</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>407</v>
+        <v>21</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>21</v>
@@ -7594,7 +7591,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7609,13 +7606,13 @@
         <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>21</v>
+        <v>412</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>21</v>
@@ -7624,12 +7621,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7640,10 +7637,10 @@
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>21</v>
@@ -7652,15 +7649,17 @@
         <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>410</v>
+        <v>200</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>416</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>417</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>21</v>
@@ -7685,13 +7684,13 @@
         <v>21</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>21</v>
+        <v>418</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>21</v>
+        <v>419</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>21</v>
@@ -7709,13 +7708,13 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>21</v>
@@ -7724,13 +7723,13 @@
         <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>413</v>
+        <v>21</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>21</v>
@@ -7739,12 +7738,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7755,10 +7754,10 @@
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>21</v>
@@ -7767,13 +7766,13 @@
         <v>21</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7824,7 +7823,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7839,13 +7838,13 @@
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>420</v>
+        <v>21</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>21</v>
@@ -7856,10 +7855,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7867,7 +7866,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>81</v>
@@ -7882,17 +7881,15 @@
         <v>21</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>426</v>
-      </c>
+        <v>430</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>21</v>
@@ -7941,7 +7938,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7956,13 +7953,13 @@
         <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>21</v>
+        <v>432</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>21</v>
@@ -7971,12 +7968,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7984,13 +7981,13 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>21</v>
@@ -7999,15 +7996,17 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>437</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>438</v>
+      </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>21</v>
@@ -8056,13 +8055,13 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>21</v>
@@ -8071,13 +8070,13 @@
         <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>21</v>
+        <v>439</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>433</v>
+        <v>21</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>21</v>
@@ -8088,10 +8087,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8102,7 +8101,7 @@
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>21</v>
@@ -8114,13 +8113,13 @@
         <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>266</v>
+        <v>442</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>267</v>
+        <v>443</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>268</v>
+        <v>444</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8171,7 +8170,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>269</v>
+        <v>441</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8183,16 +8182,16 @@
         <v>21</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>21</v>
+        <v>445</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>270</v>
+        <v>446</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>21</v>
@@ -8203,21 +8202,21 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>436</v>
+        <v>447</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>436</v>
+        <v>447</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>21</v>
@@ -8229,17 +8228,15 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>150</v>
+        <v>273</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>176</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>21</v>
@@ -8288,19 +8285,19 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>155</v>
+        <v>21</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>21</v>
@@ -8309,7 +8306,7 @@
         <v>21</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>21</v>
@@ -8320,14 +8317,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>438</v>
+        <v>173</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8340,26 +8337,24 @@
         <v>21</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
         <v>150</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>439</v>
+        <v>280</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>440</v>
+        <v>281</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="O54" t="s" s="2">
-        <v>177</v>
-      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>21</v>
       </c>
@@ -8407,7 +8402,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>441</v>
+        <v>283</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8428,7 +8423,7 @@
         <v>21</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>135</v>
+        <v>277</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>21</v>
@@ -8439,44 +8434,46 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>21</v>
+        <v>450</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>430</v>
+        <v>150</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="O55" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>21</v>
       </c>
@@ -8524,19 +8521,19 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>442</v>
+        <v>453</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>102</v>
+        <v>155</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>21</v>
@@ -8545,7 +8542,7 @@
         <v>21</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>446</v>
+        <v>135</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>21</v>
@@ -8556,10 +8553,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8582,15 +8579,17 @@
         <v>21</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>266</v>
+        <v>442</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>267</v>
+        <v>455</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>456</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>457</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>21</v>
@@ -8639,7 +8638,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>269</v>
+        <v>454</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8651,7 +8650,7 @@
         <v>21</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>21</v>
@@ -8660,7 +8659,7 @@
         <v>21</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>270</v>
+        <v>458</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>21</v>
@@ -8671,21 +8670,21 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>448</v>
+        <v>459</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>448</v>
+        <v>459</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>21</v>
@@ -8697,17 +8696,15 @@
         <v>21</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>150</v>
+        <v>273</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>176</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>21</v>
@@ -8756,19 +8753,19 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>155</v>
+        <v>21</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>21</v>
@@ -8777,7 +8774,7 @@
         <v>21</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>21</v>
@@ -8788,14 +8785,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>449</v>
+        <v>460</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>449</v>
+        <v>460</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>438</v>
+        <v>173</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8808,26 +8805,24 @@
         <v>21</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K58" t="s" s="2">
         <v>150</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>439</v>
+        <v>280</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>440</v>
+        <v>281</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="O58" t="s" s="2">
-        <v>177</v>
-      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>21</v>
       </c>
@@ -8875,7 +8870,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>441</v>
+        <v>283</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8896,7 +8891,7 @@
         <v>21</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>135</v>
+        <v>277</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>21</v>
@@ -8907,42 +8902,46 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>21</v>
+        <v>450</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="M59" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+      <c r="N59" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>21</v>
       </c>
@@ -8990,19 +8989,19 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>102</v>
+        <v>155</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>21</v>
@@ -9011,7 +9010,7 @@
         <v>21</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>454</v>
+        <v>135</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>21</v>
@@ -9022,10 +9021,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9048,13 +9047,13 @@
         <v>21</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9105,7 +9104,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9126,7 +9125,7 @@
         <v>21</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>21</v>
@@ -9137,10 +9136,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9163,13 +9162,13 @@
         <v>21</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9220,7 +9219,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9241,7 +9240,7 @@
         <v>21</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>459</v>
+        <v>471</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>21</v>
@@ -9252,10 +9251,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9278,20 +9277,16 @@
         <v>21</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>468</v>
-      </c>
+        <v>474</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>21</v>
       </c>
@@ -9339,7 +9334,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9357,10 +9352,10 @@
         <v>21</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>469</v>
+        <v>21</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>21</v>
@@ -9371,10 +9366,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9397,18 +9392,20 @@
         <v>21</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="O63" s="2"/>
+        <v>479</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>480</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>21</v>
       </c>
@@ -9456,7 +9453,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9474,24 +9471,24 @@
         <v>21</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>478</v>
+        <v>21</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9514,15 +9511,17 @@
         <v>21</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>451</v>
+        <v>484</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>486</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>487</v>
+      </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>21</v>
@@ -9571,7 +9570,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9589,24 +9588,24 @@
         <v>21</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9629,17 +9628,15 @@
         <v>21</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>488</v>
-      </c>
+        <v>493</v>
+      </c>
+      <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>21</v>
@@ -9688,7 +9685,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9706,24 +9703,24 @@
         <v>21</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>21</v>
+        <v>496</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9746,15 +9743,17 @@
         <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>492</v>
+        <v>468</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>499</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>500</v>
+      </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>21</v>
@@ -9803,7 +9802,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -9821,24 +9820,24 @@
         <v>21</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>21</v>
+        <v>501</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>362</v>
+        <v>21</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9852,7 +9851,7 @@
         <v>90</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>21</v>
@@ -9861,13 +9860,13 @@
         <v>21</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>430</v>
+        <v>504</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9918,7 +9917,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -9936,24 +9935,24 @@
         <v>21</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>499</v>
+        <v>21</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>500</v>
+        <v>507</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>21</v>
+        <v>374</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9967,7 +9966,7 @@
         <v>90</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>21</v>
@@ -9976,13 +9975,13 @@
         <v>21</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>266</v>
+        <v>442</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>267</v>
+        <v>509</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>268</v>
+        <v>510</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10033,7 +10032,7 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>269</v>
+        <v>508</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10045,16 +10044,16 @@
         <v>21</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>21</v>
+        <v>511</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>270</v>
+        <v>512</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>21</v>
@@ -10065,21 +10064,21 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>21</v>
@@ -10091,17 +10090,15 @@
         <v>21</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>150</v>
+        <v>273</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>176</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>21</v>
@@ -10150,19 +10147,19 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>155</v>
+        <v>21</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>21</v>
@@ -10171,7 +10168,7 @@
         <v>21</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>21</v>
@@ -10182,14 +10179,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>503</v>
+        <v>514</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>503</v>
+        <v>514</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>438</v>
+        <v>173</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10202,26 +10199,24 @@
         <v>21</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K70" t="s" s="2">
         <v>150</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>439</v>
+        <v>280</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>440</v>
+        <v>281</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="O70" t="s" s="2">
-        <v>177</v>
-      </c>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>21</v>
       </c>
@@ -10269,7 +10264,7 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>441</v>
+        <v>283</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10290,7 +10285,7 @@
         <v>21</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>135</v>
+        <v>277</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>21</v>
@@ -10301,44 +10296,46 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>504</v>
+        <v>515</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>504</v>
+        <v>515</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>21</v>
+        <v>450</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>505</v>
+        <v>150</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>506</v>
+        <v>451</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>507</v>
+        <v>452</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="O71" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>21</v>
       </c>
@@ -10362,13 +10359,13 @@
         <v>21</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>204</v>
+        <v>21</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>509</v>
+        <v>21</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>510</v>
+        <v>21</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>21</v>
@@ -10386,42 +10383,42 @@
         <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>504</v>
+        <v>453</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>102</v>
+        <v>155</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>499</v>
+        <v>21</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>511</v>
+        <v>135</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>512</v>
+        <v>21</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10429,7 +10426,7 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G72" t="s" s="2">
         <v>90</v>
@@ -10444,15 +10441,17 @@
         <v>21</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>200</v>
+        <v>517</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>519</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>520</v>
+      </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>21</v>
@@ -10480,31 +10479,31 @@
         <v>204</v>
       </c>
       <c r="Y72" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF72" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="Z72" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>513</v>
-      </c>
       <c r="AG72" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH72" t="s" s="2">
         <v>90</v>
@@ -10519,24 +10518,24 @@
         <v>21</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10550,7 +10549,7 @@
         <v>90</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>21</v>
@@ -10559,13 +10558,13 @@
         <v>21</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>522</v>
+        <v>200</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10592,13 +10591,13 @@
         <v>21</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>21</v>
+        <v>528</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>21</v>
+        <v>529</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>21</v>
@@ -10616,7 +10615,7 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10631,41 +10630,41 @@
         <v>102</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>525</v>
+        <v>21</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>518</v>
+        <v>530</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>21</v>
+        <v>532</v>
       </c>
     </row>
-    <row r="74" hidden="true">
+    <row r="74">
       <c r="A74" t="s" s="2">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>528</v>
+        <v>21</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>21</v>
@@ -10674,17 +10673,15 @@
         <v>21</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>532</v>
-      </c>
+        <v>536</v>
+      </c>
+      <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>21</v>
@@ -10733,13 +10730,13 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>21</v>
@@ -10748,13 +10745,13 @@
         <v>102</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>21</v>
+        <v>537</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>21</v>
+        <v>530</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>21</v>
@@ -10765,14 +10762,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>21</v>
+        <v>540</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10791,16 +10788,16 @@
         <v>21</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10850,7 +10847,7 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -10865,23 +10862,140 @@
         <v>102</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>539</v>
+        <v>21</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO75" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="76" hidden="true">
+      <c r="A76" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="O76" s="2"/>
+      <c r="P76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO76" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO75">
+  <autoFilter ref="A1:AO76">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10891,7 +11005,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI74">
+  <conditionalFormatting sqref="A2:AI75">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-20T10:02:53+00:00</t>
+    <t>2026-02-23T08:57:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T08:57:08+00:00</t>
+    <t>2026-02-23T17:25:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1409,11 +1409,11 @@
     <t>MedicationRequest.dosageInstruction</t>
   </si>
   <si>
-    <t xml:space="preserve">Dosage
+    <t xml:space="preserve">Dosage {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-emed-dosage}
 </t>
   </si>
   <si>
-    <t>Anweisungen zur Einnahme/Verabreichung des Arzneimittels. TODO: alle Elemente + R5 Extensions prüfen</t>
+    <t>Angabe der Dosierinformationen strukturiert oder als Freitext</t>
   </si>
   <si>
     <t>Indicates how the medication is to be used by the patient.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T17:25:44+00:00</t>
+    <t>2026-02-26T16:36:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>**Beschreibung:** Bildet einen Medikationsplaneintrag im Medikationsplan eines ELGA-Teilnehmers ab ("MedicationRequest"-Ressource).
+    <t>Bildet einen Medikationsplaneintrag im Medikationsplan eines ELGA-Teilnehmers ab ("MedicationRequest"-Ressource).
 Er enthält genau ein Arzneimittel und dessen Dosierung.
 Kann in weiterer Folge dazu dienen, eine geplante Abgabe zu erstellen. Verwendet R5 Backport Extensions.</t>
   </si>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T16:36:39+00:00</t>
+    <t>2026-03-03T08:59:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T08:59:33+00:00</t>
+    <t>2026-03-03T14:03:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T14:03:22+00:00</t>
+    <t>2026-03-05T12:55:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T12:55:37+00:00</t>
+    <t>2026-03-05T13:31:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T13:31:59+00:00</t>
+    <t>2026-03-06T12:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -736,6 +736,7 @@
   &lt;coding&gt;
     &lt;system value="https://fhir.hl7.at/elga/emed/r4/CodeSystem/MedicationRequestCategoryCS"/&gt;
     &lt;code value="1"/&gt;
+    &lt;display value="Medikationsplaneintrag"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T12:22:28+00:00</t>
+    <t>2026-03-06T14:18:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1414,7 +1414,7 @@
 </t>
   </si>
   <si>
-    <t>Angabe der Dosierinformationen strukturiert oder als Freitext</t>
+    <t>Angabe der Dosierinformationen strukturiert oder als Freitext. TODO: Inhalte AtEmedDosage fachlich prüfen.</t>
   </si>
   <si>
     <t>Indicates how the medication is to be used by the patient.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T14:18:10+00:00</t>
+    <t>2026-03-09T08:14:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T08:14:04+00:00</t>
+    <t>2026-03-09T10:03:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T10:03:26+00:00</t>
+    <t>2026-03-09T11:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T11:27:52+00:00</t>
+    <t>2026-03-10T08:28:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T08:28:41+00:00</t>
+    <t>2026-03-10T11:00:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1330,7 +1330,7 @@
     <t>MedicationRequest.groupIdentifier</t>
   </si>
   <si>
-    <t>TODO: Verwendung im Medikationsplaneintrag zu prüfen. Erst bei der geplanten Abgabe (Rezepterstellung) relevant. Evtl ein Verweis auf erstellte Rezepte? Würde Extension erfordern, da Kardinalität nur 0..1 zulässig</t>
+    <t>Erst bei der geplanten Abgabe (Rezepterstellung) relevant. Evtl ein Verweis auf erstellte Rezepte? Würde Extension erfordern, da Kardinalität nur 0..1 zulässig</t>
   </si>
   <si>
     <t>A shared identifier common to all requests that were authorized more or less simultaneously by a single author, representing the identifier of the requisition or prescription.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T11:00:19+00:00</t>
+    <t>2026-03-10T11:31:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$67</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2830" uniqueCount="553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2497" uniqueCount="499">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T11:31:06+00:00</t>
+    <t>2026-03-16T16:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -428,64 +428,10 @@
     <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
   </si>
   <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>DomainResource.contained</t>
   </si>
   <si>
     <t>N/A</t>
-  </si>
-  <si>
-    <t>MedicationRequest.contained:medication</t>
-  </si>
-  <si>
-    <t>medication</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medication {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-emed-medication}
-</t>
-  </si>
-  <si>
-    <t>Definition of a Medication</t>
-  </si>
-  <si>
-    <t>This resource is primarily used for the identification and definition of a medication for the purposes of prescribing, dispensing, and administering a medication as well as for making statements about medication use.</t>
-  </si>
-  <si>
-    <t>NewRx/MedicationPrescribed--or--RxFill/MedicationDispensed--or--RxHistoryResponse/MedicationDispensed--or--RxHistoryResponse/MedicationPrescribed</t>
-  </si>
-  <si>
-    <t>ManufacturedProduct[classCode=ADMM]</t>
-  </si>
-  <si>
-    <t>MedicationRequest.contained:substance</t>
-  </si>
-  <si>
-    <t>substance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Substance {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-emed-substance}
-</t>
-  </si>
-  <si>
-    <t>A homogeneous material with a definite composition</t>
-  </si>
-  <si>
-    <t>A homogeneous material with a definite composition.</t>
-  </si>
-  <si>
-    <t>Material</t>
   </si>
   <si>
     <t>MedicationRequest.extension</t>
@@ -503,6 +449,9 @@
   <si>
     <t xml:space="preserve">value:url}
 </t>
+  </si>
+  <si>
+    <t>open</t>
   </si>
   <si>
     <t>DomainResource.extension</t>
@@ -813,6 +762,10 @@
     <t>Indicates if this record was captured as a secondary 'reported' record rather than as an original primary source-of-truth record.  It may also indicate the source of the report.</t>
   </si>
   <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
     <t>closed</t>
   </si>
   <si>
@@ -844,23 +797,17 @@
     <t>MedicationRequest.medication[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Medication|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-emed-medication) &lt;&lt;contained&gt;&gt;
 </t>
   </si>
   <si>
-    <t>Medication to be taken</t>
+    <t>Das Arzneimittel wird immer in einer contained Medication Ressource dokumentiert, damit Arzneimittel mit und ohne PZN einheitlich dokumentiert werden können.</t>
   </si>
   <si>
     <t>Identifies the medication being requested. This is a link to a resource that represents the medication which may be the details of the medication or simply an attribute carrying a code that identifies the medication from a known list of medications.</t>
   </si>
   <si>
     <t>If only a code is specified, then it needs to be a code for a specific product. If more information is required, then the use of the Medication resource is recommended.  For example, if you require form or lot number or if the medication is compounded or extemporaneously prepared, then you must reference the Medication resource.</t>
-  </si>
-  <si>
-    <t>A coded concept identifying substance or product that can be ordered.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-codes|4.0.1</t>
   </si>
   <si>
     <t>Request.code</t>
@@ -884,155 +831,6 @@
     <t>RXE-2-Give Code / RXO-1-Requested Give Code / RXC-2-Component Code</t>
   </si>
   <si>
-    <t>MedicationRequest.medication[x]:medicationReference</t>
-  </si>
-  <si>
-    <t>medicationReference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-emed-medication)
-</t>
-  </si>
-  <si>
-    <t>Das Arzneimittel wird immer in einer contained Medication Ressource dokumentiert, damit Arzneimittel mit und ohne PZN einheitlich dokumentiert werden können.</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x]:medicationReference.id</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x].id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x]:medicationReference.extension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x].extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x]:medicationReference.reference</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x].reference</t>
-  </si>
-  <si>
-    <t>Literal reference, Relative, internal or absolute URL</t>
-  </si>
-  <si>
-    <t>A reference to a location at which the other resource is found. The reference may be a relative reference, in which case it is relative to the service base URL, or an absolute URL that resolves to the location where the resource is found. The reference may be version specific or not. If the reference is not to a FHIR RESTful server, then it should be assumed to be version specific. Internal fragment references (start with '#') refer to contained resources.</t>
-  </si>
-  <si>
-    <t>Using absolute URLs provides a stable scalable approach suitable for a cloud/web context, while using relative/logical references provides a flexible approach suitable for use when trading across closed eco-system boundaries.   Absolute URLs do not need to point to a FHIR RESTful server, though this is the preferred approach. If the URL conforms to the structure "/[type]/[id]" then it should be assumed that the reference is to a FHIR RESTful server.</t>
-  </si>
-  <si>
-    <t>Reference.reference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ref-1
-</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-contained-ref:Medication must be contained (#...) {$this.startsWith('#')}</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x]:medicationReference.type</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x].type</t>
-  </si>
-  <si>
-    <t>Type the reference refers to (e.g. "Patient")</t>
-  </si>
-  <si>
-    <t>The expected type of the target of the reference. If both Reference.type and Reference.reference are populated and Reference.reference is a FHIR URL, both SHALL be consistent.
-The type is the Canonical URL of Resource Definition that is the type this reference refers to. References are URLs that are relative to http://hl7.org/fhir/StructureDefinition/ e.g. "Patient" is a reference to http://hl7.org/fhir/StructureDefinition/Patient. Absolute URLs are only allowed for logical models (and can only be used in references in logical models, not resources).</t>
-  </si>
-  <si>
-    <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>Aa resource (or, for logical models, the URI of the logical model).</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
-  </si>
-  <si>
-    <t>Reference.type</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x]:medicationReference.identifier</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x].identifier</t>
-  </si>
-  <si>
-    <t>Logical reference, when literal reference is not known</t>
-  </si>
-  <si>
-    <t>An identifier for the target resource. This is used when there is no way to reference the other resource directly, either because the entity it represents is not available through a FHIR server, or because there is no way for the author of the resource to convert a known identifier to an actual location. There is no requirement that a Reference.identifier point to something that is actually exposed as a FHIR instance, but it SHALL point to a business concept that would be expected to be exposed as a FHIR instance, and that instance would need to be of a FHIR resource type allowed by the reference.</t>
-  </si>
-  <si>
-    <t>When an identifier is provided in place of a reference, any system processing the reference will only be able to resolve the identifier to a reference if it understands the business context in which the identifier is used. Sometimes this is global (e.g. a national identifier) but often it is not. For this reason, none of the useful mechanisms described for working with references (e.g. chaining, includes) are possible, nor should servers be expected to be able resolve the reference. Servers may accept an identifier based reference untouched, resolve it, and/or reject it - see CapabilityStatement.rest.resource.referencePolicy. 
-When both an identifier and a literal reference are provided, the literal reference is preferred. Applications processing the resource are allowed - but not required - to check that the identifier matches the literal reference
-Applications converting a logical reference to a literal reference may choose to leave the logical reference present, or remove it.
-Reference is intended to point to a structure that can potentially be expressed as a FHIR resource, though there is no need for it to exist as an actual FHIR resource instance - except in as much as an application wishes to actual find the target of the reference. The content referred to be the identifier must meet the logical constraints implied by any limitations on what resource types are permitted for the reference.  For example, it would not be legitimate to send the identifier for a drug prescription if the type were Reference(Observation|DiagnosticReport).  One of the use-cases for Reference.identifier is the situation where no FHIR representation exists (where the type is Reference (Any).</t>
-  </si>
-  <si>
-    <t>Reference.identifier</t>
-  </si>
-  <si>
-    <t>.identifier</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x]:medicationReference.display</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x].display</t>
-  </si>
-  <si>
-    <t>Text alternative for the resource</t>
-  </si>
-  <si>
-    <t>Plain text narrative that identifies the resource in addition to the resource reference.</t>
-  </si>
-  <si>
-    <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
-  </si>
-  <si>
-    <t>Reference.display</t>
-  </si>
-  <si>
     <t>MedicationRequest.subject</t>
   </si>
   <si>
@@ -1451,7 +1249,32 @@
     <t>MedicationRequest.dispenseRequest.id</t>
   </si>
   <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>MedicationRequest.dispenseRequest.extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
   </si>
   <si>
     <t>MedicationRequest.dispenseRequest.modifierExtension</t>
@@ -2100,10 +1923,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO76"/>
+  <dimension ref="A1:AO67"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="52.8828125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="51.68359375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="51.68359375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="22.41015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
@@ -2131,7 +1954,7 @@
     <col min="26" max="26" width="61.125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="50.90625" customWidth="true" bestFit="true" hidden="true"/>
@@ -2981,7 +2804,7 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G8" t="s" s="2">
         <v>81</v>
@@ -3043,17 +2866,19 @@
         <v>21</v>
       </c>
       <c r="AB8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF8" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="AC8" s="2"/>
-      <c r="AD8" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE8" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AF8" t="s" s="2">
-        <v>134</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -3074,7 +2899,7 @@
         <v>21</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AN8" t="s" s="2">
         <v>21</v>
@@ -3085,23 +2910,21 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="C9" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>21</v>
@@ -3113,17 +2936,15 @@
         <v>21</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>131</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>21</v>
@@ -3160,19 +2981,17 @@
         <v>21</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -3184,16 +3003,16 @@
         <v>21</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>21</v>
+        <v>141</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>21</v>
@@ -3204,13 +3023,13 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="C10" t="s" s="2">
         <v>143</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>144</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>21</v>
@@ -3220,7 +3039,7 @@
         <v>80</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>21</v>
@@ -3232,17 +3051,15 @@
         <v>21</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="L10" t="s" s="2">
         <v>145</v>
       </c>
-      <c r="L10" t="s" s="2">
+      <c r="M10" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="M10" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>131</v>
-      </c>
+      <c r="N10" s="2"/>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>21</v>
@@ -3291,7 +3108,7 @@
         <v>21</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -3300,10 +3117,10 @@
         <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>21</v>
+        <v>147</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>21</v>
+        <v>141</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>21</v>
@@ -3312,7 +3129,7 @@
         <v>21</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>21</v>
@@ -3323,12 +3140,14 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="C11" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="B11" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
         <v>21</v>
       </c>
@@ -3337,7 +3156,7 @@
         <v>80</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>21</v>
@@ -3394,17 +3213,19 @@
         <v>21</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="AC11" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC11" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD11" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3413,10 +3234,10 @@
         <v>81</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>21</v>
+        <v>147</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>21</v>
@@ -3425,7 +3246,7 @@
         <v>21</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>21</v>
+        <v>133</v>
       </c>
       <c r="AN11" t="s" s="2">
         <v>21</v>
@@ -3436,13 +3257,13 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>21</v>
@@ -3464,13 +3285,13 @@
         <v>21</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3521,7 +3342,7 @@
         <v>21</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3530,10 +3351,10 @@
         <v>81</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>21</v>
@@ -3542,7 +3363,7 @@
         <v>21</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>135</v>
+        <v>21</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>21</v>
@@ -3553,44 +3374,46 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="C13" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>21</v>
+        <v>159</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>164</v>
+        <v>135</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
+        <v>161</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="O13" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="P13" t="s" s="2">
         <v>21</v>
       </c>
@@ -3638,7 +3461,7 @@
         <v>21</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3647,10 +3470,10 @@
         <v>81</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>21</v>
@@ -3659,7 +3482,7 @@
         <v>21</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>21</v>
@@ -3670,20 +3493,18 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="C14" t="s" s="2">
-        <v>168</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>90</v>
@@ -3698,15 +3519,17 @@
         <v>21</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="L14" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>21</v>
@@ -3755,7 +3578,7 @@
         <v>21</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -3764,69 +3587,67 @@
         <v>81</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>155</v>
+        <v>102</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>21</v>
+        <v>170</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>21</v>
+        <v>171</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>21</v>
+        <v>172</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>21</v>
+        <v>173</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>21</v>
+        <v>174</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>91</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>177</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>21</v>
       </c>
@@ -3850,13 +3671,11 @@
         <v>21</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y15" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="Y15" s="2"/>
       <c r="Z15" t="s" s="2">
-        <v>21</v>
+        <v>180</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>21</v>
@@ -3874,31 +3693,31 @@
         <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>155</v>
+        <v>102</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>21</v>
+        <v>181</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>21</v>
+        <v>182</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>135</v>
+        <v>183</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>21</v>
+        <v>184</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>21</v>
@@ -3906,10 +3725,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3917,10 +3736,10 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>21</v>
@@ -3932,16 +3751,16 @@
         <v>21</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3967,13 +3786,13 @@
         <v>21</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>21</v>
+        <v>190</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>21</v>
+        <v>191</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>21</v>
+        <v>192</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>21</v>
@@ -3991,13 +3810,13 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>21</v>
@@ -4006,27 +3825,27 @@
         <v>102</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>185</v>
+        <v>21</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>187</v>
+        <v>21</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>188</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4052,13 +3871,13 @@
         <v>110</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4069,7 +3888,7 @@
         <v>21</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>21</v>
+        <v>199</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>21</v>
@@ -4084,11 +3903,13 @@
         <v>21</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="Y17" s="2"/>
+        <v>179</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>200</v>
+      </c>
       <c r="Z17" t="s" s="2">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>21</v>
@@ -4106,7 +3927,7 @@
         <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>90</v>
@@ -4121,27 +3942,27 @@
         <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>196</v>
+        <v>21</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4149,13 +3970,13 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>21</v>
@@ -4164,16 +3985,16 @@
         <v>21</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4184,7 +4005,7 @@
         <v>21</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>21</v>
+        <v>209</v>
       </c>
       <c r="T18" t="s" s="2">
         <v>21</v>
@@ -4199,37 +4020,37 @@
         <v>21</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="Y18" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="Z18" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AA18" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB18" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE18" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF18" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="Z18" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="AA18" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB18" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC18" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD18" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE18" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF18" t="s" s="2">
-        <v>199</v>
-      </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>21</v>
@@ -4238,27 +4059,27 @@
         <v>102</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>207</v>
+        <v>21</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>21</v>
+        <v>212</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4266,16 +4087,16 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J19" t="s" s="2">
         <v>91</v>
@@ -4284,14 +4105,12 @@
         <v>110</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>212</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>21</v>
@@ -4301,7 +4120,7 @@
         <v>21</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>213</v>
+        <v>21</v>
       </c>
       <c r="T19" t="s" s="2">
         <v>21</v>
@@ -4316,34 +4135,34 @@
         <v>21</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="Y19" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="Z19" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AA19" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF19" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="Z19" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="AA19" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB19" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC19" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD19" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE19" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF19" t="s" s="2">
-        <v>209</v>
-      </c>
       <c r="AG19" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>90</v>
@@ -4355,27 +4174,27 @@
         <v>102</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4383,31 +4202,31 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I20" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I20" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="J20" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4418,7 +4237,7 @@
         <v>21</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>223</v>
+        <v>21</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>21</v>
@@ -4433,13 +4252,13 @@
         <v>21</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>204</v>
+        <v>21</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>224</v>
+        <v>21</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>225</v>
+        <v>21</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>21</v>
@@ -4457,13 +4276,13 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>21</v>
@@ -4475,13 +4294,13 @@
         <v>21</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>226</v>
+        <v>21</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>227</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>218</v>
+        <v>21</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>21</v>
@@ -4500,13 +4319,13 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>21</v>
@@ -4515,13 +4334,13 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>110</v>
+        <v>229</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4548,28 +4367,26 @@
         <v>21</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>193</v>
+        <v>21</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>231</v>
+        <v>21</v>
       </c>
       <c r="Z21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB21" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="AA21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>21</v>
-      </c>
+      <c r="AC21" s="2"/>
       <c r="AD21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>21</v>
+        <v>233</v>
       </c>
       <c r="AF21" t="s" s="2">
         <v>228</v>
@@ -4587,7 +4404,7 @@
         <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>233</v>
+        <v>21</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>21</v>
@@ -4596,7 +4413,7 @@
         <v>234</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>235</v>
+        <v>21</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>21</v>
@@ -4604,12 +4421,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="C22" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="B22" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
         <v>21</v>
       </c>
@@ -4618,13 +4437,13 @@
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>91</v>
@@ -4636,11 +4455,9 @@
         <v>238</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>21</v>
@@ -4689,7 +4506,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4710,7 +4527,7 @@
         <v>21</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>21</v>
@@ -4721,24 +4538,26 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="D23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>21</v>
@@ -4747,13 +4566,13 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>243</v>
+        <v>223</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4792,17 +4611,19 @@
         <v>21</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AC23" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>246</v>
+        <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4823,7 +4644,7 @@
         <v>21</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>21</v>
@@ -4832,28 +4653,26 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="C24" t="s" s="2">
-        <v>249</v>
-      </c>
+      <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>21</v>
@@ -4862,15 +4681,17 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="M24" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="N24" s="2"/>
+      <c r="N24" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>21</v>
@@ -4922,7 +4743,7 @@
         <v>242</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>90</v>
@@ -4934,43 +4755,41 @@
         <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>21</v>
+        <v>247</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>21</v>
+        <v>248</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>21</v>
+        <v>250</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>21</v>
+        <v>251</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
         <v>252</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>21</v>
@@ -4979,15 +4798,17 @@
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>254</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>255</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>256</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>21</v>
@@ -5036,10 +4857,10 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>90</v>
@@ -5051,27 +4872,27 @@
         <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>21</v>
+        <v>257</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>21</v>
+        <v>258</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>21</v>
+        <v>260</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>21</v>
+        <v>261</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5079,31 +4900,31 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5129,32 +4950,34 @@
         <v>21</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>204</v>
+        <v>21</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>260</v>
+        <v>21</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>261</v>
+        <v>21</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AC26" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>246</v>
+        <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>90</v>
@@ -5166,62 +4989,58 @@
         <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>263</v>
+        <v>182</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="C27" t="s" s="2">
-        <v>268</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>21</v>
@@ -5270,13 +5089,13 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>21</v>
@@ -5285,27 +5104,27 @@
         <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>263</v>
+        <v>21</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>266</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5313,28 +5132,28 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5385,7 +5204,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5397,63 +5216,61 @@
         <v>21</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>21</v>
+        <v>281</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>21</v>
+        <v>282</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>21</v>
+        <v>284</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>21</v>
+        <v>285</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>150</v>
+        <v>287</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>176</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>21</v>
@@ -5490,43 +5307,43 @@
         <v>21</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>282</v>
+        <v>21</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>155</v>
+        <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>21</v>
+        <v>290</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>277</v>
+        <v>259</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>21</v>
+        <v>291</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>21</v>
@@ -5534,10 +5351,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5548,7 +5365,7 @@
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>21</v>
@@ -5557,20 +5374,18 @@
         <v>21</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>21</v>
@@ -5619,7 +5434,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5628,22 +5443,22 @@
         <v>90</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>290</v>
+        <v>21</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>291</v>
+        <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>21</v>
+        <v>296</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>135</v>
+        <v>297</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>21</v>
+        <v>298</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>21</v>
@@ -5651,10 +5466,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5665,7 +5480,7 @@
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>21</v>
@@ -5677,16 +5492,16 @@
         <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>104</v>
+        <v>186</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5712,31 +5527,31 @@
         <v>21</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>297</v>
+        <v>190</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="Z31" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF31" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="AA31" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB31" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD31" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5751,13 +5566,13 @@
         <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>21</v>
+        <v>305</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>135</v>
+        <v>306</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>21</v>
@@ -5768,10 +5583,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5782,7 +5597,7 @@
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>21</v>
@@ -5791,20 +5606,18 @@
         <v>21</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>180</v>
+        <v>308</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>305</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>21</v>
@@ -5853,7 +5666,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5874,10 +5687,10 @@
         <v>21</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>21</v>
+        <v>312</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>21</v>
@@ -5885,10 +5698,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5899,7 +5712,7 @@
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>21</v>
@@ -5908,19 +5721,19 @@
         <v>21</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>273</v>
+        <v>186</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5946,13 +5759,13 @@
         <v>21</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>21</v>
+        <v>190</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>21</v>
+        <v>317</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>21</v>
+        <v>318</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>21</v>
@@ -5976,7 +5789,7 @@
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>21</v>
@@ -5985,27 +5798,27 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>21</v>
+        <v>319</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>21</v>
+        <v>320</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>135</v>
+        <v>321</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>21</v>
+        <v>322</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>21</v>
+        <v>323</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6013,31 +5826,31 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6087,13 +5900,13 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>21</v>
@@ -6102,27 +5915,27 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>320</v>
+        <v>182</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>322</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>323</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6142,20 +5955,18 @@
         <v>21</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>328</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>21</v>
@@ -6204,13 +6015,13 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>21</v>
@@ -6219,27 +6030,27 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>196</v>
+        <v>21</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>331</v>
+        <v>21</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>332</v>
+        <v>21</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6259,16 +6070,16 @@
         <v>21</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>334</v>
+        <v>104</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6319,7 +6130,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6334,27 +6145,27 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>337</v>
+        <v>21</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>331</v>
+        <v>21</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6362,13 +6173,13 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>21</v>
@@ -6377,13 +6188,13 @@
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6434,13 +6245,13 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>21</v>
@@ -6449,27 +6260,27 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>344</v>
+        <v>21</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>345</v>
       </c>
       <c r="AN37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO37" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="38" hidden="true">
+      <c r="A38" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="AO37" t="s" s="2">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s" s="2">
-        <v>348</v>
-      </c>
       <c r="B38" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6477,13 +6288,13 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>21</v>
@@ -6492,16 +6303,18 @@
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="L38" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>21</v>
       </c>
@@ -6549,7 +6362,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6564,27 +6377,27 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AN38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO38" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="AL38" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="39" hidden="true">
-      <c r="A39" t="s" s="2">
-        <v>354</v>
-      </c>
       <c r="B39" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6595,10 +6408,10 @@
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>21</v>
@@ -6607,15 +6420,17 @@
         <v>21</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="N39" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="L39" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>21</v>
@@ -6640,13 +6455,13 @@
         <v>21</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>21</v>
+        <v>190</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>21</v>
+        <v>356</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>21</v>
+        <v>357</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>21</v>
@@ -6664,7 +6479,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6679,16 +6494,16 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="AL39" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>359</v>
-      </c>
       <c r="AN39" t="s" s="2">
-        <v>360</v>
+        <v>21</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>21</v>
@@ -6696,10 +6511,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6719,20 +6534,18 @@
         <v>21</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>200</v>
+        <v>360</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="M40" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>364</v>
-      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>21</v>
@@ -6757,13 +6570,13 @@
         <v>21</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>204</v>
+        <v>21</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>365</v>
+        <v>21</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>366</v>
+        <v>21</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>21</v>
@@ -6781,13 +6594,13 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>21</v>
@@ -6796,13 +6609,13 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>21</v>
@@ -6811,12 +6624,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6827,10 +6640,10 @@
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>21</v>
@@ -6839,13 +6652,13 @@
         <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6896,13 +6709,13 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>21</v>
@@ -6911,27 +6724,27 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>21</v>
+        <v>369</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>21</v>
+        <v>370</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>374</v>
+        <v>21</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6939,13 +6752,13 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>21</v>
@@ -6954,16 +6767,16 @@
         <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>200</v>
+        <v>373</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="N42" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6989,13 +6802,13 @@
         <v>21</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>204</v>
+        <v>21</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>379</v>
+        <v>21</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>380</v>
+        <v>21</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>21</v>
@@ -7013,7 +6826,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7028,27 +6841,27 @@
         <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>382</v>
+        <v>21</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>384</v>
+        <v>21</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>385</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7071,17 +6884,15 @@
         <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>390</v>
-      </c>
+        <v>382</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>21</v>
@@ -7130,13 +6941,13 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>21</v>
@@ -7145,16 +6956,16 @@
         <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>391</v>
+        <v>21</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>196</v>
+        <v>383</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>384</v>
+        <v>21</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>21</v>
@@ -7162,10 +6973,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7176,7 +6987,7 @@
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>21</v>
@@ -7185,16 +6996,16 @@
         <v>21</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7245,28 +7056,28 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>397</v>
+        <v>21</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>21</v>
@@ -7277,21 +7088,21 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>21</v>
+        <v>159</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>21</v>
@@ -7300,18 +7111,20 @@
         <v>21</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>393</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>21</v>
@@ -7360,7 +7173,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7372,7 +7185,7 @@
         <v>21</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>21</v>
@@ -7381,7 +7194,7 @@
         <v>21</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>21</v>
@@ -7392,42 +7205,46 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>21</v>
+        <v>396</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J46" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>403</v>
+        <v>135</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+        <v>398</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>21</v>
       </c>
@@ -7475,7 +7292,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7487,16 +7304,16 @@
         <v>21</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>406</v>
+        <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>407</v>
+        <v>133</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>21</v>
@@ -7507,10 +7324,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7521,7 +7338,7 @@
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>21</v>
@@ -7530,21 +7347,21 @@
         <v>21</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>180</v>
+        <v>380</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" t="s" s="2">
-        <v>411</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>21</v>
       </c>
@@ -7592,7 +7409,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7607,13 +7424,13 @@
         <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>412</v>
+        <v>21</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>21</v>
@@ -7622,12 +7439,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7641,7 +7458,7 @@
         <v>90</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>21</v>
@@ -7650,17 +7467,15 @@
         <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>200</v>
+        <v>386</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>415</v>
+        <v>387</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>417</v>
-      </c>
+        <v>388</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>21</v>
@@ -7685,13 +7500,13 @@
         <v>21</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>204</v>
+        <v>21</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>418</v>
+        <v>21</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>419</v>
+        <v>21</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>21</v>
@@ -7709,7 +7524,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>414</v>
+        <v>389</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7721,7 +7536,7 @@
         <v>21</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>21</v>
@@ -7730,7 +7545,7 @@
         <v>21</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>420</v>
+        <v>390</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>21</v>
@@ -7741,21 +7556,21 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>421</v>
+        <v>406</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>421</v>
+        <v>406</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>21</v>
+        <v>159</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>21</v>
@@ -7767,15 +7582,17 @@
         <v>21</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>422</v>
+        <v>135</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>423</v>
+        <v>392</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>393</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>21</v>
@@ -7824,7 +7641,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>421</v>
+        <v>394</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7836,16 +7653,16 @@
         <v>21</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>425</v>
+        <v>21</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>426</v>
+        <v>390</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>21</v>
@@ -7854,16 +7671,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>427</v>
+        <v>407</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>427</v>
+        <v>407</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>21</v>
+        <v>396</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7873,25 +7690,29 @@
         <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I50" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I50" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="J50" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>428</v>
+        <v>135</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>429</v>
+        <v>397</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+        <v>398</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>21</v>
       </c>
@@ -7939,7 +7760,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>427</v>
+        <v>399</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7951,16 +7772,16 @@
         <v>21</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>431</v>
+        <v>21</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>432</v>
+        <v>21</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>433</v>
+        <v>133</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>21</v>
@@ -7969,12 +7790,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>434</v>
+        <v>408</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>434</v>
+        <v>408</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7982,13 +7803,13 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G51" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="G51" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="H51" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>21</v>
@@ -7997,17 +7818,15 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>435</v>
+        <v>409</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>436</v>
+        <v>410</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>438</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>21</v>
@@ -8056,13 +7875,13 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>434</v>
+        <v>408</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>21</v>
@@ -8071,13 +7890,13 @@
         <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>439</v>
+        <v>21</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>440</v>
+        <v>412</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>21</v>
@@ -8088,10 +7907,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>441</v>
+        <v>413</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>441</v>
+        <v>413</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8102,7 +7921,7 @@
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>21</v>
@@ -8114,13 +7933,13 @@
         <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>442</v>
+        <v>414</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>443</v>
+        <v>415</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>444</v>
+        <v>416</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8171,7 +7990,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>441</v>
+        <v>413</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8189,10 +8008,10 @@
         <v>21</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>445</v>
+        <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>446</v>
+        <v>417</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>21</v>
@@ -8203,10 +8022,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>447</v>
+        <v>418</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>447</v>
+        <v>418</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8229,13 +8048,13 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>273</v>
+        <v>414</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>274</v>
+        <v>419</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>275</v>
+        <v>420</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8286,7 +8105,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>276</v>
+        <v>418</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8298,7 +8117,7 @@
         <v>21</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>21</v>
@@ -8307,7 +8126,7 @@
         <v>21</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>277</v>
+        <v>417</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>21</v>
@@ -8318,21 +8137,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>448</v>
+        <v>421</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>448</v>
+        <v>421</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>21</v>
@@ -8344,18 +8163,20 @@
         <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>150</v>
+        <v>422</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>280</v>
+        <v>423</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>281</v>
+        <v>424</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>425</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>426</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>21</v>
       </c>
@@ -8403,28 +8224,28 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>283</v>
+        <v>421</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>155</v>
+        <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>21</v>
+        <v>427</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>277</v>
+        <v>428</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>21</v>
@@ -8435,46 +8256,44 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>449</v>
+        <v>429</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>449</v>
+        <v>429</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>450</v>
+        <v>21</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>150</v>
+        <v>430</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>451</v>
+        <v>431</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>452</v>
+        <v>432</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>177</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>21</v>
       </c>
@@ -8522,42 +8341,42 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>453</v>
+        <v>429</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>155</v>
+        <v>102</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>21</v>
+        <v>434</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>135</v>
+        <v>435</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>21</v>
+        <v>436</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>454</v>
+        <v>437</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>454</v>
+        <v>437</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8580,17 +8399,15 @@
         <v>21</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>442</v>
+        <v>409</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>455</v>
+        <v>438</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>457</v>
-      </c>
+        <v>439</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>21</v>
@@ -8639,7 +8456,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>454</v>
+        <v>437</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8657,24 +8474,24 @@
         <v>21</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>21</v>
+        <v>440</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>458</v>
+        <v>441</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>21</v>
+        <v>442</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>459</v>
+        <v>443</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>459</v>
+        <v>443</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8697,15 +8514,17 @@
         <v>21</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>273</v>
+        <v>414</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>274</v>
+        <v>444</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>445</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>446</v>
+      </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>21</v>
@@ -8754,7 +8573,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>276</v>
+        <v>443</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8766,16 +8585,16 @@
         <v>21</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>21</v>
+        <v>447</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>277</v>
+        <v>448</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>21</v>
@@ -8786,21 +8605,21 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>460</v>
+        <v>449</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>460</v>
+        <v>449</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>21</v>
@@ -8812,17 +8631,15 @@
         <v>21</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>150</v>
+        <v>450</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>280</v>
+        <v>451</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>176</v>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>21</v>
@@ -8871,19 +8688,19 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>283</v>
+        <v>449</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>155</v>
+        <v>102</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>21</v>
@@ -8892,57 +8709,53 @@
         <v>21</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>277</v>
+        <v>453</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>21</v>
+        <v>312</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>450</v>
+        <v>21</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>150</v>
+        <v>380</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>177</v>
-      </c>
+        <v>456</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>21</v>
       </c>
@@ -8990,28 +8803,28 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>155</v>
+        <v>102</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>21</v>
+        <v>457</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>135</v>
+        <v>458</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>21</v>
@@ -9022,10 +8835,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9048,13 +8861,13 @@
         <v>21</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>463</v>
+        <v>386</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>464</v>
+        <v>387</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>465</v>
+        <v>388</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9105,7 +8918,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>462</v>
+        <v>389</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9117,7 +8930,7 @@
         <v>21</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>21</v>
@@ -9126,7 +8939,7 @@
         <v>21</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>466</v>
+        <v>390</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>21</v>
@@ -9137,21 +8950,21 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>21</v>
+        <v>159</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>21</v>
@@ -9163,15 +8976,17 @@
         <v>21</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>468</v>
+        <v>135</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>469</v>
+        <v>392</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>393</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>21</v>
@@ -9220,19 +9035,19 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>467</v>
+        <v>394</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>21</v>
@@ -9241,7 +9056,7 @@
         <v>21</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>471</v>
+        <v>390</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>21</v>
@@ -9252,42 +9067,46 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>472</v>
+        <v>461</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>472</v>
+        <v>461</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>21</v>
+        <v>396</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>468</v>
+        <v>135</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>473</v>
+        <v>397</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+        <v>398</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>21</v>
       </c>
@@ -9335,19 +9154,19 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>472</v>
+        <v>399</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>21</v>
@@ -9356,7 +9175,7 @@
         <v>21</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>471</v>
+        <v>133</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>21</v>
@@ -9367,10 +9186,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>475</v>
+        <v>462</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>475</v>
+        <v>462</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9378,7 +9197,7 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>90</v>
@@ -9393,20 +9212,18 @@
         <v>21</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>476</v>
+        <v>463</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>477</v>
+        <v>464</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>478</v>
+        <v>465</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>480</v>
-      </c>
+        <v>466</v>
+      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>21</v>
       </c>
@@ -9430,13 +9247,13 @@
         <v>21</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>21</v>
+        <v>190</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>21</v>
+        <v>467</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>21</v>
+        <v>468</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>21</v>
@@ -9454,10 +9271,10 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>475</v>
+        <v>462</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>90</v>
@@ -9472,24 +9289,24 @@
         <v>21</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>481</v>
+        <v>457</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>482</v>
+        <v>469</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>21</v>
+        <v>470</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9512,17 +9329,15 @@
         <v>21</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>484</v>
+        <v>186</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>485</v>
+        <v>472</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>487</v>
-      </c>
+        <v>473</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>21</v>
@@ -9547,13 +9362,13 @@
         <v>21</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>21</v>
+        <v>190</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>21</v>
+        <v>474</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>21</v>
+        <v>475</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>21</v>
@@ -9571,7 +9386,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9589,24 +9404,24 @@
         <v>21</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>490</v>
+        <v>478</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9620,7 +9435,7 @@
         <v>90</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>21</v>
@@ -9629,13 +9444,13 @@
         <v>21</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>463</v>
+        <v>480</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>492</v>
+        <v>481</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>493</v>
+        <v>482</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9686,7 +9501,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9701,38 +9516,38 @@
         <v>102</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>21</v>
+        <v>483</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>494</v>
+        <v>476</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>495</v>
+        <v>484</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>496</v>
+        <v>21</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>21</v>
+        <v>486</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>21</v>
@@ -9744,16 +9559,16 @@
         <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>468</v>
+        <v>487</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>498</v>
+        <v>488</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>499</v>
+        <v>489</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9803,13 +9618,13 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>21</v>
@@ -9821,10 +9636,10 @@
         <v>21</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>501</v>
+        <v>21</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>21</v>
@@ -9835,10 +9650,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>503</v>
+        <v>492</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>503</v>
+        <v>492</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9849,7 +9664,7 @@
         <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>21</v>
@@ -9861,15 +9676,17 @@
         <v>21</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>504</v>
+        <v>493</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>505</v>
+        <v>494</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="N67" s="2"/>
+        <v>495</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>496</v>
+      </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>21</v>
@@ -9918,13 +9735,13 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>503</v>
+        <v>492</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>21</v>
@@ -9933,1070 +9750,23 @@
         <v>102</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>21</v>
+        <v>497</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>374</v>
+        <v>21</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="C68" s="2"/>
-      <c r="D68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E68" s="2"/>
-      <c r="F68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G68" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H68" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="I68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K68" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="L68" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
-      <c r="P68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q68" s="2"/>
-      <c r="R68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="AG68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH68" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ68" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="69" hidden="true">
-      <c r="A69" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="C69" s="2"/>
-      <c r="D69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E69" s="2"/>
-      <c r="F69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G69" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K69" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="L69" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
-      <c r="P69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q69" s="2"/>
-      <c r="R69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="AG69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AK69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="70" hidden="true">
-      <c r="A70" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="C70" s="2"/>
-      <c r="D70" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="E70" s="2"/>
-      <c r="F70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K70" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="L70" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="O70" s="2"/>
-      <c r="P70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q70" s="2"/>
-      <c r="R70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="AG70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ70" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="AK70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="71" hidden="true">
-      <c r="A71" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="C71" s="2"/>
-      <c r="D71" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="E71" s="2"/>
-      <c r="F71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I71" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="J71" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K71" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="L71" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="P71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q71" s="2"/>
-      <c r="R71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="AG71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ71" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="AK71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="72" hidden="true">
-      <c r="A72" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="C72" s="2"/>
-      <c r="D72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E72" s="2"/>
-      <c r="F72" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="G72" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K72" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="L72" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="O72" s="2"/>
-      <c r="P72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q72" s="2"/>
-      <c r="R72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X72" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="Z72" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="AG72" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AH72" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ72" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="73" hidden="true">
-      <c r="A73" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="C73" s="2"/>
-      <c r="D73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E73" s="2"/>
-      <c r="F73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G73" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K73" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="N73" s="2"/>
-      <c r="O73" s="2"/>
-      <c r="P73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q73" s="2"/>
-      <c r="R73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X73" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="Z73" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="AG73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH73" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ73" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO73" t="s" s="2">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="C74" s="2"/>
-      <c r="D74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E74" s="2"/>
-      <c r="F74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G74" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H74" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="I74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K74" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
-      <c r="P74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q74" s="2"/>
-      <c r="R74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="AG74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH74" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ74" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK74" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="75" hidden="true">
-      <c r="A75" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="C75" s="2"/>
-      <c r="D75" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="E75" s="2"/>
-      <c r="F75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K75" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="L75" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="O75" s="2"/>
-      <c r="P75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q75" s="2"/>
-      <c r="R75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="AG75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ75" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="76" hidden="true">
-      <c r="A76" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="C76" s="2"/>
-      <c r="D76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E76" s="2"/>
-      <c r="F76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K76" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="L76" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="O76" s="2"/>
-      <c r="P76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q76" s="2"/>
-      <c r="R76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="AG76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ76" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK76" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="AL76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO76" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO76">
+  <autoFilter ref="A1:AO67">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11006,7 +9776,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI75">
+  <conditionalFormatting sqref="A2:AI66">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T16:50:24+00:00</t>
+    <t>2026-03-19T16:44:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T16:44:44+00:00</t>
+    <t>2026-03-20T13:50:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T13:50:58+00:00</t>
+    <t>2026-03-20T15:30:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T15:30:14+00:00</t>
+    <t>2026-03-24T10:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -543,17 +543,17 @@
 </t>
   </si>
   <si>
-    <t>Medikationsplaneintrag-ID. TODO: Verwendung einer logischen Medikationsplaneintrag-ID prüfen.
+    <t>Medikationsplaneintrag-ID. TODO: Verwendung einer logischen Medikationsplaneintrag-ID prüfen. Details zur Herstellung von Bezügen von geänderten Planeinträgen, siehe Definition.</t>
+  </si>
+  <si>
+    <t>Medikationsplaneintrag-ID.
 Evt. mit Zeitstempel (Planeintrag-ID_{Zeitstempel}) zur Herstellung eines Bezugs von geänderten Planeinträgen.
 Vorteil: 
 - Auch wenn sich die PZN ändert, aber logisch der gleiche Eintrag betroffen ist (z.B. Austausch eines Arzneimittels durch ein anderes mit weniger Wechselwirkung), kann ein Bezug hergestellt werden.
 - Wenn zur Vorversion des Eintrags bereits eine geplante Abgabe erstellt wurde, kann ein Bezug zum ursprünglichen Eintrag hergestellt werden.
 Nachteil: 
 - Falls Planeinträge mit komplett neuer Arznei überschrieben werden, entsteht dadurch ein verwirrender Bezug. 
-- Die Verantwortung, dass nur Einträge geändert werden, die keine komplett neue Medikation beinhalten, liegt beim Client.</t>
-  </si>
-  <si>
-    <t>Identifiers associated with this medication request that are defined by business processes and/or used to refer to it when a direct URL reference to the resource itself is not appropriate. They are business identifiers assigned to this resource by the performer or other systems and remain constant as the resource is updated and propagates from server to server.</t>
+- Die Verantwortung, dass nur Einträge geändert werden, die keine komplett neue Medikation beinhalten, liegt beim Ersteller des Eintrags.</t>
   </si>
   <si>
     <t>This is a business identifier, not a resource identifier.</t>
@@ -577,10 +577,16 @@
     <t>MedicationRequest.status</t>
   </si>
   <si>
-    <t>Status des Medikationsplaneintrags. VS Einschränkung auf active, complete, on-hold, stopped (?); TODO: Fachlich zu püfen, ob im Medikationsplan dokumentiert werden soll, dass und warum ein Medikament abgesetzt wurde (Status: stopped, z.B. bei Allergie). Auch im Kontext mit statusReason, wo dieser Grund codiert angegeben werden kann (entfernt: cancelled, entered-in-error, draft, unknown)</t>
-  </si>
-  <si>
-    <t>A code specifying the current state of the order.  Generally, this will be active or completed state.</t>
+    <t>Status des Medikationsplaneintrags. active | completed | on-hold | stopped. TODO: Fachlich zu püfen, ob im Medikationsplan dokumentiert werden soll, dass und warum ein Medikament abgesetzt wurde (Status: stopped, z.B. bei Allergie). Details siehe Definition.</t>
+  </si>
+  <si>
+    <t>Status des Medikationsplaneintrags:
+* \"active\": aktive Therapie; soll aktuell vom Patienten eingenommen werden
+* \"completed\": Therapie regulär abgeschlossen
+* \"on-hold\": Therapie vorübergehend unterbrochen; Wiederaufnahme vorgesehen
+* \"stopped\": begonnen Therapie, aber vorzeitig und ohne regulären Abschluss beendet
+(nicht verwendet: cancelled, entered-in-error, draft, unknown)
+https://hl7.org/fhir/R4/valueset-medicationrequest-status.html</t>
   </si>
   <si>
     <t>This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
@@ -1146,7 +1152,7 @@
     <t>MedicationRequest.courseOfTherapyType</t>
   </si>
   <si>
-    <t>Gesamtmuster der Medikamentengabe (z.B. saisonal). Verwendung im Medikationsplaneintrag prüfen (dosageInstruction), evtl. durch Dosierungsinformationen abgedeck.</t>
+    <t>Gesamtmuster der Medikamentengabe. continuous | acute | seasonal. Verwendung im Medikationsplaneintrag prüfen, evtl. durch Dosierungsinformationen abgedeckt.</t>
   </si>
   <si>
     <t>The description of the overall patte3rn of the administration of the medication to the patient.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T10:00:40+00:00</t>
+    <t>2026-03-24T15:12:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T15:12:36+00:00</t>
+    <t>2026-03-27T10:18:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T10:18:57+00:00</t>
+    <t>2026-03-30T07:39:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T07:39:16+00:00</t>
+    <t>2026-03-30T10:13:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T10:13:35+00:00</t>
+    <t>2026-04-01T13:59:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T13:59:59+00:00</t>
+    <t>2026-04-02T15:01:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T15:01:02+00:00</t>
+    <t>2026-04-07T09:06:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T09:06:22+00:00</t>
+    <t>2026-04-07T15:41:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T15:41:53+00:00</t>
+    <t>2026-04-07T16:09:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T16:09:01+00:00</t>
+    <t>2026-04-08T18:33:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T18:33:44+00:00</t>
+    <t>2026-04-09T06:40:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T06:40:16+00:00</t>
+    <t>2026-04-09T18:30:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T18:30:31+00:00</t>
+    <t>2026-04-10T11:48:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T11:48:51+00:00</t>
+    <t>2026-04-13T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T14:44:53+00:00</t>
+    <t>2026-04-13T15:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T15:27:52+00:00</t>
+    <t>2026-04-13T20:12:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,9 +87,9 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Bildet einen Medikationsplaneintrag im Medikationsplan eines ELGA-Teilnehmers ab ("MedicationRequest"-Ressource).
-Er enthält genau ein Arzneimittel und dessen Dosierung.
-Kann in weiterer Folge dazu dienen, eine geplante Abgabe zu erstellen. Verwendet R5 Backport Extensions.</t>
+    <t>Ein Medikationsplaneintrag im Medikationsplan eines ELGA-Teilnehmers bzw. einer ELGA-Teilnehmerin wird durch eine "MedicationRequest"-Ressource abgebildet.
+Die Ressource enthält genau ein Medikament mit der zugehörigen Dosierung, wobei das Medikament verpflichtend in einer contained Medication-Ressource (inline), also innerhalb der Ressource, dokumentiert wird.
+Der Medikationsplaneintrag kann in weiterer Folge als Grundlage für die Erstellung einer geplanten Abgabe dienen. Es werden R5-Backport-Extensions verwendet.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -577,16 +577,10 @@
     <t>MedicationRequest.status</t>
   </si>
   <si>
-    <t>Status des Medikationsplaneintrags. active | completed | on-hold | stopped. TODO: Fachlich zu püfen, ob im Medikationsplan dokumentiert werden soll, dass und warum ein Medikament abgesetzt wurde (Status: stopped, z.B. bei Allergie). Details siehe Definition.</t>
-  </si>
-  <si>
-    <t>Status des Medikationsplaneintrags:
-* \"active\": aktive Therapie; soll aktuell vom Patienten eingenommen werden
-* \"completed\": Therapie regulär abgeschlossen
-* \"on-hold\": Therapie vorübergehend unterbrochen; Wiederaufnahme vorgesehen
-* \"stopped\": begonnen Therapie, aber vorzeitig und ohne regulären Abschluss beendet
-(nicht verwendet: cancelled, entered-in-error, draft, unknown)
-https://hl7.org/fhir/R4/valueset-medicationrequest-status.html</t>
+    <t>Status des Medikationsplaneintrags. Mögliche Ausprägungen: [active | on-hold | completed | stopped | entered-in-error]. Bedeutung: active: Planeintrag einer aktiven Medikation, die eingenommen werden soll | on-hold: Planeintrag ist pausiert, die Therapie ist unterbrochen (Wiederaufnahme vorgesehen) | completed: Therapie gemäß Planeintrag wie geplant durchgeführt und abgeschlossen | stopped: Therapie gemäß Planeintrag vorzeitig gestoppt und abgeschlossen | entered-in-error: Fehlerhafter Planeintrag storniert und abgeschlossen.</t>
+  </si>
+  <si>
+    <t>A code specifying the current state of the order.  Generally, this will be active or completed state.</t>
   </si>
   <si>
     <t>This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
@@ -617,7 +611,7 @@
 </t>
   </si>
   <si>
-    <t>Grund für den aktuellen Status des Medikationsplaneintrags: (ex) https://hl7.org/fhir/R4/valueset-medicationrequest-status-reason.html. TODO: Verwendung fachlich zu prüfen im Zusammenhang mit Status.</t>
+    <t>Grund für den aktuellen Status des Medikationsplaneintrags: (ex) https://hl7.org/fhir/R4/valueset-medicationrequest-status-reason.html.</t>
   </si>
   <si>
     <t>Captures the reason for the current state of the MedicationRequest.</t>
@@ -3745,7 +3739,7 @@
         <v>80</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T20:12:42+00:00</t>
+    <t>2026-04-14T10:13:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2497" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2499" uniqueCount="501">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T10:13:14+00:00</t>
+    <t>2026-04-17T19:15:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -88,7 +88,7 @@
   </si>
   <si>
     <t>Ein Medikationsplaneintrag im Medikationsplan eines ELGA-Teilnehmers bzw. einer ELGA-Teilnehmerin wird durch eine "MedicationRequest"-Ressource abgebildet.
-Die Ressource enthält genau ein Medikament mit der zugehörigen Dosierung, wobei das Medikament verpflichtend in einer contained Medication-Ressource (inline), also innerhalb der Ressource, dokumentiert wird.
+Die Ressource enthält genau ein Medikament mit der zugehörigen Dosierung, wobei das Medikament verpflichtend in einer contained Medication-Ressource (inline, d.h. innerhalb der Ressource), dokumentiert wird.
 Der Medikationsplaneintrag kann in weiterer Folge als Grundlage für die Erstellung einer geplanten Abgabe dienen. Es werden R5-Backport-Extensions verwendet.</t>
   </si>
   <si>
@@ -271,7 +271,7 @@
 </t>
   </si>
   <si>
-    <t>Ordering of medication for patient or group</t>
+    <t>Medikationsplaneintrag</t>
   </si>
   <si>
     <t>An order or request for both supply of the medication and the instructions for administration of the medication to a patient. The resource is called "MedicationRequest" rather than "MedicationPrescription" or "MedicationOrder" to generalize the use across inpatient and outpatient settings, including care plans, etc., and to harmonize with workflow patterns.</t>
@@ -477,6 +477,10 @@
     <t>Zeitraum, über den die Medikation eingenommen werden soll. Wenn mehrere dosageInstruction-Zeilen vorhanden sind (z. B. bei einer ausschleichenden Dosierung), entspricht dieser Zeitraum dem frühesten Startdatum und dem spätesten Enddatum der dosageInstructions.</t>
   </si>
   <si>
+    <t>Element `MedicationRequest.effectiveDosePeriod` has a context of MedicationRequest based on following the parent source element upwards and mapping to `MedicationRequest`.
+Element `MedicationRequest.effectiveDosePeriod` has no mapping targets in FHIR R4. Typically, this is because the element has been added (is a new element).</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
@@ -494,7 +498,11 @@
     <t>Vollständige Darstellung der Dosierungsanweisungen</t>
   </si>
   <si>
-    <t>Optional Extension Element - found in all resources.</t>
+    <t>R5: `MedicationRequest.renderedDosageInstruction` (new:markdown)</t>
+  </si>
+  <si>
+    <t>Element `MedicationRequest.renderedDosageInstruction` has a context of MedicationRequest based on following the parent source element upwards and mapping to `MedicationRequest`.
+Element `MedicationRequest.renderedDosageInstruction` has no mapping targets in FHIR R4. Typically, this is because the element has been added (is a new element).</t>
   </si>
   <si>
     <t>MedicationRequest.extension:offLabelUse</t>
@@ -3059,7 +3067,9 @@
       <c r="M10" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="N10" s="2"/>
+      <c r="N10" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>21</v>
@@ -3117,7 +3127,7 @@
         <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>141</v>
@@ -3129,7 +3139,7 @@
         <v>21</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>21</v>
@@ -3140,13 +3150,13 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B11" t="s" s="2">
         <v>134</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>21</v>
@@ -3168,15 +3178,17 @@
         <v>21</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="N11" s="2"/>
+        <v>153</v>
+      </c>
+      <c r="N11" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>21</v>
@@ -3234,7 +3246,7 @@
         <v>81</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>141</v>
@@ -3246,7 +3258,7 @@
         <v>21</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="AN11" t="s" s="2">
         <v>21</v>
@@ -3257,13 +3269,13 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>134</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>21</v>
@@ -3285,13 +3297,13 @@
         <v>21</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3351,7 +3363,7 @@
         <v>81</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>141</v>
@@ -3374,14 +3386,14 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -3403,16 +3415,16 @@
         <v>135</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O13" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>21</v>
@@ -3461,7 +3473,7 @@
         <v>21</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3493,10 +3505,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3519,16 +3531,16 @@
         <v>21</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3578,7 +3590,7 @@
         <v>21</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -3593,27 +3605,27 @@
         <v>102</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3639,13 +3651,13 @@
         <v>110</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3671,11 +3683,11 @@
         <v>21</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Y15" s="2"/>
       <c r="Z15" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>21</v>
@@ -3693,7 +3705,7 @@
         <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>90</v>
@@ -3708,16 +3720,16 @@
         <v>102</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>21</v>
@@ -3725,10 +3737,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3751,16 +3763,16 @@
         <v>21</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3786,13 +3798,13 @@
         <v>21</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>21</v>
@@ -3810,7 +3822,7 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3825,13 +3837,13 @@
         <v>102</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>21</v>
@@ -3842,10 +3854,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3871,13 +3883,13 @@
         <v>110</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3888,7 +3900,7 @@
         <v>21</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>21</v>
@@ -3903,13 +3915,13 @@
         <v>21</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>21</v>
@@ -3927,7 +3939,7 @@
         <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>90</v>
@@ -3942,16 +3954,16 @@
         <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>21</v>
@@ -3959,10 +3971,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3985,16 +3997,16 @@
         <v>21</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4005,7 +4017,7 @@
         <v>21</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="T18" t="s" s="2">
         <v>21</v>
@@ -4020,13 +4032,13 @@
         <v>21</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>21</v>
@@ -4044,7 +4056,7 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4062,13 +4074,13 @@
         <v>21</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>21</v>
@@ -4076,10 +4088,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4105,10 +4117,10 @@
         <v>110</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4135,13 +4147,13 @@
         <v>21</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>21</v>
@@ -4159,7 +4171,7 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4174,16 +4186,16 @@
         <v>102</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>21</v>
@@ -4191,10 +4203,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4217,16 +4229,16 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4276,7 +4288,7 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4297,7 +4309,7 @@
         <v>21</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>21</v>
@@ -4308,10 +4320,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4334,13 +4346,13 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4379,17 +4391,17 @@
         <v>21</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AC21" s="2"/>
       <c r="AD21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4410,7 +4422,7 @@
         <v>21</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>21</v>
@@ -4421,13 +4433,13 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>21</v>
@@ -4449,13 +4461,13 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4506,7 +4518,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4527,7 +4539,7 @@
         <v>21</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>21</v>
@@ -4538,13 +4550,13 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>21</v>
@@ -4566,13 +4578,13 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4623,7 +4635,7 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4644,7 +4656,7 @@
         <v>21</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>21</v>
@@ -4655,10 +4667,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4681,16 +4693,16 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4740,7 +4752,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>90</v>
@@ -4755,27 +4767,27 @@
         <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4798,16 +4810,16 @@
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4857,7 +4869,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>90</v>
@@ -4872,27 +4884,27 @@
         <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4915,16 +4927,16 @@
         <v>21</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4974,7 +4986,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4989,27 +5001,27 @@
         <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5032,13 +5044,13 @@
         <v>21</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5089,7 +5101,7 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5104,16 +5116,16 @@
         <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>21</v>
@@ -5121,10 +5133,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5147,13 +5159,13 @@
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5204,7 +5216,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5219,27 +5231,27 @@
         <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5262,13 +5274,13 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5319,7 +5331,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5334,16 +5346,16 @@
         <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>21</v>
@@ -5351,10 +5363,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5377,13 +5389,13 @@
         <v>21</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5434,7 +5446,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5449,16 +5461,16 @@
         <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>21</v>
@@ -5466,10 +5478,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5492,16 +5504,16 @@
         <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5527,13 +5539,13 @@
         <v>21</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>21</v>
@@ -5551,7 +5563,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5566,13 +5578,13 @@
         <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>21</v>
@@ -5583,10 +5595,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5609,13 +5621,13 @@
         <v>21</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5666,7 +5678,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5687,10 +5699,10 @@
         <v>21</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>21</v>
@@ -5698,10 +5710,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5724,16 +5736,16 @@
         <v>21</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5759,13 +5771,13 @@
         <v>21</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>21</v>
@@ -5783,7 +5795,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5798,27 +5810,27 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5841,16 +5853,16 @@
         <v>21</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5900,7 +5912,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5915,16 +5927,16 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>21</v>
@@ -5932,10 +5944,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5958,13 +5970,13 @@
         <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6015,7 +6027,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6030,13 +6042,13 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>21</v>
@@ -6047,10 +6059,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6076,10 +6088,10 @@
         <v>104</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6130,7 +6142,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6151,7 +6163,7 @@
         <v>21</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>21</v>
@@ -6162,10 +6174,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6188,13 +6200,13 @@
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6245,7 +6257,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6260,13 +6272,13 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>21</v>
@@ -6277,10 +6289,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6303,17 +6315,17 @@
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>21</v>
@@ -6362,7 +6374,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6377,13 +6389,13 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>21</v>
@@ -6394,10 +6406,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6420,16 +6432,16 @@
         <v>21</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6455,13 +6467,13 @@
         <v>21</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>21</v>
@@ -6479,7 +6491,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6500,7 +6512,7 @@
         <v>21</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>21</v>
@@ -6511,10 +6523,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6537,13 +6549,13 @@
         <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6594,7 +6606,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6609,13 +6621,13 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>21</v>
@@ -6626,10 +6638,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6652,13 +6664,13 @@
         <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6709,7 +6721,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6724,13 +6736,13 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>21</v>
@@ -6741,10 +6753,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6767,16 +6779,16 @@
         <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6826,7 +6838,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6841,13 +6853,13 @@
         <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>21</v>
@@ -6858,10 +6870,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6884,13 +6896,13 @@
         <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6941,7 +6953,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6959,10 +6971,10 @@
         <v>21</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>21</v>
@@ -6973,10 +6985,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6999,13 +7011,13 @@
         <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7056,7 +7068,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7077,7 +7089,7 @@
         <v>21</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>21</v>
@@ -7088,14 +7100,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7117,13 +7129,13 @@
         <v>135</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7173,7 +7185,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7194,7 +7206,7 @@
         <v>21</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>21</v>
@@ -7205,14 +7217,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7234,16 +7246,16 @@
         <v>135</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>21</v>
@@ -7292,7 +7304,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7324,10 +7336,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7350,16 +7362,16 @@
         <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7409,7 +7421,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7430,7 +7442,7 @@
         <v>21</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>21</v>
@@ -7441,10 +7453,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7467,13 +7479,13 @@
         <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7524,7 +7536,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7545,7 +7557,7 @@
         <v>21</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>21</v>
@@ -7556,14 +7568,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7585,13 +7597,13 @@
         <v>135</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7641,7 +7653,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7662,7 +7674,7 @@
         <v>21</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>21</v>
@@ -7673,14 +7685,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7702,16 +7714,16 @@
         <v>135</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>21</v>
@@ -7760,7 +7772,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7792,10 +7804,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7818,13 +7830,13 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7875,7 +7887,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7896,7 +7908,7 @@
         <v>21</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>21</v>
@@ -7907,10 +7919,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7933,13 +7945,13 @@
         <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7990,7 +8002,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8011,7 +8023,7 @@
         <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>21</v>
@@ -8022,10 +8034,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8048,13 +8060,13 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8105,7 +8117,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8126,7 +8138,7 @@
         <v>21</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>21</v>
@@ -8137,10 +8149,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8163,19 +8175,19 @@
         <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>21</v>
@@ -8224,7 +8236,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8242,10 +8254,10 @@
         <v>21</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>21</v>
@@ -8256,10 +8268,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8282,16 +8294,16 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8341,7 +8353,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8359,24 +8371,24 @@
         <v>21</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8399,13 +8411,13 @@
         <v>21</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8456,7 +8468,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8474,24 +8486,24 @@
         <v>21</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8514,16 +8526,16 @@
         <v>21</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8573,7 +8585,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8591,10 +8603,10 @@
         <v>21</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>21</v>
@@ -8605,10 +8617,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8631,13 +8643,13 @@
         <v>21</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8688,7 +8700,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8709,10 +8721,10 @@
         <v>21</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>21</v>
@@ -8720,10 +8732,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8746,13 +8758,13 @@
         <v>21</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8803,7 +8815,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -8821,10 +8833,10 @@
         <v>21</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>21</v>
@@ -8835,10 +8847,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8861,13 +8873,13 @@
         <v>21</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8918,7 +8930,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -8939,7 +8951,7 @@
         <v>21</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>21</v>
@@ -8950,14 +8962,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -8979,13 +8991,13 @@
         <v>135</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9035,7 +9047,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9056,7 +9068,7 @@
         <v>21</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>21</v>
@@ -9067,14 +9079,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9096,16 +9108,16 @@
         <v>135</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>21</v>
@@ -9154,7 +9166,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9186,10 +9198,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9212,16 +9224,16 @@
         <v>21</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9247,13 +9259,13 @@
         <v>21</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>21</v>
@@ -9271,7 +9283,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>90</v>
@@ -9289,24 +9301,24 @@
         <v>21</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9329,13 +9341,13 @@
         <v>21</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9362,13 +9374,13 @@
         <v>21</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>21</v>
@@ -9386,7 +9398,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9404,24 +9416,24 @@
         <v>21</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9444,13 +9456,13 @@
         <v>21</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9501,7 +9513,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9516,13 +9528,13 @@
         <v>102</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>21</v>
@@ -9533,14 +9545,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9559,16 +9571,16 @@
         <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9618,7 +9630,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -9639,7 +9651,7 @@
         <v>21</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>21</v>
@@ -9650,10 +9662,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9676,16 +9688,16 @@
         <v>21</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9735,7 +9747,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -9750,13 +9762,13 @@
         <v>102</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T19:15:07+00:00</t>
+    <t>2026-04-20T08:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T08:20:06+00:00</t>
+    <t>2026-04-20T16:24:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2499" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2499" uniqueCount="500">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T16:24:35+00:00</t>
+    <t>2026-04-20T19:04:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -551,17 +551,10 @@
 </t>
   </si>
   <si>
-    <t>Medikationsplaneintrag-ID. TODO: Verwendung einer logischen Medikationsplaneintrag-ID prüfen. Details zur Herstellung von Bezügen von geänderten Planeinträgen, siehe Definition.</t>
-  </si>
-  <si>
-    <t>Medikationsplaneintrag-ID.
-Evt. mit Zeitstempel (Planeintrag-ID_{Zeitstempel}) zur Herstellung eines Bezugs von geänderten Planeinträgen.
-Vorteil: 
-- Auch wenn sich die PZN ändert, aber logisch der gleiche Eintrag betroffen ist (z.B. Austausch eines Arzneimittels durch ein anderes mit weniger Wechselwirkung), kann ein Bezug hergestellt werden.
-- Wenn zur Vorversion des Eintrags bereits eine geplante Abgabe erstellt wurde, kann ein Bezug zum ursprünglichen Eintrag hergestellt werden.
-Nachteil: 
-- Falls Planeinträge mit komplett neuer Arznei überschrieben werden, entsteht dadurch ein verwirrender Bezug. 
-- Die Verantwortung, dass nur Einträge geändert werden, die keine komplett neue Medikation beinhalten, liegt beim Ersteller des Eintrags.</t>
+    <t>Medikationsplaneintrag-ID.</t>
+  </si>
+  <si>
+    <t>Identifiers associated with this medication request that are defined by business processes and/or used to refer to it when a direct URL reference to the resource itself is not appropriate. They are business identifiers assigned to this resource by the performer or other systems and remain constant as the resource is updated and propagates from server to server.</t>
   </si>
   <si>
     <t>This is a business identifier, not a resource identifier.</t>
@@ -799,7 +792,7 @@
     <t>reportedBoolean</t>
   </si>
   <si>
-    <t>TRUE im Falle der Dokumentation von Fremdmedikation (ein anderer Arzt hat das Medikament ursprünglich verordnet), sonst FALSE. TODO: Klären ob hier der GDA eindeutig identifiziert sein muss (im GDA-I vorhanden) oder analog zu e-Impfpass Freitext sein kann. Juristisch Verantwortlichkeit für Korrektheit des Eintrags zu klären.</t>
+    <t>TRUE im Falle der Dokumentation von Fremdmedikation (ein anderer Arzt hat das Medikament ursprünglich verordnet), sonst FALSE.</t>
   </si>
   <si>
     <t>MedicationRequest.medication[x]</t>
@@ -973,7 +966,7 @@
 </t>
   </si>
   <si>
-    <t>Der gewünschte Ausführende der medikamentösen Behandlung (z.B. der Ausführende der Medikamentengabe). Keine Verwendung im Planeintrag. TODO: evtl im Kontext Medikationsblatt zu prüfen.</t>
+    <t>Der gewünschte Ausführende der medikamentösen Behandlung (z.B. der Ausführende der Medikamentengabe). Keine Verwendung im Planeintrag.</t>
   </si>
   <si>
     <t>The specified desired performer of the medication treatment (e.g. the performer of the medication administration).</t>
@@ -991,7 +984,7 @@
     <t>MedicationRequest.performerType</t>
   </si>
   <si>
-    <t>Rollen: https://hl7.org/fhir/R4/valueset-performer-role.html. Keine Verwendung im Planeintrag. TODO: evtl im Kontext Medikationsblatt zu prüfen.</t>
+    <t>Rollen: https://hl7.org/fhir/R4/valueset-performer-role.html. Keine Verwendung im Planeintrag.</t>
   </si>
   <si>
     <t>Indicates the type of performer of the administration of the medication.</t>
@@ -1019,7 +1012,7 @@
 </t>
   </si>
   <si>
-    <t>Die Person, die den Medikationsplaneintrag im Auftrag eines GDA eingegeben hat. TODO: Prüfen, ob eine juristische Verpflichtung zur Dokumentation der Schreibkraft besteht.</t>
+    <t>Die Person, die den Medikationsplaneintrag im Auftrag eines GDA eingegeben hat.</t>
   </si>
   <si>
     <t>The person who entered the order on behalf of another individual for example in the case of a verbal or a telephone order.</t>
@@ -1034,7 +1027,7 @@
     <t>MedicationRequest.reasonCode</t>
   </si>
   <si>
-    <t>Grund für die Verordnung des Arzneimittels. Entweder Code oder Referenz (TODO: Evtl. Invariante). Erst wenn codierte Angabe möglich.</t>
+    <t>Grund für die Verordnung des Arzneimittels. Entweder Code oder Referenz. Verwendung erst, wenn codierte Angabe möglich.</t>
   </si>
   <si>
     <t>The reason or the indication for ordering or not ordering the medication.</t>
@@ -1093,7 +1086,7 @@
 </t>
   </si>
   <si>
-    <t>URL, die auf ein Protokoll (Richtlinie, Guideline) verweist, das von diesem Medikationsplaneintrag ganz oder teilweise eingehalten wird. Derzeit keine Verwendung im Medikationsplaneintrag.</t>
+    <t>URL, die auf eine Richtlinie/Guideline verweist, die von diesem Medikationsplaneintrag ganz oder teilweise eingehalten wird. Derzeit keine Verwendung im Medikationsplaneintrag.</t>
   </si>
   <si>
     <t>The URL pointing to a protocol, guideline, orderset, or other definition that is adhered to in whole or in part by this MedicationRequest.</t>
@@ -1108,7 +1101,7 @@
     <t>MedicationRequest.instantiatesUri</t>
   </si>
   <si>
-    <t>URL, die auf ein extern gepflegtes Protokoll (Richtlinie, Guideline) verweist, das von diesem Medikationsplaneintrag ganz oder teilweise eingehalten wird. Derzeit keine Verwendung im Medikationsplaneintrag.</t>
+    <t>URL, die auf eine extern gepflegte Richtlinie/Guideline verweist, die von diesem Medikationsplaneintrag ganz oder teilweise eingehalten wird. Derzeit keine Verwendung im Medikationsplaneintrag.</t>
   </si>
   <si>
     <t>The URL pointing to an externally maintained protocol, guideline, orderset or other definition that is adhered to in whole or in part by this MedicationRequest.</t>
@@ -1121,7 +1114,7 @@
 </t>
   </si>
   <si>
-    <t>TODO: Verwendung im Medikationsplaneintrag zu prüfen. Vermutlich nicht möglich, da keine versionsspezifischen Referenzen verwendet werden.</t>
+    <t>Keine Verwendung im Medikationsplaneintrag.</t>
   </si>
   <si>
     <t>A plan or request that is fulfilled in whole or in part by this medication request.</t>
@@ -1136,7 +1129,7 @@
     <t>MedicationRequest.groupIdentifier</t>
   </si>
   <si>
-    <t>Erst bei der geplanten Abgabe (Rezepterstellung) relevant. Evtl ein Verweis auf erstellte Rezepte? Würde Extension erfordern, da Kardinalität nur 0..1 zulässig</t>
+    <t>Erst bei der geplanten Abgabe (Rezepterstellung) relevant.</t>
   </si>
   <si>
     <t>A shared identifier common to all requests that were authorized more or less simultaneously by a single author, representing the identifier of the requisition or prescription.</t>
@@ -1154,7 +1147,7 @@
     <t>MedicationRequest.courseOfTherapyType</t>
   </si>
   <si>
-    <t>Gesamtmuster der Medikamentengabe. continuous | acute | seasonal. Verwendung im Medikationsplaneintrag prüfen, evtl. durch Dosierungsinformationen abgedeckt.</t>
+    <t>Gesamtmuster der Medikamentengabe. continuous | acute | seasonal.</t>
   </si>
   <si>
     <t>The description of the overall patte3rn of the administration of the medication to the patient.</t>
@@ -1179,9 +1172,6 @@
 </t>
   </si>
   <si>
-    <t>Keine Verwendung im Medikationsplaneintrag.</t>
-  </si>
-  <si>
     <t>Insurance plans, coverage extensions, pre-authorizations and/or pre-determinations that may be required for delivering the requested service.</t>
   </si>
   <si>
@@ -1198,7 +1188,7 @@
 </t>
   </si>
   <si>
-    <t>Zusätzliche Informationen zum Medikationsplaneintrag. TODO: fachlich prüfen, an welchen Stellen überall Freitext erforderlich sein soll/muss. Auch im Kontext zu entered-in-error Informationen.</t>
+    <t>Zusätzliche Informationen zum Medikationsplaneintrag.</t>
   </si>
   <si>
     <t>Extra information about the prescription that could not be conveyed by the other attributes.</t>
@@ -1220,7 +1210,7 @@
 </t>
   </si>
   <si>
-    <t>Angabe der Dosierinformationen strukturiert oder als Freitext. TODO: Inhalte AtEmedDosage fachlich prüfen.</t>
+    <t>Angabe der Dosierinformationen strukturiert oder als Freitext.</t>
   </si>
   <si>
     <t>Indicates how the medication is to be used by the patient.</t>
@@ -1472,7 +1462,7 @@
     <t>MedicationRequest.substitution</t>
   </si>
   <si>
-    <t>Gibt an, ob das Arzneimittel substituiert werden darf oder nicht. Erläutert die Absicht des Arztes, der den Medikationsplaneintrag erstellt. Wenn nichts angegeben ist, kann eine Substitution vorgenommen werden. Die Dokumentation über eine tatsächlich erfolgte Substitution erfolgt in der Dispense-Resource. TODO: Usecase fachlich zu prüfen. Es kann für den Patienten selbst oder das Pflegeheim eine wichtige Information sein, mit welchem Medikament das verordnete Medikament im Bedarfsfall ersetzen werden kann.</t>
+    <t>Gibt an, ob das Arzneimittel substituiert werden darf oder nicht. Erläutert die Absicht des Arztes, der den Medikationsplaneintrag erstellt. Wenn nichts angegeben ist, kann eine Substitution vorgenommen werden.</t>
   </si>
   <si>
     <t>Indicates whether or not substitution can or should be part of the dispense. In some cases, substitution must happen, in other cases substitution must not happen. This block explains the prescriber's intent. If nothing is specified substitution may be done.</t>
@@ -1575,7 +1565,7 @@
 </t>
   </si>
   <si>
-    <t>Klinisches Problem mit Maßnahme. Nur mittesl Referenz auf Ressouce DetectedIssue, Keine Verwendung im Medikationsplaneintrag.</t>
+    <t>Klinisches Problem mit Maßnahme (Referenz auf Ressouce DetectedIssue). Keine Verwendung im Medikationsplaneintrag.</t>
   </si>
   <si>
     <t>Indicates an actual or potential clinical issue with or between one or more active or proposed clinical actions for a patient; e.g. Drug-drug interaction, duplicate therapy, dosage alert etc.</t>
@@ -6552,10 +6542,10 @@
         <v>362</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6621,13 +6611,13 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>21</v>
@@ -6638,10 +6628,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6664,13 +6654,13 @@
         <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6721,7 +6711,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6736,13 +6726,13 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AL41" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="AL41" t="s" s="2">
+      <c r="AM41" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>21</v>
@@ -6753,10 +6743,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6779,16 +6769,16 @@
         <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6838,7 +6828,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6853,13 +6843,13 @@
         <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="AL42" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>21</v>
@@ -6870,10 +6860,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6896,13 +6886,13 @@
         <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6953,7 +6943,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6971,10 +6961,10 @@
         <v>21</v>
       </c>
       <c r="AL43" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AM43" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>21</v>
@@ -6985,10 +6975,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7011,13 +7001,13 @@
         <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7068,7 +7058,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7089,7 +7079,7 @@
         <v>21</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>21</v>
@@ -7100,10 +7090,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7129,10 +7119,10 @@
         <v>135</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>164</v>
@@ -7185,7 +7175,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7206,7 +7196,7 @@
         <v>21</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>21</v>
@@ -7217,14 +7207,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7246,10 +7236,10 @@
         <v>135</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>164</v>
@@ -7304,7 +7294,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7336,10 +7326,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7362,16 +7352,16 @@
         <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7421,7 +7411,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7442,7 +7432,7 @@
         <v>21</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>21</v>
@@ -7453,10 +7443,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7479,13 +7469,13 @@
         <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7536,7 +7526,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7557,7 +7547,7 @@
         <v>21</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>21</v>
@@ -7568,10 +7558,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7597,10 +7587,10 @@
         <v>135</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>164</v>
@@ -7653,7 +7643,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7674,7 +7664,7 @@
         <v>21</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>21</v>
@@ -7685,14 +7675,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7714,10 +7704,10 @@
         <v>135</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="N50" t="s" s="2">
         <v>164</v>
@@ -7772,7 +7762,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7804,10 +7794,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7830,13 +7820,13 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7887,7 +7877,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7908,7 +7898,7 @@
         <v>21</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>21</v>
@@ -7919,10 +7909,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7945,13 +7935,13 @@
         <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8002,7 +7992,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8023,7 +8013,7 @@
         <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>21</v>
@@ -8034,10 +8024,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8060,13 +8050,13 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8117,7 +8107,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8138,7 +8128,7 @@
         <v>21</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>21</v>
@@ -8149,10 +8139,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8175,19 +8165,19 @@
         <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="N54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>21</v>
@@ -8236,7 +8226,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8254,10 +8244,10 @@
         <v>21</v>
       </c>
       <c r="AL54" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AM54" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>21</v>
@@ -8268,10 +8258,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8294,16 +8284,16 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8353,7 +8343,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8371,24 +8361,24 @@
         <v>21</v>
       </c>
       <c r="AL55" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="AM55" t="s" s="2">
+      <c r="AN55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO55" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>438</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8411,13 +8401,13 @@
         <v>21</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8468,7 +8458,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8486,24 +8476,24 @@
         <v>21</v>
       </c>
       <c r="AL56" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AM56" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="AM56" t="s" s="2">
+      <c r="AN56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO56" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>444</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8526,16 +8516,16 @@
         <v>21</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8585,7 +8575,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8603,10 +8593,10 @@
         <v>21</v>
       </c>
       <c r="AL57" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AM57" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>21</v>
@@ -8617,10 +8607,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8643,13 +8633,13 @@
         <v>21</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8700,7 +8690,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8721,7 +8711,7 @@
         <v>21</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>314</v>
@@ -8732,10 +8722,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8758,13 +8748,13 @@
         <v>21</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8815,7 +8805,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -8833,10 +8823,10 @@
         <v>21</v>
       </c>
       <c r="AL59" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>21</v>
@@ -8847,10 +8837,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8873,13 +8863,13 @@
         <v>21</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8930,7 +8920,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -8951,7 +8941,7 @@
         <v>21</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>21</v>
@@ -8962,10 +8952,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8991,10 +8981,10 @@
         <v>135</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="N61" t="s" s="2">
         <v>164</v>
@@ -9047,7 +9037,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9068,7 +9058,7 @@
         <v>21</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>21</v>
@@ -9079,14 +9069,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9108,10 +9098,10 @@
         <v>135</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="N62" t="s" s="2">
         <v>164</v>
@@ -9166,7 +9156,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9198,10 +9188,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9224,16 +9214,16 @@
         <v>21</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>468</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9262,11 +9252,11 @@
         <v>192</v>
       </c>
       <c r="Y63" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="Z63" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="Z63" t="s" s="2">
-        <v>470</v>
-      </c>
       <c r="AA63" t="s" s="2">
         <v>21</v>
       </c>
@@ -9283,7 +9273,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>90</v>
@@ -9301,24 +9291,24 @@
         <v>21</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AM63" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO63" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>472</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9344,10 +9334,10 @@
         <v>188</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9377,11 +9367,11 @@
         <v>192</v>
       </c>
       <c r="Y64" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="Z64" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="Z64" t="s" s="2">
-        <v>477</v>
-      </c>
       <c r="AA64" t="s" s="2">
         <v>21</v>
       </c>
@@ -9398,7 +9388,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9416,24 +9406,24 @@
         <v>21</v>
       </c>
       <c r="AL64" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AM64" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="AM64" t="s" s="2">
+      <c r="AN64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO64" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>480</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9456,13 +9446,13 @@
         <v>21</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
         <v>483</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>484</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9513,7 +9503,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9528,13 +9518,13 @@
         <v>102</v>
       </c>
       <c r="AK65" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AM65" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>486</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>21</v>
@@ -9545,14 +9535,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9571,16 +9561,16 @@
         <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9630,7 +9620,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -9651,7 +9641,7 @@
         <v>21</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>21</v>
@@ -9662,10 +9652,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9688,16 +9678,16 @@
         <v>21</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="L67" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="L67" t="s" s="2">
+      <c r="M67" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9747,7 +9737,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -9762,13 +9752,13 @@
         <v>102</v>
       </c>
       <c r="AK67" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM67" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="AL67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>500</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T19:04:12+00:00</t>
+    <t>2026-04-21T08:44:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T08:44:51+00:00</t>
+    <t>2026-04-21T11:54:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T11:54:48+00:00</t>
+    <t>2026-04-21T14:09:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T14:09:10+00:00</t>
+    <t>2026-04-21T17:01:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T17:01:26+00:00</t>
+    <t>2026-04-22T08:49:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-22T08:49:17+00:00</t>
+    <t>2026-04-22T10:01:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-22T10:01:54+00:00</t>
+    <t>2026-04-22T10:11:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-22T10:11:27+00:00</t>
+    <t>2026-04-28T11:58:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$71</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2499" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2648" uniqueCount="519">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-28T11:58:02+00:00</t>
+    <t>2026-04-29T14:27:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -612,7 +612,7 @@
 </t>
   </si>
   <si>
-    <t>Grund für den aktuellen Status des Medikationsplaneintrags: (ex) https://hl7.org/fhir/R4/valueset-medicationrequest-status-reason.html.</t>
+    <t>Reason for current status</t>
   </si>
   <si>
     <t>Captures the reason for the current state of the MedicationRequest.</t>
@@ -634,6 +634,92 @@
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ].source[classCode=CACT, moodCode=EVN].reasonCOde</t>
+  </si>
+  <si>
+    <t>MedicationRequest.statusReason.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>MedicationRequest.statusReason.extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.statusReason.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Codierter Grund für den aktuellen Status des Medikationsplaneintrags, z.B. warum ein Medikament abgesetzt wurde. Keine codierte Angabe im Medikationsplaneintrag.</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>MedicationRequest.statusReason.text</t>
+  </si>
+  <si>
+    <t>Grund für den aktuellen Status des Medikationsplaneintrags (Freitext), z.B. warum ein Medikament abgesetzt wurde.</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
   </si>
   <si>
     <t>MedicationRequest.intent</t>
@@ -753,10 +839,6 @@
     <t>MedicationRequest.reported[x]</t>
   </si>
   <si>
-    <t>boolean
-Reference(Patient|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)</t>
-  </si>
-  <si>
     <t>Reported rather than primary record</t>
   </si>
   <si>
@@ -779,11 +861,11 @@
     <t>reportedReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Practitioner|PractitionerRole)
+    <t xml:space="preserve">Reference(Patient|Practitioner|PractitionerRole|RelatedPerson|Organization)
 </t>
   </si>
   <si>
-    <t>Im Falle einer Fremdmedikation Angabe einer Referenz auf: (Patient | Practitioner | PractitionerRole | RelatedPerson | Organization)</t>
+    <t>Im Falle einer Fremdmedikation Angabe einer Referenz auf: (Patient | Practitioner | PractitionerRole | RelatedPerson | Organization). Keine Verwendung im Medikationsplan.</t>
   </si>
   <si>
     <t>MedicationRequest.reported[x]:reportedBoolean</t>
@@ -1247,32 +1329,7 @@
     <t>MedicationRequest.dispenseRequest.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>MedicationRequest.dispenseRequest.extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>MedicationRequest.dispenseRequest.modifierExtension</t>
@@ -1921,7 +1978,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO67"/>
+  <dimension ref="A1:AO71"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="51.68359375" customWidth="true" bestFit="true"/>
@@ -1952,7 +2009,7 @@
     <col min="26" max="26" width="61.125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="50.90625" customWidth="true" bestFit="true" hidden="true"/>
@@ -3842,7 +3899,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
         <v>197</v>
       </c>
@@ -3855,32 +3912,30 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>110</v>
+        <v>198</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N17" t="s" s="2">
         <v>200</v>
       </c>
+      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>21</v>
@@ -3890,49 +3945,49 @@
         <v>21</v>
       </c>
       <c r="S17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="T17" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U17" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V17" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W17" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X17" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="Z17" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>197</v>
-      </c>
       <c r="AG17" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>90</v>
@@ -3941,44 +3996,44 @@
         <v>21</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>204</v>
+        <v>21</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>206</v>
+        <v>21</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>21</v>
@@ -3987,16 +4042,16 @@
         <v>21</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>188</v>
+        <v>135</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>210</v>
+        <v>164</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4007,7 +4062,7 @@
         <v>21</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>211</v>
+        <v>21</v>
       </c>
       <c r="T18" t="s" s="2">
         <v>21</v>
@@ -4022,28 +4077,28 @@
         <v>21</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>192</v>
+        <v>21</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>212</v>
+        <v>21</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>213</v>
+        <v>21</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>21</v>
+        <v>206</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AF18" t="s" s="2">
         <v>207</v>
@@ -4058,19 +4113,19 @@
         <v>21</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>214</v>
+        <v>21</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>206</v>
+        <v>21</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>21</v>
@@ -4078,10 +4133,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4104,16 +4159,20 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>110</v>
+        <v>209</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
+        <v>211</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="O19" t="s" s="2">
+        <v>213</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>21</v>
       </c>
@@ -4137,13 +4196,13 @@
         <v>21</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>181</v>
+        <v>21</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>219</v>
+        <v>21</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>220</v>
+        <v>21</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>21</v>
@@ -4161,13 +4220,13 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>21</v>
@@ -4176,27 +4235,27 @@
         <v>102</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>221</v>
+        <v>21</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>223</v>
+        <v>21</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>21</v>
+        <v>216</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4207,30 +4266,32 @@
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J20" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>225</v>
+        <v>198</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="O20" s="2"/>
+        <v>220</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>21</v>
       </c>
@@ -4278,7 +4339,7 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4299,21 +4360,21 @@
         <v>21</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>21</v>
+        <v>224</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4330,21 +4391,23 @@
         <v>91</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J21" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>231</v>
+        <v>110</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>227</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>21</v>
@@ -4354,7 +4417,7 @@
         <v>21</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>21</v>
+        <v>229</v>
       </c>
       <c r="T21" t="s" s="2">
         <v>21</v>
@@ -4369,32 +4432,34 @@
         <v>21</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>21</v>
+        <v>181</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>21</v>
+        <v>230</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>21</v>
+        <v>231</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="AC21" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>235</v>
+        <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>90</v>
@@ -4406,60 +4471,60 @@
         <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>21</v>
+        <v>232</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>21</v>
+        <v>234</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="C22" t="s" s="2">
-        <v>238</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>239</v>
+        <v>188</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>237</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>21</v>
@@ -4469,7 +4534,7 @@
         <v>21</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="T22" t="s" s="2">
         <v>21</v>
@@ -4484,13 +4549,13 @@
         <v>21</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>21</v>
+        <v>192</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>21</v>
+        <v>240</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>21</v>
+        <v>241</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>21</v>
@@ -4508,13 +4573,13 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>21</v>
@@ -4526,13 +4591,13 @@
         <v>21</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>21</v>
+        <v>242</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>21</v>
+        <v>234</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>21</v>
@@ -4540,14 +4605,12 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="C23" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
         <v>21</v>
       </c>
@@ -4556,7 +4619,7 @@
         <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>21</v>
@@ -4568,13 +4631,13 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>225</v>
+        <v>110</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4601,13 +4664,13 @@
         <v>21</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>21</v>
+        <v>181</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>21</v>
+        <v>247</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>21</v>
+        <v>248</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>21</v>
@@ -4625,7 +4688,7 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4640,27 +4703,27 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>21</v>
+        <v>249</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>21</v>
+        <v>251</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4668,31 +4731,31 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H24" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I24" t="s" s="2">
         <v>91</v>
-      </c>
-      <c r="I24" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4742,10 +4805,10 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>90</v>
@@ -4757,27 +4820,27 @@
         <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>249</v>
+        <v>21</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>250</v>
+        <v>21</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>252</v>
+        <v>21</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>253</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4791,7 +4854,7 @@
         <v>90</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>21</v>
@@ -4800,17 +4863,15 @@
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>258</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>21</v>
@@ -4847,22 +4908,20 @@
         <v>21</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="AC25" s="2"/>
       <c r="AD25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>21</v>
+        <v>262</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>90</v>
@@ -4874,19 +4933,19 @@
         <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>259</v>
+        <v>21</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>260</v>
+        <v>21</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>262</v>
+        <v>21</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>263</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" hidden="true">
@@ -4894,9 +4953,11 @@
         <v>264</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="C26" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="D26" t="s" s="2">
         <v>21</v>
       </c>
@@ -4914,20 +4975,18 @@
         <v>21</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>268</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>21</v>
@@ -4976,7 +5035,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4991,29 +5050,31 @@
         <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AN26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO26" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="C27" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="AL26" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="27" hidden="true">
-      <c r="A27" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>21</v>
       </c>
@@ -5022,25 +5083,25 @@
         <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>274</v>
+        <v>253</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>276</v>
+        <v>260</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5091,13 +5152,13 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>273</v>
+        <v>258</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>21</v>
@@ -5106,16 +5167,16 @@
         <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>277</v>
+        <v>21</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>271</v>
+        <v>21</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>21</v>
@@ -5123,10 +5184,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5149,15 +5210,17 @@
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>274</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>275</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>21</v>
@@ -5206,10 +5269,10 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>90</v>
@@ -5221,27 +5284,27 @@
         <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>287</v>
+        <v>280</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5264,15 +5327,17 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>284</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>285</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>21</v>
@@ -5321,10 +5386,10 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>90</v>
@@ -5336,27 +5401,27 @@
         <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>21</v>
+        <v>287</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>261</v>
+        <v>288</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>21</v>
+        <v>290</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5379,15 +5444,17 @@
         <v>21</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="N30" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="L30" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>21</v>
@@ -5436,7 +5503,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5451,27 +5518,27 @@
         <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="AL30" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AO30" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>21</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5491,10 +5558,10 @@
         <v>21</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>188</v>
+        <v>301</v>
       </c>
       <c r="L31" t="s" s="2">
         <v>302</v>
@@ -5502,9 +5569,7 @@
       <c r="M31" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="N31" t="s" s="2">
-        <v>304</v>
-      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>21</v>
@@ -5529,13 +5594,13 @@
         <v>21</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>192</v>
+        <v>21</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>305</v>
+        <v>21</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>306</v>
+        <v>21</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>21</v>
@@ -5553,13 +5618,13 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>21</v>
@@ -5568,27 +5633,27 @@
         <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>21</v>
+        <v>298</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5596,28 +5661,28 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5668,7 +5733,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5683,22 +5748,22 @@
         <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>21</v>
+        <v>310</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>21</v>
+        <v>311</v>
       </c>
       <c r="AM32" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="AN32" t="s" s="2">
+      <c r="AO32" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="AO32" t="s" s="2">
-        <v>21</v>
-      </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>315</v>
       </c>
@@ -5711,32 +5776,30 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>188</v>
+        <v>316</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="N33" t="s" s="2">
         <v>318</v>
       </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>21</v>
@@ -5761,13 +5824,13 @@
         <v>21</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>192</v>
+        <v>21</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>319</v>
+        <v>21</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>320</v>
+        <v>21</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>21</v>
@@ -5791,7 +5854,7 @@
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>21</v>
@@ -5800,27 +5863,27 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>322</v>
+        <v>21</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>323</v>
+        <v>288</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>325</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5843,17 +5906,15 @@
         <v>21</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>21</v>
@@ -5902,13 +5963,13 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>21</v>
@@ -5917,16 +5978,16 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>184</v>
+        <v>21</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>21</v>
@@ -5934,10 +5995,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5960,15 +6021,17 @@
         <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>334</v>
+        <v>188</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>330</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>331</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>21</v>
@@ -5993,13 +6056,13 @@
         <v>21</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>21</v>
+        <v>192</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>21</v>
+        <v>332</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>21</v>
+        <v>333</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>21</v>
@@ -6017,13 +6080,13 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>21</v>
@@ -6032,13 +6095,13 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>21</v>
@@ -6049,10 +6112,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6072,16 +6135,16 @@
         <v>21</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>104</v>
+        <v>337</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6132,13 +6195,13 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>21</v>
@@ -6153,10 +6216,10 @@
         <v>21</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>21</v>
+        <v>341</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>21</v>
@@ -6187,18 +6250,20 @@
         <v>21</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>21</v>
@@ -6223,13 +6288,13 @@
         <v>21</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>21</v>
+        <v>192</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>21</v>
+        <v>346</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>21</v>
+        <v>347</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>21</v>
@@ -6262,27 +6327,27 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>21</v>
+        <v>349</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>21</v>
+        <v>351</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>21</v>
+        <v>352</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6302,21 +6367,21 @@
         <v>21</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>168</v>
+        <v>354</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" t="s" s="2">
-        <v>351</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>21</v>
       </c>
@@ -6364,13 +6429,13 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>21</v>
@@ -6379,27 +6444,27 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>21</v>
+        <v>184</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>21</v>
+        <v>351</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6410,29 +6475,27 @@
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J39" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I39" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J39" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K39" t="s" s="2">
-        <v>188</v>
+        <v>361</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>357</v>
-      </c>
+        <v>363</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>21</v>
@@ -6457,13 +6520,13 @@
         <v>21</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>192</v>
+        <v>21</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>358</v>
+        <v>21</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>359</v>
+        <v>21</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>21</v>
@@ -6481,13 +6544,13 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>21</v>
@@ -6496,13 +6559,13 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>21</v>
+        <v>364</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>21</v>
@@ -6513,10 +6576,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6536,16 +6599,16 @@
         <v>21</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>362</v>
+        <v>104</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>344</v>
+        <v>367</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6596,7 +6659,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6611,7 +6674,7 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>364</v>
+        <v>21</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>21</v>
@@ -6626,12 +6689,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6642,25 +6705,25 @@
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J41" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I41" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J41" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K41" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6711,7 +6774,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6726,13 +6789,13 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>371</v>
+        <v>21</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>21</v>
@@ -6741,12 +6804,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6754,33 +6817,33 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J42" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I42" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J42" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K42" t="s" s="2">
-        <v>374</v>
+        <v>168</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="N42" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="O42" s="2"/>
+      <c r="N42" s="2"/>
+      <c r="O42" t="s" s="2">
+        <v>378</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>21</v>
       </c>
@@ -6828,13 +6891,13 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>21</v>
@@ -6843,13 +6906,13 @@
         <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>21</v>
@@ -6858,12 +6921,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6874,10 +6937,10 @@
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>21</v>
@@ -6886,7 +6949,7 @@
         <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>381</v>
+        <v>188</v>
       </c>
       <c r="L43" t="s" s="2">
         <v>382</v>
@@ -6894,7 +6957,9 @@
       <c r="M43" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="N43" s="2"/>
+      <c r="N43" t="s" s="2">
+        <v>384</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>21</v>
@@ -6919,13 +6984,13 @@
         <v>21</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>21</v>
+        <v>192</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>21</v>
+        <v>385</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>21</v>
+        <v>386</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>21</v>
@@ -6943,7 +7008,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6961,10 +7026,10 @@
         <v>21</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>384</v>
+        <v>21</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>21</v>
@@ -6975,10 +7040,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6989,7 +7054,7 @@
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>21</v>
@@ -7001,13 +7066,13 @@
         <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>388</v>
+        <v>371</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7058,28 +7123,28 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>21</v>
+        <v>391</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>21</v>
@@ -7088,16 +7153,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7107,7 +7172,7 @@
         <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>21</v>
@@ -7116,17 +7181,15 @@
         <v>21</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>135</v>
+        <v>394</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>164</v>
-      </c>
+        <v>396</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>21</v>
@@ -7175,7 +7238,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7187,16 +7250,16 @@
         <v>21</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>21</v>
+        <v>397</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>21</v>
+        <v>398</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>21</v>
@@ -7205,48 +7268,46 @@
         <v>21</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>397</v>
+        <v>21</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>135</v>
+        <v>401</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>165</v>
-      </c>
+        <v>404</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>21</v>
       </c>
@@ -7306,16 +7367,16 @@
         <v>21</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>21</v>
+        <v>405</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>133</v>
+        <v>406</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>21</v>
@@ -7326,10 +7387,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7340,7 +7401,7 @@
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>21</v>
@@ -7352,17 +7413,15 @@
         <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>404</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>21</v>
@@ -7411,7 +7470,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7429,10 +7488,10 @@
         <v>21</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>21</v>
+        <v>411</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>21</v>
@@ -7443,10 +7502,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7469,13 +7528,13 @@
         <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>387</v>
+        <v>198</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>388</v>
+        <v>199</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>389</v>
+        <v>200</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7526,7 +7585,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>390</v>
+        <v>201</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7547,7 +7606,7 @@
         <v>21</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>391</v>
+        <v>202</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>21</v>
@@ -7558,10 +7617,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7587,10 +7646,10 @@
         <v>135</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>393</v>
+        <v>204</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>394</v>
+        <v>205</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>164</v>
@@ -7643,7 +7702,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>395</v>
+        <v>207</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7664,7 +7723,7 @@
         <v>21</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>391</v>
+        <v>202</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>21</v>
@@ -7675,14 +7734,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>397</v>
+        <v>416</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7704,10 +7763,10 @@
         <v>135</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>398</v>
+        <v>417</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>399</v>
+        <v>418</v>
       </c>
       <c r="N50" t="s" s="2">
         <v>164</v>
@@ -7762,7 +7821,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>400</v>
+        <v>419</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7794,10 +7853,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7820,15 +7879,17 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>422</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>423</v>
+      </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>21</v>
@@ -7877,7 +7938,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7898,7 +7959,7 @@
         <v>21</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>413</v>
+        <v>424</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>21</v>
@@ -7909,10 +7970,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>414</v>
+        <v>425</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>414</v>
+        <v>425</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7935,13 +7996,13 @@
         <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>415</v>
+        <v>198</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>416</v>
+        <v>199</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>417</v>
+        <v>200</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7992,7 +8053,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>414</v>
+        <v>201</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8004,7 +8065,7 @@
         <v>21</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>21</v>
@@ -8013,7 +8074,7 @@
         <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>418</v>
+        <v>202</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>21</v>
@@ -8024,21 +8085,21 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>21</v>
@@ -8050,15 +8111,17 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>415</v>
+        <v>135</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>420</v>
+        <v>204</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>205</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>164</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>21</v>
@@ -8107,19 +8170,19 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>419</v>
+        <v>207</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>21</v>
@@ -8128,7 +8191,7 @@
         <v>21</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>418</v>
+        <v>202</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>21</v>
@@ -8139,45 +8202,45 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>21</v>
+        <v>416</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>423</v>
+        <v>135</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>426</v>
+        <v>164</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>427</v>
+        <v>165</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>21</v>
@@ -8226,28 +8289,28 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>428</v>
+        <v>21</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>429</v>
+        <v>133</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>21</v>
@@ -8258,10 +8321,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8284,17 +8347,15 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="L55" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>434</v>
-      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>21</v>
@@ -8343,7 +8404,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8361,24 +8422,24 @@
         <v>21</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>435</v>
+        <v>21</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>437</v>
+        <v>21</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8401,13 +8462,13 @@
         <v>21</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>410</v>
+        <v>434</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8458,7 +8519,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8476,24 +8537,24 @@
         <v>21</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>441</v>
+        <v>21</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>443</v>
+        <v>21</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8516,17 +8577,15 @@
         <v>21</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>415</v>
+        <v>434</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>447</v>
-      </c>
+        <v>440</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>21</v>
@@ -8575,7 +8634,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8593,10 +8652,10 @@
         <v>21</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>448</v>
+        <v>21</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>449</v>
+        <v>437</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>21</v>
@@ -8607,10 +8666,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8633,16 +8692,20 @@
         <v>21</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
+        <v>444</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>446</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>21</v>
       </c>
@@ -8690,7 +8753,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8708,24 +8771,24 @@
         <v>21</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>21</v>
+        <v>447</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>314</v>
+        <v>21</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8739,7 +8802,7 @@
         <v>90</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>21</v>
@@ -8748,15 +8811,17 @@
         <v>21</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>381</v>
+        <v>450</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>452</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>453</v>
+      </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>21</v>
@@ -8805,7 +8870,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -8823,24 +8888,24 @@
         <v>21</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>21</v>
+        <v>456</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8863,13 +8928,13 @@
         <v>21</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>387</v>
+        <v>429</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>388</v>
+        <v>458</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>389</v>
+        <v>459</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8920,7 +8985,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>390</v>
+        <v>457</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -8932,41 +8997,41 @@
         <v>21</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>21</v>
+        <v>460</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>391</v>
+        <v>461</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>21</v>
+        <v>462</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>21</v>
@@ -8978,16 +9043,16 @@
         <v>21</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>135</v>
+        <v>434</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>393</v>
+        <v>464</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>394</v>
+        <v>465</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>164</v>
+        <v>466</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9037,28 +9102,28 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>395</v>
+        <v>463</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>21</v>
+        <v>467</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>391</v>
+        <v>468</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>21</v>
@@ -9069,46 +9134,42 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>397</v>
+        <v>21</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>135</v>
+        <v>470</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>398</v>
+        <v>471</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>165</v>
-      </c>
+        <v>472</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>21</v>
       </c>
@@ -9156,19 +9217,19 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>400</v>
+        <v>469</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>21</v>
@@ -9177,21 +9238,21 @@
         <v>21</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>133</v>
+        <v>473</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>21</v>
+        <v>341</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9199,13 +9260,13 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>21</v>
@@ -9214,17 +9275,15 @@
         <v>21</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>464</v>
+        <v>408</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>465</v>
+        <v>475</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>467</v>
-      </c>
+        <v>476</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>21</v>
@@ -9249,13 +9308,13 @@
         <v>21</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>192</v>
+        <v>21</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>468</v>
+        <v>21</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>469</v>
+        <v>21</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>21</v>
@@ -9273,10 +9332,10 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>90</v>
@@ -9291,24 +9350,24 @@
         <v>21</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>458</v>
+        <v>477</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>471</v>
+        <v>21</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9331,13 +9390,13 @@
         <v>21</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>473</v>
+        <v>199</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>474</v>
+        <v>200</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9364,13 +9423,13 @@
         <v>21</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>192</v>
+        <v>21</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>475</v>
+        <v>21</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>476</v>
+        <v>21</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>21</v>
@@ -9388,7 +9447,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>472</v>
+        <v>201</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9400,25 +9459,25 @@
         <v>21</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>477</v>
+        <v>21</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>478</v>
+        <v>202</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>479</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
         <v>480</v>
       </c>
@@ -9427,17 +9486,17 @@
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>21</v>
@@ -9446,15 +9505,17 @@
         <v>21</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>481</v>
+        <v>135</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>482</v>
+        <v>204</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>205</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>164</v>
+      </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>21</v>
@@ -9503,28 +9564,28 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>480</v>
+        <v>207</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>484</v>
+        <v>21</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>477</v>
+        <v>21</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>485</v>
+        <v>202</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>21</v>
@@ -9535,44 +9596,46 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>487</v>
+        <v>416</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>488</v>
+        <v>135</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>489</v>
+        <v>417</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>490</v>
+        <v>418</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="O66" s="2"/>
+        <v>164</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>165</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>21</v>
       </c>
@@ -9620,7 +9683,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>486</v>
+        <v>419</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -9632,7 +9695,7 @@
         <v>21</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>21</v>
@@ -9641,7 +9704,7 @@
         <v>21</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>492</v>
+        <v>133</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>21</v>
@@ -9652,10 +9715,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>493</v>
+        <v>482</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>493</v>
+        <v>482</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9663,10 +9726,10 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>21</v>
@@ -9678,16 +9741,16 @@
         <v>21</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>494</v>
+        <v>483</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>495</v>
+        <v>484</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>496</v>
+        <v>485</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>497</v>
+        <v>486</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9713,13 +9776,13 @@
         <v>21</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>21</v>
+        <v>192</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>21</v>
+        <v>487</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>21</v>
+        <v>488</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>21</v>
@@ -9737,13 +9800,13 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>493</v>
+        <v>482</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>21</v>
@@ -9752,23 +9815,487 @@
         <v>102</v>
       </c>
       <c r="AK67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
+      <c r="P68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO68" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="AL67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM67" t="s" s="2">
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="AN67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO67" t="s" s="2">
+      <c r="B69" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO71" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO67">
+  <autoFilter ref="A1:AO71">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9778,7 +10305,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI66">
+  <conditionalFormatting sqref="A2:AI70">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T14:27:58+00:00</t>
+    <t>2026-04-30T15:16:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T15:16:21+00:00</t>
+    <t>2026-04-30T15:23:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T15:23:35+00:00</t>
+    <t>2026-05-04T14:46:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-planeintrag.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$70</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2648" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2611" uniqueCount="514">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T14:46:25+00:00</t>
+    <t>2026-05-08T13:20:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -503,22 +503,6 @@
   <si>
     <t>Element `MedicationRequest.renderedDosageInstruction` has a context of MedicationRequest based on following the parent source element upwards and mapping to `MedicationRequest`.
 Element `MedicationRequest.renderedDosageInstruction` has no mapping targets in FHIR R4. Typically, this is because the element has been added (is a new element).</t>
-  </si>
-  <si>
-    <t>MedicationRequest.extension:offLabelUse</t>
-  </si>
-  <si>
-    <t>offLabelUse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://profiles.ihe.net/PHARM/MPD/StructureDefinition/ihe-ext-offLabel}
-</t>
-  </si>
-  <si>
-    <t>Weist darauf hin, dass der verschreibende Arzt das Medikament wissentlich für eine Indikation, Altersgruppe, Dosierung oder Verabreichungsform verschrieben hat, die nicht von den Aufsichtsbehörden zugelassen ist und in der Verschreibungsinformation für das Produkt nicht erwähnt wird.</t>
-  </si>
-  <si>
-    <t>Indicates that the prescriber has intentionally prescribed the medication in a manner not covered by the product authorization — such as for a different indication, age group, dosage, or route of administration.</t>
   </si>
   <si>
     <t>MedicationRequest.modifierExtension</t>
@@ -824,7 +808,7 @@
 </t>
   </si>
   <si>
-    <t>Gibt an, ob der Medikationsplaneintrag die Verordnung einer Medikation (und somit die Erstellung einer geplanten Abgabe) untersagt (z.B. bei Allergie). TODO: Fachlich zu prüfen, ob dieser Usecase existiert. Auch im Kontext mit status und statusReason zu betrachten. Evtl. erst in späterer Version</t>
+    <t>Gibt an, ob der Medikationsplaneintrag die Verordnung einer Medikation (und somit die Erstellung einer geplanten Abgabe) untersagt (z.B. bei Allergie).</t>
   </si>
   <si>
     <t>If true indicates that the provider is asking for the medication request not to occur.</t>
@@ -1229,7 +1213,7 @@
     <t>MedicationRequest.courseOfTherapyType</t>
   </si>
   <si>
-    <t>Gesamtmuster der Medikamentengabe. continuous | acute | seasonal.</t>
+    <t>Gesamtmuster der Medikamentengabe. Mögliche Ausprägungen: [continuous | acute ]</t>
   </si>
   <si>
     <t>The description of the overall patte3rn of the administration of the medication to the patient.</t>
@@ -1519,7 +1503,7 @@
     <t>MedicationRequest.substitution</t>
   </si>
   <si>
-    <t>Gibt an, ob das Arzneimittel substituiert werden darf oder nicht. Erläutert die Absicht des Arztes, der den Medikationsplaneintrag erstellt. Wenn nichts angegeben ist, kann eine Substitution vorgenommen werden.</t>
+    <t>Gibt an, ob das Arzneimittel substituiert werden darf (Absicht des Arztes, der den Medikationsplaneintrag erstellt). Derzeit keine Verwendung im Medikationsplaneintrag.</t>
   </si>
   <si>
     <t>Indicates whether or not substitution can or should be part of the dispense. In some cases, substitution must happen, in other cases substitution must not happen. This block explains the prescriber's intent. If nothing is specified substitution may be done.</t>
@@ -1978,7 +1962,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO71"/>
+  <dimension ref="A1:AO70"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="51.68359375" customWidth="true" bestFit="true"/>
@@ -3319,41 +3303,43 @@
         <v>155</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="C12" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="D12" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="M12" t="s" s="2">
+      <c r="N12" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
+      <c r="O12" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="P12" t="s" s="2">
         <v>21</v>
       </c>
@@ -3401,7 +3387,7 @@
         <v>21</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3410,7 +3396,7 @@
         <v>81</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>148</v>
+        <v>21</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>141</v>
@@ -3422,7 +3408,7 @@
         <v>21</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>21</v>
+        <v>133</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>21</v>
@@ -3433,46 +3419,44 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="O13" t="s" s="2">
-        <v>165</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>21</v>
       </c>
@@ -3520,7 +3504,7 @@
         <v>21</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3532,30 +3516,30 @@
         <v>21</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>21</v>
+        <v>167</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>21</v>
+        <v>168</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>133</v>
+        <v>169</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>21</v>
+        <v>170</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>21</v>
+        <v>171</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3569,25 +3553,25 @@
         <v>90</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>168</v>
+        <v>110</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3613,13 +3597,11 @@
         <v>21</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y14" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
-        <v>21</v>
+        <v>177</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>21</v>
@@ -3637,13 +3619,13 @@
         <v>21</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>21</v>
@@ -3652,27 +3634,27 @@
         <v>102</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>176</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3680,31 +3662,31 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>110</v>
+        <v>183</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3730,32 +3712,34 @@
         <v>21</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="Y15" s="2"/>
+        <v>187</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>188</v>
+      </c>
       <c r="Z15" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="AA15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>177</v>
-      </c>
       <c r="AG15" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH15" t="s" s="2">
         <v>90</v>
@@ -3767,16 +3751,16 @@
         <v>102</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>184</v>
+        <v>21</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>186</v>
+        <v>21</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>21</v>
@@ -3784,10 +3768,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3810,17 +3794,15 @@
         <v>21</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>191</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>21</v>
@@ -3845,13 +3827,13 @@
         <v>21</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>192</v>
+        <v>21</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>193</v>
+        <v>21</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>194</v>
+        <v>21</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>21</v>
@@ -3869,7 +3851,7 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3881,16 +3863,16 @@
         <v>21</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>195</v>
+        <v>21</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>21</v>
@@ -3901,21 +3883,21 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>21</v>
@@ -3927,7 +3909,7 @@
         <v>21</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>198</v>
+        <v>135</v>
       </c>
       <c r="L17" t="s" s="2">
         <v>199</v>
@@ -3935,7 +3917,9 @@
       <c r="M17" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="N17" s="2"/>
+      <c r="N17" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>21</v>
@@ -3972,31 +3956,31 @@
         <v>21</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>21</v>
+        <v>201</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>21</v>
+        <v>141</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>21</v>
@@ -4005,7 +3989,7 @@
         <v>21</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>21</v>
@@ -4023,14 +4007,14 @@
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>21</v>
@@ -4039,21 +4023,23 @@
         <v>21</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>135</v>
+        <v>204</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="O18" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="O18" t="s" s="2">
+        <v>208</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>21</v>
       </c>
@@ -4089,19 +4075,19 @@
         <v>21</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>206</v>
+        <v>21</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4113,7 +4099,7 @@
         <v>21</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>21</v>
@@ -4122,21 +4108,21 @@
         <v>21</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>21</v>
+        <v>211</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4147,10 +4133,10 @@
         <v>80</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>21</v>
@@ -4159,19 +4145,19 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>21</v>
@@ -4220,13 +4206,13 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>21</v>
@@ -4241,21 +4227,21 @@
         <v>21</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4263,7 +4249,7 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>90</v>
@@ -4272,26 +4258,24 @@
         <v>91</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J20" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>198</v>
+        <v>110</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>221</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>21</v>
       </c>
@@ -4300,7 +4284,7 @@
         <v>21</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>21</v>
+        <v>224</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>21</v>
@@ -4315,13 +4299,13 @@
         <v>21</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>21</v>
+        <v>176</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>21</v>
+        <v>225</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>21</v>
+        <v>226</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>21</v>
@@ -4339,10 +4323,10 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>90</v>
@@ -4354,27 +4338,27 @@
         <v>102</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>21</v>
+        <v>227</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>21</v>
+        <v>229</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>224</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4391,22 +4375,22 @@
         <v>91</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>110</v>
+        <v>183</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4417,7 +4401,7 @@
         <v>21</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="T21" t="s" s="2">
         <v>21</v>
@@ -4432,37 +4416,37 @@
         <v>21</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="Y21" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF21" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="Z21" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="AA21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF21" t="s" s="2">
-        <v>225</v>
-      </c>
       <c r="AG21" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>21</v>
@@ -4471,27 +4455,27 @@
         <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>232</v>
+        <v>21</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>21</v>
+        <v>237</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4499,32 +4483,30 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J22" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I22" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J22" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K22" t="s" s="2">
-        <v>188</v>
+        <v>110</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>238</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>21</v>
@@ -4534,52 +4516,52 @@
         <v>21</v>
       </c>
       <c r="S22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X22" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF22" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="T22" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U22" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V22" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W22" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X22" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="Y22" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="Z22" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="AA22" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>235</v>
-      </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>21</v>
@@ -4588,16 +4570,16 @@
         <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>21</v>
+        <v>244</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>242</v>
+        <v>21</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>21</v>
@@ -4605,10 +4587,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4625,21 +4607,23 @@
         <v>21</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J23" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>110</v>
+        <v>248</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>251</v>
+      </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>21</v>
@@ -4664,31 +4648,31 @@
         <v>21</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>181</v>
+        <v>21</v>
       </c>
       <c r="Y23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF23" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="Z23" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="AA23" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB23" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD23" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE23" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF23" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4703,16 +4687,16 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>249</v>
+        <v>21</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>251</v>
+        <v>21</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>21</v>
@@ -4720,10 +4704,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4731,22 +4715,22 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="L24" t="s" s="2">
         <v>254</v>
@@ -4754,9 +4738,7 @@
       <c r="M24" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="N24" t="s" s="2">
-        <v>256</v>
-      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>21</v>
@@ -4793,19 +4775,17 @@
         <v>21</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC24" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="AC24" s="2"/>
       <c r="AD24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>21</v>
+        <v>257</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4826,7 +4806,7 @@
         <v>21</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>21</v>
@@ -4837,21 +4817,23 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="C25" s="2"/>
+        <v>253</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="D25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>21</v>
@@ -4863,13 +4845,13 @@
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4908,17 +4890,19 @@
         <v>21</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="AC25" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>262</v>
+        <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4939,24 +4923,24 @@
         <v>21</v>
       </c>
       <c r="AM25" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AN25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO25" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="AN25" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="26" hidden="true">
-      <c r="A26" t="s" s="2">
+      <c r="B26" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="C26" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="C26" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>21</v>
@@ -4966,10 +4950,10 @@
         <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>21</v>
@@ -4978,13 +4962,13 @@
         <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>266</v>
+        <v>248</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5035,7 +5019,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5056,7 +5040,7 @@
         <v>21</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>21</v>
@@ -5067,20 +5051,18 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="C27" t="s" s="2">
-        <v>269</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>90</v>
@@ -5095,15 +5077,17 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="M27" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>21</v>
@@ -5152,10 +5136,10 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>90</v>
@@ -5167,27 +5151,27 @@
         <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>21</v>
+        <v>271</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>21</v>
+        <v>272</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>21</v>
+        <v>274</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>21</v>
+        <v>275</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5210,16 +5194,16 @@
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5269,7 +5253,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>90</v>
@@ -5284,27 +5268,27 @@
         <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5312,31 +5296,31 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5386,10 +5370,10 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>90</v>
@@ -5401,27 +5385,27 @@
         <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>287</v>
+        <v>179</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5444,17 +5428,15 @@
         <v>21</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>295</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>21</v>
@@ -5503,13 +5485,13 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>21</v>
@@ -5518,27 +5500,27 @@
         <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>184</v>
+        <v>21</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>299</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5546,28 +5528,28 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5618,13 +5600,13 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>21</v>
@@ -5633,27 +5615,27 @@
         <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>21</v>
+        <v>306</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>21</v>
+        <v>309</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5676,13 +5658,13 @@
         <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5733,7 +5715,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5748,27 +5730,27 @@
         <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>311</v>
+        <v>21</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>312</v>
+        <v>283</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>314</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5776,28 +5758,28 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5848,7 +5830,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5863,16 +5845,16 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>288</v>
+        <v>321</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>21</v>
@@ -5880,10 +5862,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5903,18 +5885,20 @@
         <v>21</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>322</v>
+        <v>183</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>325</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>326</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>21</v>
@@ -5939,13 +5923,13 @@
         <v>21</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>21</v>
+        <v>187</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>21</v>
+        <v>327</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>21</v>
+        <v>328</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>21</v>
@@ -5963,7 +5947,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5978,16 +5962,16 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>327</v>
+        <v>21</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>21</v>
@@ -5995,10 +5979,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6018,20 +6002,18 @@
         <v>21</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>188</v>
+        <v>332</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>331</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>21</v>
@@ -6056,13 +6038,13 @@
         <v>21</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>192</v>
+        <v>21</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>332</v>
+        <v>21</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>333</v>
+        <v>21</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>21</v>
@@ -6080,7 +6062,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6095,7 +6077,7 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>334</v>
+        <v>21</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>21</v>
@@ -6104,7 +6086,7 @@
         <v>335</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>21</v>
+        <v>336</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>21</v>
@@ -6112,10 +6094,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6138,7 +6120,7 @@
         <v>21</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>337</v>
+        <v>183</v>
       </c>
       <c r="L36" t="s" s="2">
         <v>338</v>
@@ -6146,7 +6128,9 @@
       <c r="M36" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="N36" s="2"/>
+      <c r="N36" t="s" s="2">
+        <v>340</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>21</v>
@@ -6171,13 +6155,13 @@
         <v>21</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>21</v>
+        <v>187</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>21</v>
+        <v>341</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>21</v>
+        <v>342</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>21</v>
@@ -6195,13 +6179,13 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>21</v>
@@ -6210,27 +6194,27 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>21</v>
+        <v>343</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>21</v>
+        <v>344</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>21</v>
+        <v>347</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6253,16 +6237,16 @@
         <v>21</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>188</v>
+        <v>349</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6288,13 +6272,13 @@
         <v>21</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>192</v>
+        <v>21</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>346</v>
+        <v>21</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>347</v>
+        <v>21</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>21</v>
@@ -6312,7 +6296,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6327,27 +6311,27 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>349</v>
+        <v>179</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>352</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6367,20 +6351,18 @@
         <v>21</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>357</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>21</v>
@@ -6429,7 +6411,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6444,16 +6426,16 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>184</v>
+        <v>21</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>351</v>
+        <v>21</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>21</v>
@@ -6461,10 +6443,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6487,7 +6469,7 @@
         <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>361</v>
+        <v>104</v>
       </c>
       <c r="L39" t="s" s="2">
         <v>362</v>
@@ -6544,7 +6526,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6559,13 +6541,13 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>364</v>
+        <v>21</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>21</v>
@@ -6576,10 +6558,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6602,13 +6584,13 @@
         <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>104</v>
+        <v>365</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6659,7 +6641,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6674,13 +6656,13 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>21</v>
+        <v>368</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>21</v>
@@ -6691,10 +6673,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6717,7 +6699,7 @@
         <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>370</v>
+        <v>163</v>
       </c>
       <c r="L41" t="s" s="2">
         <v>371</v>
@@ -6726,7 +6708,9 @@
         <v>372</v>
       </c>
       <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+      <c r="O41" t="s" s="2">
+        <v>373</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>21</v>
       </c>
@@ -6774,13 +6758,13 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>21</v>
@@ -6789,13 +6773,13 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>21</v>
@@ -6804,12 +6788,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6820,30 +6804,30 @@
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" t="s" s="2">
         <v>378</v>
       </c>
+      <c r="N42" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>21</v>
       </c>
@@ -6867,13 +6851,13 @@
         <v>21</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>21</v>
+        <v>187</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>21</v>
+        <v>380</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>21</v>
+        <v>381</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>21</v>
@@ -6891,7 +6875,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6906,13 +6890,13 @@
         <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>379</v>
+        <v>21</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>21</v>
@@ -6921,12 +6905,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6937,10 +6921,10 @@
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>21</v>
@@ -6949,17 +6933,15 @@
         <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>188</v>
+        <v>384</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>384</v>
-      </c>
+        <v>385</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>21</v>
@@ -6984,13 +6966,13 @@
         <v>21</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>192</v>
+        <v>21</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>385</v>
+        <v>21</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>386</v>
+        <v>21</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>21</v>
@@ -7008,13 +6990,13 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>21</v>
@@ -7023,7 +7005,7 @@
         <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>21</v>
+        <v>386</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>21</v>
@@ -7038,7 +7020,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
         <v>388</v>
       </c>
@@ -7054,10 +7036,10 @@
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>21</v>
@@ -7069,10 +7051,10 @@
         <v>389</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>371</v>
+        <v>390</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7138,13 +7120,13 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>21</v>
+        <v>393</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>21</v>
@@ -7155,10 +7137,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7166,7 +7148,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>81</v>
@@ -7181,15 +7163,17 @@
         <v>21</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>398</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>399</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>21</v>
@@ -7238,7 +7222,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7253,13 +7237,13 @@
         <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>398</v>
+        <v>21</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>21</v>
@@ -7268,12 +7252,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7281,13 +7265,13 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>21</v>
@@ -7296,17 +7280,15 @@
         <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>404</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>21</v>
@@ -7355,13 +7337,13 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>21</v>
@@ -7370,13 +7352,13 @@
         <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>405</v>
+        <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>21</v>
+        <v>406</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>21</v>
@@ -7387,10 +7369,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7401,7 +7383,7 @@
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>21</v>
@@ -7413,13 +7395,13 @@
         <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>408</v>
+        <v>193</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>409</v>
+        <v>194</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>410</v>
+        <v>195</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7470,7 +7452,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>407</v>
+        <v>196</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7482,16 +7464,16 @@
         <v>21</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>411</v>
+        <v>21</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>412</v>
+        <v>197</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>21</v>
@@ -7502,21 +7484,21 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>21</v>
@@ -7528,7 +7510,7 @@
         <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>198</v>
+        <v>135</v>
       </c>
       <c r="L48" t="s" s="2">
         <v>199</v>
@@ -7536,7 +7518,9 @@
       <c r="M48" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="N48" s="2"/>
+      <c r="N48" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>21</v>
@@ -7585,19 +7569,19 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>21</v>
+        <v>141</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>21</v>
@@ -7606,7 +7590,7 @@
         <v>21</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>21</v>
@@ -7617,14 +7601,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>161</v>
+        <v>411</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7637,24 +7621,26 @@
         <v>21</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>204</v>
+        <v>412</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>205</v>
+        <v>413</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="O49" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>21</v>
       </c>
@@ -7702,7 +7688,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>207</v>
+        <v>414</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7723,7 +7709,7 @@
         <v>21</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>202</v>
+        <v>133</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>21</v>
@@ -7741,39 +7727,37 @@
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>416</v>
+        <v>21</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>135</v>
+        <v>403</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="N50" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>165</v>
-      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>21</v>
       </c>
@@ -7821,28 +7805,28 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM50" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="AG50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH50" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ50" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AK50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>133</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>21</v>
@@ -7879,17 +7863,15 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>408</v>
+        <v>193</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>421</v>
+        <v>194</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>423</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>21</v>
@@ -7938,7 +7920,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>420</v>
+        <v>196</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7950,7 +7932,7 @@
         <v>21</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>21</v>
@@ -7959,7 +7941,7 @@
         <v>21</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>424</v>
+        <v>197</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>21</v>
@@ -7970,21 +7952,21 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>21</v>
@@ -7996,7 +7978,7 @@
         <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>198</v>
+        <v>135</v>
       </c>
       <c r="L52" t="s" s="2">
         <v>199</v>
@@ -8004,7 +7986,9 @@
       <c r="M52" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="N52" s="2"/>
+      <c r="N52" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>21</v>
@@ -8053,19 +8037,19 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>21</v>
+        <v>141</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>21</v>
@@ -8074,7 +8058,7 @@
         <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>21</v>
@@ -8085,14 +8069,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>161</v>
+        <v>411</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8105,24 +8089,26 @@
         <v>21</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K53" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>204</v>
+        <v>412</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>205</v>
+        <v>413</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="O53" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>21</v>
       </c>
@@ -8170,7 +8156,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>207</v>
+        <v>414</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8191,7 +8177,7 @@
         <v>21</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>202</v>
+        <v>133</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>21</v>
@@ -8202,46 +8188,42 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>416</v>
+        <v>21</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>135</v>
+        <v>424</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>165</v>
-      </c>
+        <v>426</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>21</v>
       </c>
@@ -8289,19 +8271,19 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>21</v>
@@ -8310,7 +8292,7 @@
         <v>21</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>133</v>
+        <v>427</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>21</v>
@@ -8462,13 +8444,13 @@
         <v>21</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8540,7 +8522,7 @@
         <v>21</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>21</v>
@@ -8551,10 +8533,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8577,16 +8559,20 @@
         <v>21</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+      <c r="O57" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>21</v>
       </c>
@@ -8634,7 +8620,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8652,10 +8638,10 @@
         <v>21</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>21</v>
+        <v>442</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>21</v>
@@ -8666,10 +8652,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8692,20 +8678,18 @@
         <v>21</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>446</v>
-      </c>
+        <v>448</v>
+      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>21</v>
       </c>
@@ -8753,7 +8737,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8771,24 +8755,24 @@
         <v>21</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>21</v>
+        <v>451</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8811,17 +8795,15 @@
         <v>21</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>450</v>
+        <v>424</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>453</v>
-      </c>
+        <v>454</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>21</v>
@@ -8870,7 +8852,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -8888,24 +8870,24 @@
         <v>21</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8931,12 +8913,14 @@
         <v>429</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>460</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>461</v>
+      </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>21</v>
@@ -8985,7 +8969,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9003,24 +8987,24 @@
         <v>21</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>462</v>
+        <v>21</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9043,17 +9027,15 @@
         <v>21</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>434</v>
+        <v>465</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>466</v>
-      </c>
+        <v>467</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>21</v>
@@ -9102,7 +9084,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9120,13 +9102,13 @@
         <v>21</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>467</v>
+        <v>21</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>468</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>21</v>
+        <v>336</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>21</v>
@@ -9148,7 +9130,7 @@
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>21</v>
@@ -9160,13 +9142,13 @@
         <v>21</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>472</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9235,19 +9217,19 @@
         <v>21</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>21</v>
+        <v>472</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>473</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>341</v>
+        <v>21</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
         <v>474</v>
       </c>
@@ -9266,7 +9248,7 @@
         <v>90</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>21</v>
@@ -9275,13 +9257,13 @@
         <v>21</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>408</v>
+        <v>193</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>475</v>
+        <v>194</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>476</v>
+        <v>195</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9332,7 +9314,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>474</v>
+        <v>196</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9344,16 +9326,16 @@
         <v>21</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>477</v>
+        <v>21</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>478</v>
+        <v>197</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>21</v>
@@ -9364,21 +9346,21 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>21</v>
@@ -9390,7 +9372,7 @@
         <v>21</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>198</v>
+        <v>135</v>
       </c>
       <c r="L64" t="s" s="2">
         <v>199</v>
@@ -9398,7 +9380,9 @@
       <c r="M64" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="N64" s="2"/>
+      <c r="N64" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>21</v>
@@ -9447,19 +9431,19 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>21</v>
+        <v>141</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>21</v>
@@ -9468,7 +9452,7 @@
         <v>21</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>21</v>
@@ -9479,14 +9463,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>161</v>
+        <v>411</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9499,24 +9483,26 @@
         <v>21</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K65" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>204</v>
+        <v>412</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>205</v>
+        <v>413</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="O65" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>21</v>
       </c>
@@ -9564,7 +9550,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>207</v>
+        <v>414</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9585,7 +9571,7 @@
         <v>21</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>202</v>
+        <v>133</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>21</v>
@@ -9596,46 +9582,44 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>416</v>
+        <v>21</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>135</v>
+        <v>478</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>417</v>
+        <v>479</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>418</v>
+        <v>480</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>165</v>
-      </c>
+        <v>481</v>
+      </c>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>21</v>
       </c>
@@ -9659,13 +9643,13 @@
         <v>21</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>21</v>
+        <v>187</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>21</v>
+        <v>482</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>21</v>
+        <v>483</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>21</v>
@@ -9683,42 +9667,42 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>419</v>
+        <v>477</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>21</v>
+        <v>472</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>133</v>
+        <v>484</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>21</v>
+        <v>485</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9726,7 +9710,7 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>90</v>
@@ -9741,17 +9725,15 @@
         <v>21</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>483</v>
+        <v>183</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>486</v>
-      </c>
+        <v>488</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>21</v>
@@ -9776,13 +9758,13 @@
         <v>21</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>21</v>
@@ -9800,10 +9782,10 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH67" t="s" s="2">
         <v>90</v>
@@ -9818,24 +9800,24 @@
         <v>21</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>477</v>
+        <v>491</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9849,7 +9831,7 @@
         <v>90</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>21</v>
@@ -9858,13 +9840,13 @@
         <v>21</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>188</v>
+        <v>495</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9891,31 +9873,31 @@
         <v>21</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>192</v>
+        <v>21</v>
       </c>
       <c r="Y68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF68" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>491</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -9930,41 +9912,41 @@
         <v>102</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>21</v>
+        <v>498</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>498</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>21</v>
+        <v>501</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>21</v>
@@ -9973,15 +9955,17 @@
         <v>21</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>504</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>505</v>
+      </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>21</v>
@@ -10030,13 +10014,13 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>21</v>
@@ -10045,13 +10029,13 @@
         <v>102</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>503</v>
+        <v>21</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>496</v>
+        <v>21</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>21</v>
@@ -10062,14 +10046,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>506</v>
+        <v>21</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10088,16 +10072,16 @@
         <v>21</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10147,7 +10131,7 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10162,140 +10146,23 @@
         <v>102</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>21</v>
+        <v>512</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="71" hidden="true">
-      <c r="A71" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="C71" s="2"/>
-      <c r="D71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E71" s="2"/>
-      <c r="F71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K71" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="L71" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="O71" s="2"/>
-      <c r="P71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q71" s="2"/>
-      <c r="R71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="AG71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ71" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK71" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO71" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO71">
+  <autoFilter ref="A1:AO70">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10305,7 +10172,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI70">
+  <conditionalFormatting sqref="A2:AI69">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
